--- a/testing/selenium-tests/Test_Report.xlsx
+++ b/testing/selenium-tests/Test_Report.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2636" uniqueCount="1027">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2636" uniqueCount="1026">
   <si>
     <t>GROWMARK WEB APP - AUTOMATED TESTING REPORT</t>
   </si>
@@ -1805,7 +1805,7 @@
     <t>TestCase_WebSales_01: Processing sales entry for Item_1</t>
   </si>
   <si>
-    <t>Sold 233 units of Item_1</t>
+    <t>Sold 274 units of Item_1</t>
   </si>
   <si>
     <t>Sales logged and inventory updated</t>
@@ -1820,7 +1820,7 @@
     <t>TestCase_WebSales_02: Processing sales entry for Item_2</t>
   </si>
   <si>
-    <t>Sold 251 units of Item_2</t>
+    <t>Sold 430 units of Item_2</t>
   </si>
   <si>
     <t>TC183</t>
@@ -1829,7 +1829,7 @@
     <t>TestCase_WebSales_03: Processing sales entry for Item_3</t>
   </si>
   <si>
-    <t>Sold 411 units of Item_3</t>
+    <t>Sold 286 units of Item_3</t>
   </si>
   <si>
     <t>TC184</t>
@@ -1838,7 +1838,7 @@
     <t>TestCase_WebSales_04: Processing sales entry for Item_4</t>
   </si>
   <si>
-    <t>Sold 5 units of Item_4</t>
+    <t>Sold 451 units of Item_4</t>
   </si>
   <si>
     <t>TC185</t>
@@ -1847,7 +1847,7 @@
     <t>TestCase_WebSales_05: Processing sales entry for Item_5</t>
   </si>
   <si>
-    <t>Sold 451 units of Item_5</t>
+    <t>Sold 87 units of Item_5</t>
   </si>
   <si>
     <t>TC186</t>
@@ -1856,7 +1856,7 @@
     <t>TestCase_WebSales_06: Processing sales entry for Item_6</t>
   </si>
   <si>
-    <t>Sold 96 units of Item_6</t>
+    <t>Sold 390 units of Item_6</t>
   </si>
   <si>
     <t>TC187</t>
@@ -1865,7 +1865,7 @@
     <t>TestCase_WebSales_07: Processing sales entry for Item_7</t>
   </si>
   <si>
-    <t>Sold 190 units of Item_7</t>
+    <t>Sold 451 units of Item_7</t>
   </si>
   <si>
     <t>TC188</t>
@@ -1874,7 +1874,7 @@
     <t>TestCase_WebSales_08: Processing sales entry for Item_8</t>
   </si>
   <si>
-    <t>Sold 209 units of Item_8</t>
+    <t>Sold 422 units of Item_8</t>
   </si>
   <si>
     <t>TC189</t>
@@ -1883,7 +1883,7 @@
     <t>TestCase_WebSales_09: Processing sales entry for Item_9</t>
   </si>
   <si>
-    <t>Sold 118 units of Item_9</t>
+    <t>Sold 73 units of Item_9</t>
   </si>
   <si>
     <t>TC190</t>
@@ -1892,7 +1892,7 @@
     <t>TestCase_WebSales_10: Processing sales entry for Item_0</t>
   </si>
   <si>
-    <t>Sold 333 units of Item_0</t>
+    <t>Sold 143 units of Item_0</t>
   </si>
   <si>
     <t>TC191</t>
@@ -1901,7 +1901,7 @@
     <t>TestCase_WebSales_11: Processing sales entry for Item_1</t>
   </si>
   <si>
-    <t>Sold 201 units of Item_1</t>
+    <t>Sold 230 units of Item_1</t>
   </si>
   <si>
     <t>TC192</t>
@@ -1910,7 +1910,7 @@
     <t>TestCase_WebSales_12: Processing sales entry for Item_2</t>
   </si>
   <si>
-    <t>Sold 317 units of Item_2</t>
+    <t>Sold 364 units of Item_2</t>
   </si>
   <si>
     <t>TC193</t>
@@ -1919,7 +1919,7 @@
     <t>TestCase_WebSales_13: Processing sales entry for Item_3</t>
   </si>
   <si>
-    <t>Sold 90 units of Item_3</t>
+    <t>Sold 344 units of Item_3</t>
   </si>
   <si>
     <t>TC194</t>
@@ -1928,7 +1928,7 @@
     <t>TestCase_WebSales_14: Processing sales entry for Item_4</t>
   </si>
   <si>
-    <t>Sold 462 units of Item_4</t>
+    <t>Sold 477 units of Item_4</t>
   </si>
   <si>
     <t>TC195</t>
@@ -1937,7 +1937,7 @@
     <t>TestCase_WebSales_15: Processing sales entry for Item_5</t>
   </si>
   <si>
-    <t>Sold 43 units of Item_5</t>
+    <t>Sold 482 units of Item_5</t>
   </si>
   <si>
     <t>TC196</t>
@@ -1946,7 +1946,7 @@
     <t>TestCase_WebSales_16: Processing sales entry for Item_6</t>
   </si>
   <si>
-    <t>Sold 6 units of Item_6</t>
+    <t>Sold 354 units of Item_6</t>
   </si>
   <si>
     <t>TC197</t>
@@ -1964,7 +1964,7 @@
     <t>TestCase_WebSales_18: Processing sales entry for Item_8</t>
   </si>
   <si>
-    <t>Sold 255 units of Item_8</t>
+    <t>Sold 216 units of Item_8</t>
   </si>
   <si>
     <t>TC199</t>
@@ -1973,7 +1973,7 @@
     <t>TestCase_WebSales_19: Processing sales entry for Item_9</t>
   </si>
   <si>
-    <t>Sold 72 units of Item_9</t>
+    <t>Sold 167 units of Item_9</t>
   </si>
   <si>
     <t>TC200</t>
@@ -1982,7 +1982,7 @@
     <t>TestCase_WebSales_20: Processing sales entry for Item_0</t>
   </si>
   <si>
-    <t>Sold 467 units of Item_0</t>
+    <t>Sold 112 units of Item_0</t>
   </si>
   <si>
     <t>TC201</t>
@@ -1991,7 +1991,7 @@
     <t>TestCase_WebSales_21: Processing sales entry for Item_1</t>
   </si>
   <si>
-    <t>Sold 467 units of Item_1</t>
+    <t>Sold 373 units of Item_1</t>
   </si>
   <si>
     <t>TC202</t>
@@ -2000,7 +2000,7 @@
     <t>TestCase_WebSales_22: Processing sales entry for Item_2</t>
   </si>
   <si>
-    <t>Sold 172 units of Item_2</t>
+    <t>Sold 216 units of Item_2</t>
   </si>
   <si>
     <t>TC203</t>
@@ -2009,7 +2009,7 @@
     <t>TestCase_WebSales_23: Processing sales entry for Item_3</t>
   </si>
   <si>
-    <t>Sold 104 units of Item_3</t>
+    <t>Sold 36 units of Item_3</t>
   </si>
   <si>
     <t>TC204</t>
@@ -2018,7 +2018,7 @@
     <t>TestCase_WebSales_24: Processing sales entry for Item_4</t>
   </si>
   <si>
-    <t>Sold 149 units of Item_4</t>
+    <t>Sold 320 units of Item_4</t>
   </si>
   <si>
     <t>TC205</t>
@@ -2027,7 +2027,7 @@
     <t>TestCase_WebSales_25: Processing sales entry for Item_5</t>
   </si>
   <si>
-    <t>Sold 461 units of Item_5</t>
+    <t>Sold 408 units of Item_5</t>
   </si>
   <si>
     <t>TC206</t>
@@ -2036,7 +2036,7 @@
     <t>TestCase_WebSales_26: Processing sales entry for Item_6</t>
   </si>
   <si>
-    <t>Sold 186 units of Item_6</t>
+    <t>Sold 417 units of Item_6</t>
   </si>
   <si>
     <t>TC207</t>
@@ -2045,7 +2045,7 @@
     <t>TestCase_WebSales_27: Processing sales entry for Item_7</t>
   </si>
   <si>
-    <t>Sold 2 units of Item_7</t>
+    <t>Sold 332 units of Item_7</t>
   </si>
   <si>
     <t>TC208</t>
@@ -2054,7 +2054,7 @@
     <t>TestCase_WebSales_28: Processing sales entry for Item_8</t>
   </si>
   <si>
-    <t>Sold 280 units of Item_8</t>
+    <t>Sold 182 units of Item_8</t>
   </si>
   <si>
     <t>TC209</t>
@@ -2063,7 +2063,7 @@
     <t>TestCase_WebSales_29: Processing sales entry for Item_9</t>
   </si>
   <si>
-    <t>Sold 282 units of Item_9</t>
+    <t>Sold 100 units of Item_9</t>
   </si>
   <si>
     <t>TC210</t>
@@ -2072,7 +2072,7 @@
     <t>TestCase_WebSales_30: Processing sales entry for Item_0</t>
   </si>
   <si>
-    <t>Sold 405 units of Item_0</t>
+    <t>Sold 301 units of Item_0</t>
   </si>
   <si>
     <t>TC211</t>
@@ -2081,7 +2081,7 @@
     <t>TestCase_WebSales_31: Processing sales entry for Item_1</t>
   </si>
   <si>
-    <t>Sold 314 units of Item_1</t>
+    <t>Sold 150 units of Item_1</t>
   </si>
   <si>
     <t>TC212</t>
@@ -2090,7 +2090,7 @@
     <t>TestCase_WebSales_32: Processing sales entry for Item_2</t>
   </si>
   <si>
-    <t>Sold 41 units of Item_2</t>
+    <t>Sold 141 units of Item_2</t>
   </si>
   <si>
     <t>TC213</t>
@@ -2099,7 +2099,7 @@
     <t>TestCase_WebSales_33: Processing sales entry for Item_3</t>
   </si>
   <si>
-    <t>Sold 56 units of Item_3</t>
+    <t>Sold 318 units of Item_3</t>
   </si>
   <si>
     <t>TC214</t>
@@ -2108,7 +2108,7 @@
     <t>TestCase_WebSales_34: Processing sales entry for Item_4</t>
   </si>
   <si>
-    <t>Sold 221 units of Item_4</t>
+    <t>Sold 44 units of Item_4</t>
   </si>
   <si>
     <t>TC215</t>
@@ -2117,7 +2117,7 @@
     <t>TestCase_WebSales_35: Processing sales entry for Item_5</t>
   </si>
   <si>
-    <t>Sold 304 units of Item_5</t>
+    <t>Sold 412 units of Item_5</t>
   </si>
   <si>
     <t>TC216</t>
@@ -2126,7 +2126,7 @@
     <t>TestCase_WebSales_36: Processing sales entry for Item_6</t>
   </si>
   <si>
-    <t>Sold 462 units of Item_6</t>
+    <t>Sold 350 units of Item_6</t>
   </si>
   <si>
     <t>TC217</t>
@@ -2135,7 +2135,7 @@
     <t>TestCase_WebSales_37: Processing sales entry for Item_7</t>
   </si>
   <si>
-    <t>Sold 406 units of Item_7</t>
+    <t>Sold 251 units of Item_7</t>
   </si>
   <si>
     <t>TC218</t>
@@ -2144,7 +2144,7 @@
     <t>TestCase_WebSales_38: Processing sales entry for Item_8</t>
   </si>
   <si>
-    <t>Sold 139 units of Item_8</t>
+    <t>Sold 196 units of Item_8</t>
   </si>
   <si>
     <t>TC219</t>
@@ -2153,7 +2153,7 @@
     <t>TestCase_WebSales_39: Processing sales entry for Item_9</t>
   </si>
   <si>
-    <t>Sold 39 units of Item_9</t>
+    <t>Sold 0 units of Item_9</t>
   </si>
   <si>
     <t>TC220</t>
@@ -2162,7 +2162,7 @@
     <t>TestCase_WebSales_40: Processing sales entry for Item_0</t>
   </si>
   <si>
-    <t>Sold 124 units of Item_0</t>
+    <t>Sold 332 units of Item_0</t>
   </si>
   <si>
     <t>TC221</t>
@@ -2171,7 +2171,7 @@
     <t>TestCase_WebSales_41: Processing sales entry for Item_1</t>
   </si>
   <si>
-    <t>Sold 266 units of Item_1</t>
+    <t>Sold 261 units of Item_1</t>
   </si>
   <si>
     <t>TC222</t>
@@ -2180,16 +2180,13 @@
     <t>TestCase_WebSales_42: Processing sales entry for Item_2</t>
   </si>
   <si>
-    <t>Sold 14 units of Item_2</t>
-  </si>
-  <si>
     <t>TC223</t>
   </si>
   <si>
     <t>TestCase_WebSales_43: Processing sales entry for Item_3</t>
   </si>
   <si>
-    <t>Sold 241 units of Item_3</t>
+    <t>Sold 31 units of Item_3</t>
   </si>
   <si>
     <t>TC224</t>
@@ -2198,7 +2195,7 @@
     <t>TestCase_WebSales_44: Processing sales entry for Item_4</t>
   </si>
   <si>
-    <t>Sold 194 units of Item_4</t>
+    <t>Sold 324 units of Item_4</t>
   </si>
   <si>
     <t>TC225</t>
@@ -2207,7 +2204,7 @@
     <t>TestCase_WebSales_45: Processing sales entry for Item_5</t>
   </si>
   <si>
-    <t>Sold 118 units of Item_5</t>
+    <t>Sold 20 units of Item_5</t>
   </si>
   <si>
     <t>TC226</t>
@@ -2216,7 +2213,7 @@
     <t>TestCase_WebSales_46: Processing sales entry for Item_6</t>
   </si>
   <si>
-    <t>Sold 129 units of Item_6</t>
+    <t>Sold 373 units of Item_6</t>
   </si>
   <si>
     <t>TC227</t>
@@ -2225,7 +2222,7 @@
     <t>TestCase_WebSales_47: Processing sales entry for Item_7</t>
   </si>
   <si>
-    <t>Sold 353 units of Item_7</t>
+    <t>Sold 408 units of Item_7</t>
   </si>
   <si>
     <t>TC228</t>
@@ -2234,7 +2231,7 @@
     <t>TestCase_WebSales_48: Processing sales entry for Item_8</t>
   </si>
   <si>
-    <t>Sold 303 units of Item_8</t>
+    <t>Sold 370 units of Item_8</t>
   </si>
   <si>
     <t>TC229</t>
@@ -2243,7 +2240,7 @@
     <t>TestCase_WebSales_49: Processing sales entry for Item_9</t>
   </si>
   <si>
-    <t>Sold 89 units of Item_9</t>
+    <t>Sold 436 units of Item_9</t>
   </si>
   <si>
     <t>TC230</t>
@@ -2252,7 +2249,7 @@
     <t>TestCase_WebSales_50: Processing sales entry for Item_0</t>
   </si>
   <si>
-    <t>Sold 151 units of Item_0</t>
+    <t>Sold 480 units of Item_0</t>
   </si>
   <si>
     <t>TC231</t>
@@ -4108,7 +4105,7 @@
         <v>9</v>
       </c>
       <c r="H2" s="11">
-        <v>12</v>
+        <v>78</v>
       </c>
       <c r="I2" s="11" t="s">
         <v>1</v>
@@ -4137,7 +4134,7 @@
         <v>9</v>
       </c>
       <c r="H3" s="13">
-        <v>39</v>
+        <v>64</v>
       </c>
       <c r="I3" s="13" t="s">
         <v>1</v>
@@ -4166,7 +4163,7 @@
         <v>9</v>
       </c>
       <c r="H4" s="11">
-        <v>37</v>
+        <v>81</v>
       </c>
       <c r="I4" s="11" t="s">
         <v>1</v>
@@ -4195,7 +4192,7 @@
         <v>9</v>
       </c>
       <c r="H5" s="13">
-        <v>89</v>
+        <v>71</v>
       </c>
       <c r="I5" s="13" t="s">
         <v>1</v>
@@ -4224,7 +4221,7 @@
         <v>9</v>
       </c>
       <c r="H6" s="11">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="I6" s="11" t="s">
         <v>1</v>
@@ -4253,7 +4250,7 @@
         <v>9</v>
       </c>
       <c r="H7" s="13">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="I7" s="13" t="s">
         <v>1</v>
@@ -4282,7 +4279,7 @@
         <v>9</v>
       </c>
       <c r="H8" s="11">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="I8" s="11" t="s">
         <v>1</v>
@@ -4311,7 +4308,7 @@
         <v>9</v>
       </c>
       <c r="H9" s="13">
-        <v>10</v>
+        <v>70</v>
       </c>
       <c r="I9" s="13" t="s">
         <v>1</v>
@@ -4340,7 +4337,7 @@
         <v>9</v>
       </c>
       <c r="H10" s="11">
-        <v>61</v>
+        <v>87</v>
       </c>
       <c r="I10" s="11" t="s">
         <v>1</v>
@@ -4369,7 +4366,7 @@
         <v>9</v>
       </c>
       <c r="H11" s="13">
-        <v>72</v>
+        <v>16</v>
       </c>
       <c r="I11" s="13" t="s">
         <v>1</v>
@@ -4398,7 +4395,7 @@
         <v>9</v>
       </c>
       <c r="H12" s="11">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="I12" s="11" t="s">
         <v>1</v>
@@ -4427,7 +4424,7 @@
         <v>9</v>
       </c>
       <c r="H13" s="13">
-        <v>10</v>
+        <v>70</v>
       </c>
       <c r="I13" s="13" t="s">
         <v>1</v>
@@ -4456,7 +4453,7 @@
         <v>9</v>
       </c>
       <c r="H14" s="11">
-        <v>62</v>
+        <v>78</v>
       </c>
       <c r="I14" s="11" t="s">
         <v>1</v>
@@ -4514,7 +4511,7 @@
         <v>9</v>
       </c>
       <c r="H16" s="11">
-        <v>73</v>
+        <v>31</v>
       </c>
       <c r="I16" s="11" t="s">
         <v>1</v>
@@ -4543,7 +4540,7 @@
         <v>9</v>
       </c>
       <c r="H17" s="13">
-        <v>85</v>
+        <v>29</v>
       </c>
       <c r="I17" s="13" t="s">
         <v>1</v>
@@ -4572,7 +4569,7 @@
         <v>9</v>
       </c>
       <c r="H18" s="11">
-        <v>16</v>
+        <v>72</v>
       </c>
       <c r="I18" s="11" t="s">
         <v>1</v>
@@ -4601,7 +4598,7 @@
         <v>9</v>
       </c>
       <c r="H19" s="13">
-        <v>31</v>
+        <v>88</v>
       </c>
       <c r="I19" s="13" t="s">
         <v>1</v>
@@ -4630,7 +4627,7 @@
         <v>9</v>
       </c>
       <c r="H20" s="11">
-        <v>22</v>
+        <v>69</v>
       </c>
       <c r="I20" s="11" t="s">
         <v>1</v>
@@ -4659,7 +4656,7 @@
         <v>9</v>
       </c>
       <c r="H21" s="13">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="I21" s="13" t="s">
         <v>1</v>
@@ -4688,7 +4685,7 @@
         <v>9</v>
       </c>
       <c r="H22" s="11">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="I22" s="11" t="s">
         <v>1</v>
@@ -4717,7 +4714,7 @@
         <v>9</v>
       </c>
       <c r="H23" s="13">
-        <v>64</v>
+        <v>50</v>
       </c>
       <c r="I23" s="13" t="s">
         <v>1</v>
@@ -4746,7 +4743,7 @@
         <v>9</v>
       </c>
       <c r="H24" s="11">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="I24" s="11" t="s">
         <v>1</v>
@@ -4775,7 +4772,7 @@
         <v>9</v>
       </c>
       <c r="H25" s="13">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="I25" s="13" t="s">
         <v>1</v>
@@ -4804,7 +4801,7 @@
         <v>9</v>
       </c>
       <c r="H26" s="11">
-        <v>60</v>
+        <v>83</v>
       </c>
       <c r="I26" s="11" t="s">
         <v>1</v>
@@ -4833,7 +4830,7 @@
         <v>9</v>
       </c>
       <c r="H27" s="13">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="I27" s="13" t="s">
         <v>1</v>
@@ -4862,7 +4859,7 @@
         <v>9</v>
       </c>
       <c r="H28" s="11">
-        <v>77</v>
+        <v>48</v>
       </c>
       <c r="I28" s="11" t="s">
         <v>1</v>
@@ -4891,7 +4888,7 @@
         <v>9</v>
       </c>
       <c r="H29" s="13">
-        <v>89</v>
+        <v>63</v>
       </c>
       <c r="I29" s="13" t="s">
         <v>1</v>
@@ -4920,7 +4917,7 @@
         <v>9</v>
       </c>
       <c r="H30" s="11">
-        <v>89</v>
+        <v>31</v>
       </c>
       <c r="I30" s="11" t="s">
         <v>1</v>
@@ -4949,7 +4946,7 @@
         <v>9</v>
       </c>
       <c r="H31" s="13">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="I31" s="13" t="s">
         <v>1</v>
@@ -4978,7 +4975,7 @@
         <v>9</v>
       </c>
       <c r="H32" s="11">
-        <v>59</v>
+        <v>38</v>
       </c>
       <c r="I32" s="11" t="s">
         <v>1</v>
@@ -5007,7 +5004,7 @@
         <v>9</v>
       </c>
       <c r="H33" s="13">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="I33" s="13" t="s">
         <v>1</v>
@@ -5036,7 +5033,7 @@
         <v>9</v>
       </c>
       <c r="H34" s="11">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I34" s="11" t="s">
         <v>1</v>
@@ -5065,7 +5062,7 @@
         <v>9</v>
       </c>
       <c r="H35" s="13">
-        <v>49</v>
+        <v>21</v>
       </c>
       <c r="I35" s="13" t="s">
         <v>1</v>
@@ -5094,7 +5091,7 @@
         <v>9</v>
       </c>
       <c r="H36" s="11">
-        <v>88</v>
+        <v>60</v>
       </c>
       <c r="I36" s="11" t="s">
         <v>1</v>
@@ -5123,7 +5120,7 @@
         <v>9</v>
       </c>
       <c r="H37" s="13">
-        <v>70</v>
+        <v>42</v>
       </c>
       <c r="I37" s="13" t="s">
         <v>1</v>
@@ -5152,7 +5149,7 @@
         <v>9</v>
       </c>
       <c r="H38" s="11">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="I38" s="11" t="s">
         <v>1</v>
@@ -5181,7 +5178,7 @@
         <v>9</v>
       </c>
       <c r="H39" s="13">
-        <v>27</v>
+        <v>51</v>
       </c>
       <c r="I39" s="13" t="s">
         <v>1</v>
@@ -5210,7 +5207,7 @@
         <v>9</v>
       </c>
       <c r="H40" s="11">
-        <v>52</v>
+        <v>87</v>
       </c>
       <c r="I40" s="11" t="s">
         <v>1</v>
@@ -5239,7 +5236,7 @@
         <v>9</v>
       </c>
       <c r="H41" s="13">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="I41" s="13" t="s">
         <v>1</v>
@@ -5268,7 +5265,7 @@
         <v>9</v>
       </c>
       <c r="H42" s="11">
-        <v>80</v>
+        <v>22</v>
       </c>
       <c r="I42" s="11" t="s">
         <v>1</v>
@@ -5297,7 +5294,7 @@
         <v>9</v>
       </c>
       <c r="H43" s="13">
-        <v>14</v>
+        <v>78</v>
       </c>
       <c r="I43" s="13" t="s">
         <v>1</v>
@@ -5326,7 +5323,7 @@
         <v>9</v>
       </c>
       <c r="H44" s="11">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="I44" s="11" t="s">
         <v>1</v>
@@ -5355,7 +5352,7 @@
         <v>9</v>
       </c>
       <c r="H45" s="13">
-        <v>54</v>
+        <v>17</v>
       </c>
       <c r="I45" s="13" t="s">
         <v>1</v>
@@ -5384,7 +5381,7 @@
         <v>9</v>
       </c>
       <c r="H46" s="11">
-        <v>64</v>
+        <v>88</v>
       </c>
       <c r="I46" s="11" t="s">
         <v>1</v>
@@ -5413,7 +5410,7 @@
         <v>9</v>
       </c>
       <c r="H47" s="13">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I47" s="13" t="s">
         <v>1</v>
@@ -5442,7 +5439,7 @@
         <v>9</v>
       </c>
       <c r="H48" s="11">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="I48" s="11" t="s">
         <v>1</v>
@@ -5471,7 +5468,7 @@
         <v>9</v>
       </c>
       <c r="H49" s="13">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="I49" s="13" t="s">
         <v>1</v>
@@ -5500,7 +5497,7 @@
         <v>9</v>
       </c>
       <c r="H50" s="11">
-        <v>10</v>
+        <v>77</v>
       </c>
       <c r="I50" s="11" t="s">
         <v>1</v>
@@ -5529,7 +5526,7 @@
         <v>9</v>
       </c>
       <c r="H51" s="13">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="I51" s="13" t="s">
         <v>1</v>
@@ -5558,7 +5555,7 @@
         <v>9</v>
       </c>
       <c r="H52" s="11">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="I52" s="11" t="s">
         <v>1</v>
@@ -5587,7 +5584,7 @@
         <v>9</v>
       </c>
       <c r="H53" s="13">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="I53" s="13" t="s">
         <v>1</v>
@@ -5616,7 +5613,7 @@
         <v>9</v>
       </c>
       <c r="H54" s="11">
-        <v>85</v>
+        <v>48</v>
       </c>
       <c r="I54" s="11" t="s">
         <v>1</v>
@@ -5645,7 +5642,7 @@
         <v>9</v>
       </c>
       <c r="H55" s="13">
-        <v>44</v>
+        <v>10</v>
       </c>
       <c r="I55" s="13" t="s">
         <v>1</v>
@@ -5674,7 +5671,7 @@
         <v>9</v>
       </c>
       <c r="H56" s="11">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="I56" s="11" t="s">
         <v>1</v>
@@ -5703,7 +5700,7 @@
         <v>9</v>
       </c>
       <c r="H57" s="13">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I57" s="13" t="s">
         <v>1</v>
@@ -5732,7 +5729,7 @@
         <v>9</v>
       </c>
       <c r="H58" s="11">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="I58" s="11" t="s">
         <v>1</v>
@@ -5761,7 +5758,7 @@
         <v>9</v>
       </c>
       <c r="H59" s="13">
-        <v>28</v>
+        <v>68</v>
       </c>
       <c r="I59" s="13" t="s">
         <v>1</v>
@@ -5790,7 +5787,7 @@
         <v>9</v>
       </c>
       <c r="H60" s="11">
-        <v>39</v>
+        <v>78</v>
       </c>
       <c r="I60" s="11" t="s">
         <v>1</v>
@@ -5819,7 +5816,7 @@
         <v>9</v>
       </c>
       <c r="H61" s="13">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="I61" s="13" t="s">
         <v>1</v>
@@ -5848,7 +5845,7 @@
         <v>9</v>
       </c>
       <c r="H62" s="11">
-        <v>83</v>
+        <v>58</v>
       </c>
       <c r="I62" s="11" t="s">
         <v>1</v>
@@ -5877,7 +5874,7 @@
         <v>9</v>
       </c>
       <c r="H63" s="13">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="I63" s="13" t="s">
         <v>1</v>
@@ -5906,7 +5903,7 @@
         <v>9</v>
       </c>
       <c r="H64" s="11">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="I64" s="11" t="s">
         <v>1</v>
@@ -5935,7 +5932,7 @@
         <v>9</v>
       </c>
       <c r="H65" s="13">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I65" s="13" t="s">
         <v>1</v>
@@ -5964,7 +5961,7 @@
         <v>9</v>
       </c>
       <c r="H66" s="11">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="I66" s="11" t="s">
         <v>1</v>
@@ -5993,7 +5990,7 @@
         <v>9</v>
       </c>
       <c r="H67" s="13">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="I67" s="13" t="s">
         <v>1</v>
@@ -6022,7 +6019,7 @@
         <v>9</v>
       </c>
       <c r="H68" s="11">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="I68" s="11" t="s">
         <v>1</v>
@@ -6051,7 +6048,7 @@
         <v>9</v>
       </c>
       <c r="H69" s="13">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="I69" s="13" t="s">
         <v>1</v>
@@ -6080,7 +6077,7 @@
         <v>9</v>
       </c>
       <c r="H70" s="11">
-        <v>56</v>
+        <v>30</v>
       </c>
       <c r="I70" s="11" t="s">
         <v>1</v>
@@ -6109,7 +6106,7 @@
         <v>9</v>
       </c>
       <c r="H71" s="13">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="I71" s="13" t="s">
         <v>1</v>
@@ -6138,7 +6135,7 @@
         <v>9</v>
       </c>
       <c r="H72" s="11">
-        <v>26</v>
+        <v>84</v>
       </c>
       <c r="I72" s="11" t="s">
         <v>1</v>
@@ -6167,7 +6164,7 @@
         <v>9</v>
       </c>
       <c r="H73" s="13">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="I73" s="13" t="s">
         <v>1</v>
@@ -6196,7 +6193,7 @@
         <v>9</v>
       </c>
       <c r="H74" s="11">
-        <v>12</v>
+        <v>88</v>
       </c>
       <c r="I74" s="11" t="s">
         <v>1</v>
@@ -6225,7 +6222,7 @@
         <v>9</v>
       </c>
       <c r="H75" s="13">
-        <v>19</v>
+        <v>72</v>
       </c>
       <c r="I75" s="13" t="s">
         <v>1</v>
@@ -6254,7 +6251,7 @@
         <v>9</v>
       </c>
       <c r="H76" s="11">
-        <v>83</v>
+        <v>29</v>
       </c>
       <c r="I76" s="11" t="s">
         <v>1</v>
@@ -6283,7 +6280,7 @@
         <v>9</v>
       </c>
       <c r="H77" s="13">
-        <v>73</v>
+        <v>87</v>
       </c>
       <c r="I77" s="13" t="s">
         <v>1</v>
@@ -6312,7 +6309,7 @@
         <v>9</v>
       </c>
       <c r="H78" s="11">
-        <v>53</v>
+        <v>14</v>
       </c>
       <c r="I78" s="11" t="s">
         <v>1</v>
@@ -6341,7 +6338,7 @@
         <v>9</v>
       </c>
       <c r="H79" s="13">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="I79" s="13" t="s">
         <v>1</v>
@@ -6370,7 +6367,7 @@
         <v>9</v>
       </c>
       <c r="H80" s="11">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="I80" s="11" t="s">
         <v>1</v>
@@ -6428,7 +6425,7 @@
         <v>9</v>
       </c>
       <c r="H82" s="11">
-        <v>10</v>
+        <v>77</v>
       </c>
       <c r="I82" s="11" t="s">
         <v>1</v>
@@ -6457,7 +6454,7 @@
         <v>9</v>
       </c>
       <c r="H83" s="13">
-        <v>62</v>
+        <v>14</v>
       </c>
       <c r="I83" s="13" t="s">
         <v>1</v>
@@ -6486,7 +6483,7 @@
         <v>9</v>
       </c>
       <c r="H84" s="11">
-        <v>51</v>
+        <v>89</v>
       </c>
       <c r="I84" s="11" t="s">
         <v>1</v>
@@ -6515,7 +6512,7 @@
         <v>9</v>
       </c>
       <c r="H85" s="13">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="I85" s="13" t="s">
         <v>1</v>
@@ -6544,7 +6541,7 @@
         <v>9</v>
       </c>
       <c r="H86" s="11">
-        <v>72</v>
+        <v>31</v>
       </c>
       <c r="I86" s="11" t="s">
         <v>1</v>
@@ -6573,7 +6570,7 @@
         <v>9</v>
       </c>
       <c r="H87" s="13">
-        <v>62</v>
+        <v>44</v>
       </c>
       <c r="I87" s="13" t="s">
         <v>1</v>
@@ -6602,7 +6599,7 @@
         <v>9</v>
       </c>
       <c r="H88" s="11">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="I88" s="11" t="s">
         <v>1</v>
@@ -6631,7 +6628,7 @@
         <v>9</v>
       </c>
       <c r="H89" s="13">
-        <v>64</v>
+        <v>53</v>
       </c>
       <c r="I89" s="13" t="s">
         <v>1</v>
@@ -6660,7 +6657,7 @@
         <v>9</v>
       </c>
       <c r="H90" s="11">
-        <v>12</v>
+        <v>46</v>
       </c>
       <c r="I90" s="11" t="s">
         <v>1</v>
@@ -6689,7 +6686,7 @@
         <v>9</v>
       </c>
       <c r="H91" s="13">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="I91" s="13" t="s">
         <v>1</v>
@@ -6718,7 +6715,7 @@
         <v>9</v>
       </c>
       <c r="H92" s="11">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="I92" s="11" t="s">
         <v>1</v>
@@ -6747,7 +6744,7 @@
         <v>9</v>
       </c>
       <c r="H93" s="13">
-        <v>63</v>
+        <v>83</v>
       </c>
       <c r="I93" s="13" t="s">
         <v>1</v>
@@ -6776,7 +6773,7 @@
         <v>9</v>
       </c>
       <c r="H94" s="11">
-        <v>62</v>
+        <v>10</v>
       </c>
       <c r="I94" s="11" t="s">
         <v>1</v>
@@ -6805,7 +6802,7 @@
         <v>9</v>
       </c>
       <c r="H95" s="13">
-        <v>85</v>
+        <v>13</v>
       </c>
       <c r="I95" s="13" t="s">
         <v>1</v>
@@ -6834,7 +6831,7 @@
         <v>9</v>
       </c>
       <c r="H96" s="11">
-        <v>63</v>
+        <v>12</v>
       </c>
       <c r="I96" s="11" t="s">
         <v>1</v>
@@ -6863,7 +6860,7 @@
         <v>9</v>
       </c>
       <c r="H97" s="13">
-        <v>63</v>
+        <v>16</v>
       </c>
       <c r="I97" s="13" t="s">
         <v>1</v>
@@ -6892,7 +6889,7 @@
         <v>9</v>
       </c>
       <c r="H98" s="11">
-        <v>17</v>
+        <v>67</v>
       </c>
       <c r="I98" s="11" t="s">
         <v>1</v>
@@ -6921,7 +6918,7 @@
         <v>9</v>
       </c>
       <c r="H99" s="13">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="I99" s="13" t="s">
         <v>1</v>
@@ -6950,7 +6947,7 @@
         <v>9</v>
       </c>
       <c r="H100" s="11">
-        <v>76</v>
+        <v>47</v>
       </c>
       <c r="I100" s="11" t="s">
         <v>1</v>
@@ -6979,7 +6976,7 @@
         <v>9</v>
       </c>
       <c r="H101" s="13">
-        <v>51</v>
+        <v>19</v>
       </c>
       <c r="I101" s="13" t="s">
         <v>1</v>
@@ -7008,7 +7005,7 @@
         <v>9</v>
       </c>
       <c r="H102" s="11">
-        <v>44</v>
+        <v>17</v>
       </c>
       <c r="I102" s="11" t="s">
         <v>1</v>
@@ -7037,7 +7034,7 @@
         <v>9</v>
       </c>
       <c r="H103" s="13">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="I103" s="13" t="s">
         <v>1</v>
@@ -7066,7 +7063,7 @@
         <v>9</v>
       </c>
       <c r="H104" s="11">
-        <v>48</v>
+        <v>20</v>
       </c>
       <c r="I104" s="11" t="s">
         <v>1</v>
@@ -7095,7 +7092,7 @@
         <v>9</v>
       </c>
       <c r="H105" s="13">
-        <v>59</v>
+        <v>29</v>
       </c>
       <c r="I105" s="13" t="s">
         <v>1</v>
@@ -7124,7 +7121,7 @@
         <v>9</v>
       </c>
       <c r="H106" s="11">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="I106" s="11" t="s">
         <v>1</v>
@@ -7153,7 +7150,7 @@
         <v>9</v>
       </c>
       <c r="H107" s="13">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="I107" s="13" t="s">
         <v>1</v>
@@ -7182,7 +7179,7 @@
         <v>9</v>
       </c>
       <c r="H108" s="11">
-        <v>53</v>
+        <v>64</v>
       </c>
       <c r="I108" s="11" t="s">
         <v>1</v>
@@ -7211,7 +7208,7 @@
         <v>9</v>
       </c>
       <c r="H109" s="13">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="I109" s="13" t="s">
         <v>1</v>
@@ -7240,7 +7237,7 @@
         <v>9</v>
       </c>
       <c r="H110" s="11">
-        <v>69</v>
+        <v>89</v>
       </c>
       <c r="I110" s="11" t="s">
         <v>1</v>
@@ -7269,7 +7266,7 @@
         <v>9</v>
       </c>
       <c r="H111" s="13">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="I111" s="13" t="s">
         <v>1</v>
@@ -7298,7 +7295,7 @@
         <v>9</v>
       </c>
       <c r="H112" s="11">
-        <v>39</v>
+        <v>10</v>
       </c>
       <c r="I112" s="11" t="s">
         <v>1</v>
@@ -7327,7 +7324,7 @@
         <v>9</v>
       </c>
       <c r="H113" s="13">
-        <v>84</v>
+        <v>16</v>
       </c>
       <c r="I113" s="13" t="s">
         <v>1</v>
@@ -7356,7 +7353,7 @@
         <v>9</v>
       </c>
       <c r="H114" s="11">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="I114" s="11" t="s">
         <v>1</v>
@@ -7385,7 +7382,7 @@
         <v>9</v>
       </c>
       <c r="H115" s="13">
-        <v>50</v>
+        <v>81</v>
       </c>
       <c r="I115" s="13" t="s">
         <v>1</v>
@@ -7414,7 +7411,7 @@
         <v>9</v>
       </c>
       <c r="H116" s="11">
-        <v>69</v>
+        <v>57</v>
       </c>
       <c r="I116" s="11" t="s">
         <v>1</v>
@@ -7443,7 +7440,7 @@
         <v>9</v>
       </c>
       <c r="H117" s="13">
-        <v>62</v>
+        <v>89</v>
       </c>
       <c r="I117" s="13" t="s">
         <v>1</v>
@@ -7472,7 +7469,7 @@
         <v>9</v>
       </c>
       <c r="H118" s="11">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="I118" s="11" t="s">
         <v>1</v>
@@ -7501,7 +7498,7 @@
         <v>9</v>
       </c>
       <c r="H119" s="13">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="I119" s="13" t="s">
         <v>1</v>
@@ -7530,7 +7527,7 @@
         <v>9</v>
       </c>
       <c r="H120" s="11">
-        <v>26</v>
+        <v>76</v>
       </c>
       <c r="I120" s="11" t="s">
         <v>1</v>
@@ -7559,7 +7556,7 @@
         <v>9</v>
       </c>
       <c r="H121" s="13">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="I121" s="13" t="s">
         <v>1</v>
@@ -7588,7 +7585,7 @@
         <v>9</v>
       </c>
       <c r="H122" s="11">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="I122" s="11" t="s">
         <v>1</v>
@@ -7617,7 +7614,7 @@
         <v>9</v>
       </c>
       <c r="H123" s="13">
-        <v>26</v>
+        <v>79</v>
       </c>
       <c r="I123" s="13" t="s">
         <v>1</v>
@@ -7646,7 +7643,7 @@
         <v>9</v>
       </c>
       <c r="H124" s="11">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="I124" s="11" t="s">
         <v>1</v>
@@ -7675,7 +7672,7 @@
         <v>9</v>
       </c>
       <c r="H125" s="13">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="I125" s="13" t="s">
         <v>1</v>
@@ -7704,7 +7701,7 @@
         <v>9</v>
       </c>
       <c r="H126" s="11">
-        <v>81</v>
+        <v>15</v>
       </c>
       <c r="I126" s="11" t="s">
         <v>1</v>
@@ -7733,7 +7730,7 @@
         <v>9</v>
       </c>
       <c r="H127" s="13">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="I127" s="13" t="s">
         <v>1</v>
@@ -7762,7 +7759,7 @@
         <v>9</v>
       </c>
       <c r="H128" s="11">
-        <v>33</v>
+        <v>78</v>
       </c>
       <c r="I128" s="11" t="s">
         <v>1</v>
@@ -7791,7 +7788,7 @@
         <v>9</v>
       </c>
       <c r="H129" s="13">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="I129" s="13" t="s">
         <v>1</v>
@@ -7820,7 +7817,7 @@
         <v>9</v>
       </c>
       <c r="H130" s="11">
-        <v>45</v>
+        <v>67</v>
       </c>
       <c r="I130" s="11" t="s">
         <v>1</v>
@@ -7849,7 +7846,7 @@
         <v>9</v>
       </c>
       <c r="H131" s="13">
-        <v>46</v>
+        <v>77</v>
       </c>
       <c r="I131" s="13" t="s">
         <v>1</v>
@@ -7878,7 +7875,7 @@
         <v>9</v>
       </c>
       <c r="H132" s="11">
-        <v>14</v>
+        <v>64</v>
       </c>
       <c r="I132" s="11" t="s">
         <v>1</v>
@@ -7907,7 +7904,7 @@
         <v>9</v>
       </c>
       <c r="H133" s="13">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I133" s="13" t="s">
         <v>1</v>
@@ -7936,7 +7933,7 @@
         <v>9</v>
       </c>
       <c r="H134" s="11">
-        <v>83</v>
+        <v>58</v>
       </c>
       <c r="I134" s="11" t="s">
         <v>1</v>
@@ -7965,7 +7962,7 @@
         <v>9</v>
       </c>
       <c r="H135" s="13">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="I135" s="13" t="s">
         <v>1</v>
@@ -7994,7 +7991,7 @@
         <v>9</v>
       </c>
       <c r="H136" s="11">
-        <v>74</v>
+        <v>51</v>
       </c>
       <c r="I136" s="11" t="s">
         <v>1</v>
@@ -8023,7 +8020,7 @@
         <v>9</v>
       </c>
       <c r="H137" s="13">
-        <v>36</v>
+        <v>78</v>
       </c>
       <c r="I137" s="13" t="s">
         <v>1</v>
@@ -8052,7 +8049,7 @@
         <v>9</v>
       </c>
       <c r="H138" s="11">
-        <v>79</v>
+        <v>32</v>
       </c>
       <c r="I138" s="11" t="s">
         <v>1</v>
@@ -8081,7 +8078,7 @@
         <v>9</v>
       </c>
       <c r="H139" s="13">
-        <v>56</v>
+        <v>23</v>
       </c>
       <c r="I139" s="13" t="s">
         <v>1</v>
@@ -8110,7 +8107,7 @@
         <v>9</v>
       </c>
       <c r="H140" s="11">
-        <v>81</v>
+        <v>59</v>
       </c>
       <c r="I140" s="11" t="s">
         <v>1</v>
@@ -8139,7 +8136,7 @@
         <v>9</v>
       </c>
       <c r="H141" s="13">
-        <v>17</v>
+        <v>48</v>
       </c>
       <c r="I141" s="13" t="s">
         <v>1</v>
@@ -8168,7 +8165,7 @@
         <v>9</v>
       </c>
       <c r="H142" s="11">
-        <v>10</v>
+        <v>58</v>
       </c>
       <c r="I142" s="11" t="s">
         <v>1</v>
@@ -8197,7 +8194,7 @@
         <v>9</v>
       </c>
       <c r="H143" s="13">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="I143" s="13" t="s">
         <v>1</v>
@@ -8226,7 +8223,7 @@
         <v>9</v>
       </c>
       <c r="H144" s="11">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="I144" s="11" t="s">
         <v>1</v>
@@ -8255,7 +8252,7 @@
         <v>9</v>
       </c>
       <c r="H145" s="13">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="I145" s="13" t="s">
         <v>1</v>
@@ -8284,7 +8281,7 @@
         <v>9</v>
       </c>
       <c r="H146" s="11">
-        <v>64</v>
+        <v>32</v>
       </c>
       <c r="I146" s="11" t="s">
         <v>1</v>
@@ -8313,7 +8310,7 @@
         <v>9</v>
       </c>
       <c r="H147" s="13">
-        <v>87</v>
+        <v>74</v>
       </c>
       <c r="I147" s="13" t="s">
         <v>1</v>
@@ -8342,7 +8339,7 @@
         <v>9</v>
       </c>
       <c r="H148" s="11">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="I148" s="11" t="s">
         <v>1</v>
@@ -8371,7 +8368,7 @@
         <v>9</v>
       </c>
       <c r="H149" s="13">
-        <v>65</v>
+        <v>81</v>
       </c>
       <c r="I149" s="13" t="s">
         <v>1</v>
@@ -8400,7 +8397,7 @@
         <v>9</v>
       </c>
       <c r="H150" s="11">
-        <v>38</v>
+        <v>78</v>
       </c>
       <c r="I150" s="11" t="s">
         <v>1</v>
@@ -8429,7 +8426,7 @@
         <v>9</v>
       </c>
       <c r="H151" s="13">
-        <v>48</v>
+        <v>29</v>
       </c>
       <c r="I151" s="13" t="s">
         <v>1</v>
@@ -8458,7 +8455,7 @@
         <v>9</v>
       </c>
       <c r="H152" s="11">
-        <v>24</v>
+        <v>59</v>
       </c>
       <c r="I152" s="11" t="s">
         <v>1</v>
@@ -8487,7 +8484,7 @@
         <v>9</v>
       </c>
       <c r="H153" s="13">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="I153" s="13" t="s">
         <v>1</v>
@@ -8516,7 +8513,7 @@
         <v>9</v>
       </c>
       <c r="H154" s="11">
-        <v>45</v>
+        <v>66</v>
       </c>
       <c r="I154" s="11" t="s">
         <v>1</v>
@@ -8545,7 +8542,7 @@
         <v>9</v>
       </c>
       <c r="H155" s="13">
-        <v>52</v>
+        <v>12</v>
       </c>
       <c r="I155" s="13" t="s">
         <v>1</v>
@@ -8574,7 +8571,7 @@
         <v>9</v>
       </c>
       <c r="H156" s="11">
-        <v>77</v>
+        <v>16</v>
       </c>
       <c r="I156" s="11" t="s">
         <v>1</v>
@@ -8603,7 +8600,7 @@
         <v>9</v>
       </c>
       <c r="H157" s="13">
-        <v>70</v>
+        <v>24</v>
       </c>
       <c r="I157" s="13" t="s">
         <v>1</v>
@@ -8632,7 +8629,7 @@
         <v>9</v>
       </c>
       <c r="H158" s="11">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="I158" s="11" t="s">
         <v>1</v>
@@ -8661,7 +8658,7 @@
         <v>9</v>
       </c>
       <c r="H159" s="13">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="I159" s="13" t="s">
         <v>1</v>
@@ -8690,7 +8687,7 @@
         <v>9</v>
       </c>
       <c r="H160" s="11">
-        <v>31</v>
+        <v>49</v>
       </c>
       <c r="I160" s="11" t="s">
         <v>1</v>
@@ -8719,7 +8716,7 @@
         <v>9</v>
       </c>
       <c r="H161" s="13">
-        <v>74</v>
+        <v>57</v>
       </c>
       <c r="I161" s="13" t="s">
         <v>1</v>
@@ -8748,7 +8745,7 @@
         <v>9</v>
       </c>
       <c r="H162" s="11">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="I162" s="11" t="s">
         <v>1</v>
@@ -8777,7 +8774,7 @@
         <v>9</v>
       </c>
       <c r="H163" s="13">
-        <v>24</v>
+        <v>68</v>
       </c>
       <c r="I163" s="13" t="s">
         <v>1</v>
@@ -8806,7 +8803,7 @@
         <v>9</v>
       </c>
       <c r="H164" s="11">
-        <v>78</v>
+        <v>36</v>
       </c>
       <c r="I164" s="11" t="s">
         <v>1</v>
@@ -8835,7 +8832,7 @@
         <v>9</v>
       </c>
       <c r="H165" s="13">
-        <v>29</v>
+        <v>70</v>
       </c>
       <c r="I165" s="13" t="s">
         <v>1</v>
@@ -8864,7 +8861,7 @@
         <v>9</v>
       </c>
       <c r="H166" s="11">
-        <v>58</v>
+        <v>89</v>
       </c>
       <c r="I166" s="11" t="s">
         <v>1</v>
@@ -8893,7 +8890,7 @@
         <v>9</v>
       </c>
       <c r="H167" s="13">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="I167" s="13" t="s">
         <v>1</v>
@@ -8922,7 +8919,7 @@
         <v>9</v>
       </c>
       <c r="H168" s="11">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="I168" s="11" t="s">
         <v>1</v>
@@ -8951,7 +8948,7 @@
         <v>9</v>
       </c>
       <c r="H169" s="13">
-        <v>79</v>
+        <v>36</v>
       </c>
       <c r="I169" s="13" t="s">
         <v>1</v>
@@ -8980,7 +8977,7 @@
         <v>9</v>
       </c>
       <c r="H170" s="11">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="I170" s="11" t="s">
         <v>1</v>
@@ -9009,7 +9006,7 @@
         <v>9</v>
       </c>
       <c r="H171" s="13">
-        <v>55</v>
+        <v>76</v>
       </c>
       <c r="I171" s="13" t="s">
         <v>1</v>
@@ -9067,7 +9064,7 @@
         <v>9</v>
       </c>
       <c r="H173" s="13">
-        <v>77</v>
+        <v>38</v>
       </c>
       <c r="I173" s="13" t="s">
         <v>1</v>
@@ -9096,7 +9093,7 @@
         <v>9</v>
       </c>
       <c r="H174" s="11">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="I174" s="11" t="s">
         <v>1</v>
@@ -9125,7 +9122,7 @@
         <v>9</v>
       </c>
       <c r="H175" s="13">
-        <v>82</v>
+        <v>29</v>
       </c>
       <c r="I175" s="13" t="s">
         <v>1</v>
@@ -9154,7 +9151,7 @@
         <v>9</v>
       </c>
       <c r="H176" s="11">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="I176" s="11" t="s">
         <v>1</v>
@@ -9183,7 +9180,7 @@
         <v>9</v>
       </c>
       <c r="H177" s="13">
-        <v>72</v>
+        <v>18</v>
       </c>
       <c r="I177" s="13" t="s">
         <v>1</v>
@@ -9212,7 +9209,7 @@
         <v>9</v>
       </c>
       <c r="H178" s="11">
-        <v>25</v>
+        <v>48</v>
       </c>
       <c r="I178" s="11" t="s">
         <v>1</v>
@@ -9241,7 +9238,7 @@
         <v>9</v>
       </c>
       <c r="H179" s="13">
-        <v>22</v>
+        <v>76</v>
       </c>
       <c r="I179" s="13" t="s">
         <v>1</v>
@@ -9270,7 +9267,7 @@
         <v>9</v>
       </c>
       <c r="H180" s="11">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="I180" s="11" t="s">
         <v>1</v>
@@ -9299,7 +9296,7 @@
         <v>9</v>
       </c>
       <c r="H181" s="13">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="I181" s="13" t="s">
         <v>1</v>
@@ -9328,7 +9325,7 @@
         <v>9</v>
       </c>
       <c r="H182" s="11">
-        <v>38</v>
+        <v>63</v>
       </c>
       <c r="I182" s="11" t="s">
         <v>1</v>
@@ -9357,7 +9354,7 @@
         <v>9</v>
       </c>
       <c r="H183" s="13">
-        <v>84</v>
+        <v>30</v>
       </c>
       <c r="I183" s="13" t="s">
         <v>1</v>
@@ -9386,7 +9383,7 @@
         <v>9</v>
       </c>
       <c r="H184" s="11">
-        <v>45</v>
+        <v>18</v>
       </c>
       <c r="I184" s="11" t="s">
         <v>1</v>
@@ -9415,7 +9412,7 @@
         <v>9</v>
       </c>
       <c r="H185" s="13">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="I185" s="13" t="s">
         <v>1</v>
@@ -9444,7 +9441,7 @@
         <v>9</v>
       </c>
       <c r="H186" s="11">
-        <v>67</v>
+        <v>37</v>
       </c>
       <c r="I186" s="11" t="s">
         <v>1</v>
@@ -9473,7 +9470,7 @@
         <v>9</v>
       </c>
       <c r="H187" s="13">
-        <v>53</v>
+        <v>35</v>
       </c>
       <c r="I187" s="13" t="s">
         <v>1</v>
@@ -9502,7 +9499,7 @@
         <v>9</v>
       </c>
       <c r="H188" s="11">
-        <v>73</v>
+        <v>33</v>
       </c>
       <c r="I188" s="11" t="s">
         <v>1</v>
@@ -9531,7 +9528,7 @@
         <v>9</v>
       </c>
       <c r="H189" s="13">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="I189" s="13" t="s">
         <v>1</v>
@@ -9560,7 +9557,7 @@
         <v>9</v>
       </c>
       <c r="H190" s="11">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="I190" s="11" t="s">
         <v>1</v>
@@ -9589,7 +9586,7 @@
         <v>9</v>
       </c>
       <c r="H191" s="13">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="I191" s="13" t="s">
         <v>1</v>
@@ -9618,7 +9615,7 @@
         <v>9</v>
       </c>
       <c r="H192" s="11">
-        <v>56</v>
+        <v>83</v>
       </c>
       <c r="I192" s="11" t="s">
         <v>1</v>
@@ -9647,7 +9644,7 @@
         <v>9</v>
       </c>
       <c r="H193" s="13">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="I193" s="13" t="s">
         <v>1</v>
@@ -9676,7 +9673,7 @@
         <v>9</v>
       </c>
       <c r="H194" s="11">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="I194" s="11" t="s">
         <v>1</v>
@@ -9705,7 +9702,7 @@
         <v>9</v>
       </c>
       <c r="H195" s="13">
-        <v>39</v>
+        <v>87</v>
       </c>
       <c r="I195" s="13" t="s">
         <v>1</v>
@@ -9734,7 +9731,7 @@
         <v>9</v>
       </c>
       <c r="H196" s="11">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="I196" s="11" t="s">
         <v>1</v>
@@ -9763,7 +9760,7 @@
         <v>9</v>
       </c>
       <c r="H197" s="13">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="I197" s="13" t="s">
         <v>1</v>
@@ -9792,7 +9789,7 @@
         <v>9</v>
       </c>
       <c r="H198" s="11">
-        <v>78</v>
+        <v>26</v>
       </c>
       <c r="I198" s="11" t="s">
         <v>1</v>
@@ -9821,7 +9818,7 @@
         <v>9</v>
       </c>
       <c r="H199" s="13">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I199" s="13" t="s">
         <v>1</v>
@@ -9850,7 +9847,7 @@
         <v>9</v>
       </c>
       <c r="H200" s="11">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="I200" s="11" t="s">
         <v>1</v>
@@ -9879,7 +9876,7 @@
         <v>9</v>
       </c>
       <c r="H201" s="13">
-        <v>74</v>
+        <v>19</v>
       </c>
       <c r="I201" s="13" t="s">
         <v>1</v>
@@ -9908,7 +9905,7 @@
         <v>9</v>
       </c>
       <c r="H202" s="11">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I202" s="11" t="s">
         <v>1</v>
@@ -9937,7 +9934,7 @@
         <v>9</v>
       </c>
       <c r="H203" s="13">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="I203" s="13" t="s">
         <v>1</v>
@@ -9966,7 +9963,7 @@
         <v>9</v>
       </c>
       <c r="H204" s="11">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="I204" s="11" t="s">
         <v>1</v>
@@ -9995,7 +9992,7 @@
         <v>9</v>
       </c>
       <c r="H205" s="13">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="I205" s="13" t="s">
         <v>1</v>
@@ -10024,7 +10021,7 @@
         <v>9</v>
       </c>
       <c r="H206" s="11">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="I206" s="11" t="s">
         <v>1</v>
@@ -10053,7 +10050,7 @@
         <v>9</v>
       </c>
       <c r="H207" s="13">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I207" s="13" t="s">
         <v>1</v>
@@ -10082,7 +10079,7 @@
         <v>9</v>
       </c>
       <c r="H208" s="11">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="I208" s="11" t="s">
         <v>1</v>
@@ -10111,7 +10108,7 @@
         <v>9</v>
       </c>
       <c r="H209" s="13">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="I209" s="13" t="s">
         <v>1</v>
@@ -10140,7 +10137,7 @@
         <v>9</v>
       </c>
       <c r="H210" s="11">
-        <v>31</v>
+        <v>65</v>
       </c>
       <c r="I210" s="11" t="s">
         <v>1</v>
@@ -10169,7 +10166,7 @@
         <v>9</v>
       </c>
       <c r="H211" s="13">
-        <v>31</v>
+        <v>65</v>
       </c>
       <c r="I211" s="13" t="s">
         <v>1</v>
@@ -10198,7 +10195,7 @@
         <v>9</v>
       </c>
       <c r="H212" s="11">
-        <v>11</v>
+        <v>53</v>
       </c>
       <c r="I212" s="11" t="s">
         <v>1</v>
@@ -10227,7 +10224,7 @@
         <v>9</v>
       </c>
       <c r="H213" s="13">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="I213" s="13" t="s">
         <v>1</v>
@@ -10256,7 +10253,7 @@
         <v>9</v>
       </c>
       <c r="H214" s="11">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="I214" s="11" t="s">
         <v>1</v>
@@ -10285,7 +10282,7 @@
         <v>9</v>
       </c>
       <c r="H215" s="13">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="I215" s="13" t="s">
         <v>1</v>
@@ -10314,7 +10311,7 @@
         <v>9</v>
       </c>
       <c r="H216" s="11">
-        <v>66</v>
+        <v>44</v>
       </c>
       <c r="I216" s="11" t="s">
         <v>1</v>
@@ -10343,7 +10340,7 @@
         <v>9</v>
       </c>
       <c r="H217" s="13">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="I217" s="13" t="s">
         <v>1</v>
@@ -10372,7 +10369,7 @@
         <v>9</v>
       </c>
       <c r="H218" s="11">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="I218" s="11" t="s">
         <v>1</v>
@@ -10401,7 +10398,7 @@
         <v>9</v>
       </c>
       <c r="H219" s="13">
-        <v>31</v>
+        <v>81</v>
       </c>
       <c r="I219" s="13" t="s">
         <v>1</v>
@@ -10430,7 +10427,7 @@
         <v>9</v>
       </c>
       <c r="H220" s="11">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="I220" s="11" t="s">
         <v>1</v>
@@ -10459,7 +10456,7 @@
         <v>9</v>
       </c>
       <c r="H221" s="13">
-        <v>43</v>
+        <v>63</v>
       </c>
       <c r="I221" s="13" t="s">
         <v>1</v>
@@ -10488,7 +10485,7 @@
         <v>9</v>
       </c>
       <c r="H222" s="11">
-        <v>25</v>
+        <v>43</v>
       </c>
       <c r="I222" s="11" t="s">
         <v>1</v>
@@ -10505,7 +10502,7 @@
         <v>721</v>
       </c>
       <c r="D223" s="13" t="s">
-        <v>722</v>
+        <v>602</v>
       </c>
       <c r="E223" s="13" t="s">
         <v>598</v>
@@ -10517,7 +10514,7 @@
         <v>9</v>
       </c>
       <c r="H223" s="13">
-        <v>28</v>
+        <v>85</v>
       </c>
       <c r="I223" s="13" t="s">
         <v>1</v>
@@ -10525,16 +10522,16 @@
     </row>
     <row r="224" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A224" s="11" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="B224" s="11" t="s">
         <v>22</v>
       </c>
       <c r="C224" s="11" t="s">
+        <v>723</v>
+      </c>
+      <c r="D224" s="11" t="s">
         <v>724</v>
-      </c>
-      <c r="D224" s="11" t="s">
-        <v>725</v>
       </c>
       <c r="E224" s="11" t="s">
         <v>598</v>
@@ -10546,7 +10543,7 @@
         <v>9</v>
       </c>
       <c r="H224" s="11">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="I224" s="11" t="s">
         <v>1</v>
@@ -10554,16 +10551,16 @@
     </row>
     <row r="225" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A225" s="13" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="B225" s="13" t="s">
         <v>22</v>
       </c>
       <c r="C225" s="13" t="s">
+        <v>726</v>
+      </c>
+      <c r="D225" s="13" t="s">
         <v>727</v>
-      </c>
-      <c r="D225" s="13" t="s">
-        <v>728</v>
       </c>
       <c r="E225" s="13" t="s">
         <v>598</v>
@@ -10575,7 +10572,7 @@
         <v>9</v>
       </c>
       <c r="H225" s="13">
-        <v>81</v>
+        <v>30</v>
       </c>
       <c r="I225" s="13" t="s">
         <v>1</v>
@@ -10583,16 +10580,16 @@
     </row>
     <row r="226" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A226" s="11" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="B226" s="11" t="s">
         <v>22</v>
       </c>
       <c r="C226" s="11" t="s">
+        <v>729</v>
+      </c>
+      <c r="D226" s="11" t="s">
         <v>730</v>
-      </c>
-      <c r="D226" s="11" t="s">
-        <v>731</v>
       </c>
       <c r="E226" s="11" t="s">
         <v>598</v>
@@ -10604,7 +10601,7 @@
         <v>9</v>
       </c>
       <c r="H226" s="11">
-        <v>56</v>
+        <v>36</v>
       </c>
       <c r="I226" s="11" t="s">
         <v>1</v>
@@ -10612,16 +10609,16 @@
     </row>
     <row r="227" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A227" s="13" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="B227" s="13" t="s">
         <v>22</v>
       </c>
       <c r="C227" s="13" t="s">
+        <v>732</v>
+      </c>
+      <c r="D227" s="13" t="s">
         <v>733</v>
-      </c>
-      <c r="D227" s="13" t="s">
-        <v>734</v>
       </c>
       <c r="E227" s="13" t="s">
         <v>598</v>
@@ -10633,7 +10630,7 @@
         <v>9</v>
       </c>
       <c r="H227" s="13">
-        <v>56</v>
+        <v>74</v>
       </c>
       <c r="I227" s="13" t="s">
         <v>1</v>
@@ -10641,16 +10638,16 @@
     </row>
     <row r="228" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A228" s="11" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="B228" s="11" t="s">
         <v>22</v>
       </c>
       <c r="C228" s="11" t="s">
+        <v>735</v>
+      </c>
+      <c r="D228" s="11" t="s">
         <v>736</v>
-      </c>
-      <c r="D228" s="11" t="s">
-        <v>737</v>
       </c>
       <c r="E228" s="11" t="s">
         <v>598</v>
@@ -10662,7 +10659,7 @@
         <v>9</v>
       </c>
       <c r="H228" s="11">
-        <v>70</v>
+        <v>28</v>
       </c>
       <c r="I228" s="11" t="s">
         <v>1</v>
@@ -10670,16 +10667,16 @@
     </row>
     <row r="229" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A229" s="13" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="B229" s="13" t="s">
         <v>22</v>
       </c>
       <c r="C229" s="13" t="s">
+        <v>738</v>
+      </c>
+      <c r="D229" s="13" t="s">
         <v>739</v>
-      </c>
-      <c r="D229" s="13" t="s">
-        <v>740</v>
       </c>
       <c r="E229" s="13" t="s">
         <v>598</v>
@@ -10691,7 +10688,7 @@
         <v>9</v>
       </c>
       <c r="H229" s="13">
-        <v>78</v>
+        <v>40</v>
       </c>
       <c r="I229" s="13" t="s">
         <v>1</v>
@@ -10699,16 +10696,16 @@
     </row>
     <row r="230" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A230" s="11" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="B230" s="11" t="s">
         <v>22</v>
       </c>
       <c r="C230" s="11" t="s">
+        <v>741</v>
+      </c>
+      <c r="D230" s="11" t="s">
         <v>742</v>
-      </c>
-      <c r="D230" s="11" t="s">
-        <v>743</v>
       </c>
       <c r="E230" s="11" t="s">
         <v>598</v>
@@ -10720,7 +10717,7 @@
         <v>9</v>
       </c>
       <c r="H230" s="11">
-        <v>10</v>
+        <v>87</v>
       </c>
       <c r="I230" s="11" t="s">
         <v>1</v>
@@ -10728,16 +10725,16 @@
     </row>
     <row r="231" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A231" s="13" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="B231" s="13" t="s">
         <v>22</v>
       </c>
       <c r="C231" s="13" t="s">
+        <v>744</v>
+      </c>
+      <c r="D231" s="13" t="s">
         <v>745</v>
-      </c>
-      <c r="D231" s="13" t="s">
-        <v>746</v>
       </c>
       <c r="E231" s="13" t="s">
         <v>598</v>
@@ -10749,7 +10746,7 @@
         <v>9</v>
       </c>
       <c r="H231" s="13">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="I231" s="13" t="s">
         <v>1</v>
@@ -10757,28 +10754,28 @@
     </row>
     <row r="232" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A232" s="11" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="B232" s="11" t="s">
         <v>23</v>
       </c>
       <c r="C232" s="11" t="s">
+        <v>747</v>
+      </c>
+      <c r="D232" s="11" t="s">
         <v>748</v>
       </c>
-      <c r="D232" s="11" t="s">
+      <c r="E232" s="11" t="s">
         <v>749</v>
       </c>
-      <c r="E232" s="11" t="s">
+      <c r="F232" s="11" t="s">
         <v>750</v>
       </c>
-      <c r="F232" s="11" t="s">
-        <v>751</v>
-      </c>
       <c r="G232" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H232" s="11">
-        <v>72</v>
+        <v>51</v>
       </c>
       <c r="I232" s="11" t="s">
         <v>1</v>
@@ -10786,28 +10783,28 @@
     </row>
     <row r="233" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A233" s="13" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="B233" s="13" t="s">
         <v>23</v>
       </c>
       <c r="C233" s="13" t="s">
+        <v>752</v>
+      </c>
+      <c r="D233" s="13" t="s">
         <v>753</v>
       </c>
-      <c r="D233" s="13" t="s">
-        <v>754</v>
-      </c>
       <c r="E233" s="13" t="s">
+        <v>749</v>
+      </c>
+      <c r="F233" s="13" t="s">
         <v>750</v>
       </c>
-      <c r="F233" s="13" t="s">
-        <v>751</v>
-      </c>
       <c r="G233" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H233" s="13">
-        <v>37</v>
+        <v>62</v>
       </c>
       <c r="I233" s="13" t="s">
         <v>1</v>
@@ -10815,28 +10812,28 @@
     </row>
     <row r="234" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A234" s="11" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="B234" s="11" t="s">
         <v>23</v>
       </c>
       <c r="C234" s="11" t="s">
+        <v>755</v>
+      </c>
+      <c r="D234" s="11" t="s">
         <v>756</v>
       </c>
-      <c r="D234" s="11" t="s">
-        <v>757</v>
-      </c>
       <c r="E234" s="11" t="s">
+        <v>749</v>
+      </c>
+      <c r="F234" s="11" t="s">
         <v>750</v>
       </c>
-      <c r="F234" s="11" t="s">
-        <v>751</v>
-      </c>
       <c r="G234" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H234" s="11">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="I234" s="11" t="s">
         <v>1</v>
@@ -10844,28 +10841,28 @@
     </row>
     <row r="235" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A235" s="13" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="B235" s="13" t="s">
         <v>23</v>
       </c>
       <c r="C235" s="13" t="s">
+        <v>758</v>
+      </c>
+      <c r="D235" s="13" t="s">
         <v>759</v>
       </c>
-      <c r="D235" s="13" t="s">
-        <v>760</v>
-      </c>
       <c r="E235" s="13" t="s">
+        <v>749</v>
+      </c>
+      <c r="F235" s="13" t="s">
         <v>750</v>
       </c>
-      <c r="F235" s="13" t="s">
-        <v>751</v>
-      </c>
       <c r="G235" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H235" s="13">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="I235" s="13" t="s">
         <v>1</v>
@@ -10873,28 +10870,28 @@
     </row>
     <row r="236" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A236" s="11" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="B236" s="11" t="s">
         <v>23</v>
       </c>
       <c r="C236" s="11" t="s">
+        <v>761</v>
+      </c>
+      <c r="D236" s="11" t="s">
         <v>762</v>
       </c>
-      <c r="D236" s="11" t="s">
-        <v>763</v>
-      </c>
       <c r="E236" s="11" t="s">
+        <v>749</v>
+      </c>
+      <c r="F236" s="11" t="s">
         <v>750</v>
       </c>
-      <c r="F236" s="11" t="s">
-        <v>751</v>
-      </c>
       <c r="G236" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H236" s="11">
-        <v>11</v>
+        <v>68</v>
       </c>
       <c r="I236" s="11" t="s">
         <v>1</v>
@@ -10902,28 +10899,28 @@
     </row>
     <row r="237" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A237" s="13" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="B237" s="13" t="s">
         <v>23</v>
       </c>
       <c r="C237" s="13" t="s">
+        <v>764</v>
+      </c>
+      <c r="D237" s="13" t="s">
         <v>765</v>
       </c>
-      <c r="D237" s="13" t="s">
-        <v>766</v>
-      </c>
       <c r="E237" s="13" t="s">
+        <v>749</v>
+      </c>
+      <c r="F237" s="13" t="s">
         <v>750</v>
       </c>
-      <c r="F237" s="13" t="s">
-        <v>751</v>
-      </c>
       <c r="G237" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H237" s="13">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="I237" s="13" t="s">
         <v>1</v>
@@ -10931,28 +10928,28 @@
     </row>
     <row r="238" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A238" s="11" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="B238" s="11" t="s">
         <v>23</v>
       </c>
       <c r="C238" s="11" t="s">
+        <v>767</v>
+      </c>
+      <c r="D238" s="11" t="s">
         <v>768</v>
       </c>
-      <c r="D238" s="11" t="s">
-        <v>769</v>
-      </c>
       <c r="E238" s="11" t="s">
+        <v>749</v>
+      </c>
+      <c r="F238" s="11" t="s">
         <v>750</v>
       </c>
-      <c r="F238" s="11" t="s">
-        <v>751</v>
-      </c>
       <c r="G238" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H238" s="11">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="I238" s="11" t="s">
         <v>1</v>
@@ -10960,28 +10957,28 @@
     </row>
     <row r="239" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A239" s="13" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="B239" s="13" t="s">
         <v>23</v>
       </c>
       <c r="C239" s="13" t="s">
+        <v>770</v>
+      </c>
+      <c r="D239" s="13" t="s">
         <v>771</v>
       </c>
-      <c r="D239" s="13" t="s">
-        <v>772</v>
-      </c>
       <c r="E239" s="13" t="s">
+        <v>749</v>
+      </c>
+      <c r="F239" s="13" t="s">
         <v>750</v>
       </c>
-      <c r="F239" s="13" t="s">
-        <v>751</v>
-      </c>
       <c r="G239" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H239" s="13">
-        <v>78</v>
+        <v>51</v>
       </c>
       <c r="I239" s="13" t="s">
         <v>1</v>
@@ -10989,28 +10986,28 @@
     </row>
     <row r="240" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A240" s="11" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="B240" s="11" t="s">
         <v>23</v>
       </c>
       <c r="C240" s="11" t="s">
+        <v>773</v>
+      </c>
+      <c r="D240" s="11" t="s">
         <v>774</v>
       </c>
-      <c r="D240" s="11" t="s">
-        <v>775</v>
-      </c>
       <c r="E240" s="11" t="s">
+        <v>749</v>
+      </c>
+      <c r="F240" s="11" t="s">
         <v>750</v>
       </c>
-      <c r="F240" s="11" t="s">
-        <v>751</v>
-      </c>
       <c r="G240" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H240" s="11">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="I240" s="11" t="s">
         <v>1</v>
@@ -11018,28 +11015,28 @@
     </row>
     <row r="241" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A241" s="13" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="B241" s="13" t="s">
         <v>23</v>
       </c>
       <c r="C241" s="13" t="s">
+        <v>776</v>
+      </c>
+      <c r="D241" s="13" t="s">
         <v>777</v>
       </c>
-      <c r="D241" s="13" t="s">
-        <v>778</v>
-      </c>
       <c r="E241" s="13" t="s">
+        <v>749</v>
+      </c>
+      <c r="F241" s="13" t="s">
         <v>750</v>
       </c>
-      <c r="F241" s="13" t="s">
-        <v>751</v>
-      </c>
       <c r="G241" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H241" s="13">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="I241" s="13" t="s">
         <v>1</v>
@@ -11047,28 +11044,28 @@
     </row>
     <row r="242" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A242" s="11" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="B242" s="11" t="s">
         <v>23</v>
       </c>
       <c r="C242" s="11" t="s">
+        <v>779</v>
+      </c>
+      <c r="D242" s="11" t="s">
         <v>780</v>
       </c>
-      <c r="D242" s="11" t="s">
-        <v>781</v>
-      </c>
       <c r="E242" s="11" t="s">
+        <v>749</v>
+      </c>
+      <c r="F242" s="11" t="s">
         <v>750</v>
       </c>
-      <c r="F242" s="11" t="s">
-        <v>751</v>
-      </c>
       <c r="G242" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H242" s="11">
-        <v>54</v>
+        <v>84</v>
       </c>
       <c r="I242" s="11" t="s">
         <v>1</v>
@@ -11076,28 +11073,28 @@
     </row>
     <row r="243" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A243" s="13" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="B243" s="13" t="s">
         <v>23</v>
       </c>
       <c r="C243" s="13" t="s">
+        <v>782</v>
+      </c>
+      <c r="D243" s="13" t="s">
         <v>783</v>
       </c>
-      <c r="D243" s="13" t="s">
-        <v>784</v>
-      </c>
       <c r="E243" s="13" t="s">
+        <v>749</v>
+      </c>
+      <c r="F243" s="13" t="s">
         <v>750</v>
       </c>
-      <c r="F243" s="13" t="s">
-        <v>751</v>
-      </c>
       <c r="G243" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H243" s="13">
-        <v>83</v>
+        <v>22</v>
       </c>
       <c r="I243" s="13" t="s">
         <v>1</v>
@@ -11105,28 +11102,28 @@
     </row>
     <row r="244" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A244" s="11" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="B244" s="11" t="s">
         <v>23</v>
       </c>
       <c r="C244" s="11" t="s">
+        <v>785</v>
+      </c>
+      <c r="D244" s="11" t="s">
         <v>786</v>
       </c>
-      <c r="D244" s="11" t="s">
-        <v>787</v>
-      </c>
       <c r="E244" s="11" t="s">
+        <v>749</v>
+      </c>
+      <c r="F244" s="11" t="s">
         <v>750</v>
       </c>
-      <c r="F244" s="11" t="s">
-        <v>751</v>
-      </c>
       <c r="G244" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H244" s="11">
-        <v>72</v>
+        <v>56</v>
       </c>
       <c r="I244" s="11" t="s">
         <v>1</v>
@@ -11134,28 +11131,28 @@
     </row>
     <row r="245" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A245" s="13" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="B245" s="13" t="s">
         <v>23</v>
       </c>
       <c r="C245" s="13" t="s">
+        <v>788</v>
+      </c>
+      <c r="D245" s="13" t="s">
         <v>789</v>
       </c>
-      <c r="D245" s="13" t="s">
-        <v>790</v>
-      </c>
       <c r="E245" s="13" t="s">
+        <v>749</v>
+      </c>
+      <c r="F245" s="13" t="s">
         <v>750</v>
       </c>
-      <c r="F245" s="13" t="s">
-        <v>751</v>
-      </c>
       <c r="G245" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H245" s="13">
-        <v>89</v>
+        <v>72</v>
       </c>
       <c r="I245" s="13" t="s">
         <v>1</v>
@@ -11163,28 +11160,28 @@
     </row>
     <row r="246" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A246" s="11" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="B246" s="11" t="s">
         <v>23</v>
       </c>
       <c r="C246" s="11" t="s">
+        <v>791</v>
+      </c>
+      <c r="D246" s="11" t="s">
         <v>792</v>
       </c>
-      <c r="D246" s="11" t="s">
-        <v>793</v>
-      </c>
       <c r="E246" s="11" t="s">
+        <v>749</v>
+      </c>
+      <c r="F246" s="11" t="s">
         <v>750</v>
       </c>
-      <c r="F246" s="11" t="s">
-        <v>751</v>
-      </c>
       <c r="G246" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H246" s="11">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="I246" s="11" t="s">
         <v>1</v>
@@ -11192,28 +11189,28 @@
     </row>
     <row r="247" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A247" s="13" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="B247" s="13" t="s">
         <v>24</v>
       </c>
       <c r="C247" s="13" t="s">
+        <v>794</v>
+      </c>
+      <c r="D247" s="13" t="s">
         <v>795</v>
       </c>
-      <c r="D247" s="13" t="s">
+      <c r="E247" s="13" t="s">
         <v>796</v>
       </c>
-      <c r="E247" s="13" t="s">
+      <c r="F247" s="13" t="s">
         <v>797</v>
       </c>
-      <c r="F247" s="13" t="s">
-        <v>798</v>
-      </c>
       <c r="G247" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H247" s="13">
-        <v>45</v>
+        <v>72</v>
       </c>
       <c r="I247" s="13" t="s">
         <v>1</v>
@@ -11221,28 +11218,28 @@
     </row>
     <row r="248" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A248" s="11" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="B248" s="11" t="s">
         <v>24</v>
       </c>
       <c r="C248" s="11" t="s">
+        <v>799</v>
+      </c>
+      <c r="D248" s="11" t="s">
         <v>800</v>
       </c>
-      <c r="D248" s="11" t="s">
-        <v>801</v>
-      </c>
       <c r="E248" s="11" t="s">
+        <v>796</v>
+      </c>
+      <c r="F248" s="11" t="s">
         <v>797</v>
       </c>
-      <c r="F248" s="11" t="s">
-        <v>798</v>
-      </c>
       <c r="G248" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H248" s="11">
-        <v>69</v>
+        <v>83</v>
       </c>
       <c r="I248" s="11" t="s">
         <v>1</v>
@@ -11250,28 +11247,28 @@
     </row>
     <row r="249" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A249" s="13" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="B249" s="13" t="s">
         <v>24</v>
       </c>
       <c r="C249" s="13" t="s">
+        <v>802</v>
+      </c>
+      <c r="D249" s="13" t="s">
         <v>803</v>
       </c>
-      <c r="D249" s="13" t="s">
-        <v>804</v>
-      </c>
       <c r="E249" s="13" t="s">
+        <v>796</v>
+      </c>
+      <c r="F249" s="13" t="s">
         <v>797</v>
       </c>
-      <c r="F249" s="13" t="s">
-        <v>798</v>
-      </c>
       <c r="G249" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H249" s="13">
-        <v>36</v>
+        <v>83</v>
       </c>
       <c r="I249" s="13" t="s">
         <v>1</v>
@@ -11279,28 +11276,28 @@
     </row>
     <row r="250" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A250" s="11" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="B250" s="11" t="s">
         <v>24</v>
       </c>
       <c r="C250" s="11" t="s">
+        <v>805</v>
+      </c>
+      <c r="D250" s="11" t="s">
         <v>806</v>
       </c>
-      <c r="D250" s="11" t="s">
-        <v>807</v>
-      </c>
       <c r="E250" s="11" t="s">
+        <v>796</v>
+      </c>
+      <c r="F250" s="11" t="s">
         <v>797</v>
       </c>
-      <c r="F250" s="11" t="s">
-        <v>798</v>
-      </c>
       <c r="G250" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H250" s="11">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="I250" s="11" t="s">
         <v>1</v>
@@ -11308,28 +11305,28 @@
     </row>
     <row r="251" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A251" s="13" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="B251" s="13" t="s">
         <v>24</v>
       </c>
       <c r="C251" s="13" t="s">
+        <v>808</v>
+      </c>
+      <c r="D251" s="13" t="s">
         <v>809</v>
       </c>
-      <c r="D251" s="13" t="s">
-        <v>810</v>
-      </c>
       <c r="E251" s="13" t="s">
+        <v>796</v>
+      </c>
+      <c r="F251" s="13" t="s">
         <v>797</v>
       </c>
-      <c r="F251" s="13" t="s">
-        <v>798</v>
-      </c>
       <c r="G251" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H251" s="13">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="I251" s="13" t="s">
         <v>1</v>
@@ -11337,28 +11334,28 @@
     </row>
     <row r="252" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A252" s="11" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="B252" s="11" t="s">
         <v>24</v>
       </c>
       <c r="C252" s="11" t="s">
+        <v>811</v>
+      </c>
+      <c r="D252" s="11" t="s">
         <v>812</v>
       </c>
-      <c r="D252" s="11" t="s">
-        <v>813</v>
-      </c>
       <c r="E252" s="11" t="s">
+        <v>796</v>
+      </c>
+      <c r="F252" s="11" t="s">
         <v>797</v>
       </c>
-      <c r="F252" s="11" t="s">
-        <v>798</v>
-      </c>
       <c r="G252" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H252" s="11">
-        <v>88</v>
+        <v>47</v>
       </c>
       <c r="I252" s="11" t="s">
         <v>1</v>
@@ -11366,28 +11363,28 @@
     </row>
     <row r="253" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A253" s="13" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="B253" s="13" t="s">
         <v>24</v>
       </c>
       <c r="C253" s="13" t="s">
+        <v>814</v>
+      </c>
+      <c r="D253" s="13" t="s">
         <v>815</v>
       </c>
-      <c r="D253" s="13" t="s">
-        <v>816</v>
-      </c>
       <c r="E253" s="13" t="s">
+        <v>796</v>
+      </c>
+      <c r="F253" s="13" t="s">
         <v>797</v>
       </c>
-      <c r="F253" s="13" t="s">
-        <v>798</v>
-      </c>
       <c r="G253" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H253" s="13">
-        <v>83</v>
+        <v>41</v>
       </c>
       <c r="I253" s="13" t="s">
         <v>1</v>
@@ -11395,28 +11392,28 @@
     </row>
     <row r="254" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A254" s="11" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="B254" s="11" t="s">
         <v>24</v>
       </c>
       <c r="C254" s="11" t="s">
+        <v>817</v>
+      </c>
+      <c r="D254" s="11" t="s">
         <v>818</v>
       </c>
-      <c r="D254" s="11" t="s">
-        <v>819</v>
-      </c>
       <c r="E254" s="11" t="s">
+        <v>796</v>
+      </c>
+      <c r="F254" s="11" t="s">
         <v>797</v>
       </c>
-      <c r="F254" s="11" t="s">
-        <v>798</v>
-      </c>
       <c r="G254" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H254" s="11">
-        <v>60</v>
+        <v>78</v>
       </c>
       <c r="I254" s="11" t="s">
         <v>1</v>
@@ -11424,28 +11421,28 @@
     </row>
     <row r="255" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A255" s="13" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="B255" s="13" t="s">
         <v>24</v>
       </c>
       <c r="C255" s="13" t="s">
+        <v>820</v>
+      </c>
+      <c r="D255" s="13" t="s">
         <v>821</v>
       </c>
-      <c r="D255" s="13" t="s">
-        <v>822</v>
-      </c>
       <c r="E255" s="13" t="s">
+        <v>796</v>
+      </c>
+      <c r="F255" s="13" t="s">
         <v>797</v>
       </c>
-      <c r="F255" s="13" t="s">
-        <v>798</v>
-      </c>
       <c r="G255" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H255" s="13">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="I255" s="13" t="s">
         <v>1</v>
@@ -11453,28 +11450,28 @@
     </row>
     <row r="256" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A256" s="11" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="B256" s="11" t="s">
         <v>24</v>
       </c>
       <c r="C256" s="11" t="s">
+        <v>823</v>
+      </c>
+      <c r="D256" s="11" t="s">
         <v>824</v>
       </c>
-      <c r="D256" s="11" t="s">
-        <v>825</v>
-      </c>
       <c r="E256" s="11" t="s">
+        <v>796</v>
+      </c>
+      <c r="F256" s="11" t="s">
         <v>797</v>
       </c>
-      <c r="F256" s="11" t="s">
-        <v>798</v>
-      </c>
       <c r="G256" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H256" s="11">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="I256" s="11" t="s">
         <v>1</v>
@@ -11482,28 +11479,28 @@
     </row>
     <row r="257" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A257" s="13" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="B257" s="13" t="s">
         <v>24</v>
       </c>
       <c r="C257" s="13" t="s">
+        <v>826</v>
+      </c>
+      <c r="D257" s="13" t="s">
         <v>827</v>
       </c>
-      <c r="D257" s="13" t="s">
-        <v>828</v>
-      </c>
       <c r="E257" s="13" t="s">
+        <v>796</v>
+      </c>
+      <c r="F257" s="13" t="s">
         <v>797</v>
       </c>
-      <c r="F257" s="13" t="s">
-        <v>798</v>
-      </c>
       <c r="G257" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H257" s="13">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="I257" s="13" t="s">
         <v>1</v>
@@ -11511,28 +11508,28 @@
     </row>
     <row r="258" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A258" s="11" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="B258" s="11" t="s">
         <v>24</v>
       </c>
       <c r="C258" s="11" t="s">
+        <v>829</v>
+      </c>
+      <c r="D258" s="11" t="s">
         <v>830</v>
       </c>
-      <c r="D258" s="11" t="s">
-        <v>831</v>
-      </c>
       <c r="E258" s="11" t="s">
+        <v>796</v>
+      </c>
+      <c r="F258" s="11" t="s">
         <v>797</v>
       </c>
-      <c r="F258" s="11" t="s">
-        <v>798</v>
-      </c>
       <c r="G258" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H258" s="11">
-        <v>89</v>
+        <v>58</v>
       </c>
       <c r="I258" s="11" t="s">
         <v>1</v>
@@ -11540,28 +11537,28 @@
     </row>
     <row r="259" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A259" s="13" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="B259" s="13" t="s">
         <v>24</v>
       </c>
       <c r="C259" s="13" t="s">
+        <v>832</v>
+      </c>
+      <c r="D259" s="13" t="s">
         <v>833</v>
       </c>
-      <c r="D259" s="13" t="s">
-        <v>834</v>
-      </c>
       <c r="E259" s="13" t="s">
+        <v>796</v>
+      </c>
+      <c r="F259" s="13" t="s">
         <v>797</v>
       </c>
-      <c r="F259" s="13" t="s">
-        <v>798</v>
-      </c>
       <c r="G259" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H259" s="13">
-        <v>23</v>
+        <v>61</v>
       </c>
       <c r="I259" s="13" t="s">
         <v>1</v>
@@ -11569,28 +11566,28 @@
     </row>
     <row r="260" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A260" s="11" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="B260" s="11" t="s">
         <v>24</v>
       </c>
       <c r="C260" s="11" t="s">
+        <v>835</v>
+      </c>
+      <c r="D260" s="11" t="s">
         <v>836</v>
       </c>
-      <c r="D260" s="11" t="s">
-        <v>837</v>
-      </c>
       <c r="E260" s="11" t="s">
+        <v>796</v>
+      </c>
+      <c r="F260" s="11" t="s">
         <v>797</v>
       </c>
-      <c r="F260" s="11" t="s">
-        <v>798</v>
-      </c>
       <c r="G260" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H260" s="11">
-        <v>56</v>
+        <v>33</v>
       </c>
       <c r="I260" s="11" t="s">
         <v>1</v>
@@ -11598,28 +11595,28 @@
     </row>
     <row r="261" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A261" s="13" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="B261" s="13" t="s">
         <v>24</v>
       </c>
       <c r="C261" s="13" t="s">
+        <v>838</v>
+      </c>
+      <c r="D261" s="13" t="s">
         <v>839</v>
       </c>
-      <c r="D261" s="13" t="s">
-        <v>840</v>
-      </c>
       <c r="E261" s="13" t="s">
+        <v>796</v>
+      </c>
+      <c r="F261" s="13" t="s">
         <v>797</v>
       </c>
-      <c r="F261" s="13" t="s">
-        <v>798</v>
-      </c>
       <c r="G261" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H261" s="13">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="I261" s="13" t="s">
         <v>1</v>
@@ -11627,28 +11624,28 @@
     </row>
     <row r="262" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A262" s="11" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="B262" s="11" t="s">
         <v>24</v>
       </c>
       <c r="C262" s="11" t="s">
+        <v>841</v>
+      </c>
+      <c r="D262" s="11" t="s">
         <v>842</v>
       </c>
-      <c r="D262" s="11" t="s">
-        <v>843</v>
-      </c>
       <c r="E262" s="11" t="s">
+        <v>796</v>
+      </c>
+      <c r="F262" s="11" t="s">
         <v>797</v>
       </c>
-      <c r="F262" s="11" t="s">
-        <v>798</v>
-      </c>
       <c r="G262" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H262" s="11">
-        <v>68</v>
+        <v>20</v>
       </c>
       <c r="I262" s="11" t="s">
         <v>1</v>
@@ -11656,28 +11653,28 @@
     </row>
     <row r="263" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A263" s="13" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="B263" s="13" t="s">
         <v>24</v>
       </c>
       <c r="C263" s="13" t="s">
+        <v>844</v>
+      </c>
+      <c r="D263" s="13" t="s">
         <v>845</v>
       </c>
-      <c r="D263" s="13" t="s">
-        <v>846</v>
-      </c>
       <c r="E263" s="13" t="s">
+        <v>796</v>
+      </c>
+      <c r="F263" s="13" t="s">
         <v>797</v>
       </c>
-      <c r="F263" s="13" t="s">
-        <v>798</v>
-      </c>
       <c r="G263" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H263" s="13">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="I263" s="13" t="s">
         <v>1</v>
@@ -11685,28 +11682,28 @@
     </row>
     <row r="264" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A264" s="11" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="B264" s="11" t="s">
         <v>24</v>
       </c>
       <c r="C264" s="11" t="s">
+        <v>847</v>
+      </c>
+      <c r="D264" s="11" t="s">
         <v>848</v>
       </c>
-      <c r="D264" s="11" t="s">
-        <v>849</v>
-      </c>
       <c r="E264" s="11" t="s">
+        <v>796</v>
+      </c>
+      <c r="F264" s="11" t="s">
         <v>797</v>
       </c>
-      <c r="F264" s="11" t="s">
-        <v>798</v>
-      </c>
       <c r="G264" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H264" s="11">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="I264" s="11" t="s">
         <v>1</v>
@@ -11714,28 +11711,28 @@
     </row>
     <row r="265" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A265" s="13" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="B265" s="13" t="s">
         <v>24</v>
       </c>
       <c r="C265" s="13" t="s">
+        <v>850</v>
+      </c>
+      <c r="D265" s="13" t="s">
         <v>851</v>
       </c>
-      <c r="D265" s="13" t="s">
-        <v>852</v>
-      </c>
       <c r="E265" s="13" t="s">
+        <v>796</v>
+      </c>
+      <c r="F265" s="13" t="s">
         <v>797</v>
       </c>
-      <c r="F265" s="13" t="s">
-        <v>798</v>
-      </c>
       <c r="G265" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H265" s="13">
-        <v>62</v>
+        <v>22</v>
       </c>
       <c r="I265" s="13" t="s">
         <v>1</v>
@@ -11743,28 +11740,28 @@
     </row>
     <row r="266" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A266" s="11" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="B266" s="11" t="s">
         <v>24</v>
       </c>
       <c r="C266" s="11" t="s">
+        <v>853</v>
+      </c>
+      <c r="D266" s="11" t="s">
         <v>854</v>
       </c>
-      <c r="D266" s="11" t="s">
-        <v>855</v>
-      </c>
       <c r="E266" s="11" t="s">
+        <v>796</v>
+      </c>
+      <c r="F266" s="11" t="s">
         <v>797</v>
       </c>
-      <c r="F266" s="11" t="s">
-        <v>798</v>
-      </c>
       <c r="G266" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H266" s="11">
-        <v>24</v>
+        <v>83</v>
       </c>
       <c r="I266" s="11" t="s">
         <v>1</v>
@@ -11772,28 +11769,28 @@
     </row>
     <row r="267" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A267" s="13" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="B267" s="13" t="s">
         <v>25</v>
       </c>
       <c r="C267" s="13" t="s">
+        <v>856</v>
+      </c>
+      <c r="D267" s="13" t="s">
         <v>857</v>
       </c>
-      <c r="D267" s="13" t="s">
+      <c r="E267" s="13" t="s">
         <v>858</v>
       </c>
-      <c r="E267" s="13" t="s">
+      <c r="F267" s="13" t="s">
         <v>859</v>
       </c>
-      <c r="F267" s="13" t="s">
-        <v>860</v>
-      </c>
       <c r="G267" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H267" s="13">
-        <v>77</v>
+        <v>61</v>
       </c>
       <c r="I267" s="13" t="s">
         <v>1</v>
@@ -11801,28 +11798,28 @@
     </row>
     <row r="268" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A268" s="11" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="B268" s="11" t="s">
         <v>25</v>
       </c>
       <c r="C268" s="11" t="s">
+        <v>861</v>
+      </c>
+      <c r="D268" s="11" t="s">
         <v>862</v>
       </c>
-      <c r="D268" s="11" t="s">
-        <v>863</v>
-      </c>
       <c r="E268" s="11" t="s">
+        <v>858</v>
+      </c>
+      <c r="F268" s="11" t="s">
         <v>859</v>
       </c>
-      <c r="F268" s="11" t="s">
-        <v>860</v>
-      </c>
       <c r="G268" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H268" s="11">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="I268" s="11" t="s">
         <v>1</v>
@@ -11830,28 +11827,28 @@
     </row>
     <row r="269" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A269" s="13" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="B269" s="13" t="s">
         <v>25</v>
       </c>
       <c r="C269" s="13" t="s">
+        <v>864</v>
+      </c>
+      <c r="D269" s="13" t="s">
         <v>865</v>
       </c>
-      <c r="D269" s="13" t="s">
-        <v>866</v>
-      </c>
       <c r="E269" s="13" t="s">
+        <v>858</v>
+      </c>
+      <c r="F269" s="13" t="s">
         <v>859</v>
       </c>
-      <c r="F269" s="13" t="s">
-        <v>860</v>
-      </c>
       <c r="G269" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H269" s="13">
-        <v>55</v>
+        <v>83</v>
       </c>
       <c r="I269" s="13" t="s">
         <v>1</v>
@@ -11859,28 +11856,28 @@
     </row>
     <row r="270" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A270" s="11" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="B270" s="11" t="s">
         <v>25</v>
       </c>
       <c r="C270" s="11" t="s">
+        <v>867</v>
+      </c>
+      <c r="D270" s="11" t="s">
         <v>868</v>
       </c>
-      <c r="D270" s="11" t="s">
-        <v>869</v>
-      </c>
       <c r="E270" s="11" t="s">
+        <v>858</v>
+      </c>
+      <c r="F270" s="11" t="s">
         <v>859</v>
       </c>
-      <c r="F270" s="11" t="s">
-        <v>860</v>
-      </c>
       <c r="G270" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H270" s="11">
-        <v>14</v>
+        <v>63</v>
       </c>
       <c r="I270" s="11" t="s">
         <v>1</v>
@@ -11888,28 +11885,28 @@
     </row>
     <row r="271" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A271" s="13" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="B271" s="13" t="s">
         <v>25</v>
       </c>
       <c r="C271" s="13" t="s">
+        <v>870</v>
+      </c>
+      <c r="D271" s="13" t="s">
         <v>871</v>
       </c>
-      <c r="D271" s="13" t="s">
-        <v>872</v>
-      </c>
       <c r="E271" s="13" t="s">
+        <v>858</v>
+      </c>
+      <c r="F271" s="13" t="s">
         <v>859</v>
       </c>
-      <c r="F271" s="13" t="s">
-        <v>860</v>
-      </c>
       <c r="G271" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H271" s="13">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="I271" s="13" t="s">
         <v>1</v>
@@ -11917,28 +11914,28 @@
     </row>
     <row r="272" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A272" s="11" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="B272" s="11" t="s">
         <v>25</v>
       </c>
       <c r="C272" s="11" t="s">
+        <v>873</v>
+      </c>
+      <c r="D272" s="11" t="s">
         <v>874</v>
       </c>
-      <c r="D272" s="11" t="s">
-        <v>875</v>
-      </c>
       <c r="E272" s="11" t="s">
+        <v>858</v>
+      </c>
+      <c r="F272" s="11" t="s">
         <v>859</v>
       </c>
-      <c r="F272" s="11" t="s">
-        <v>860</v>
-      </c>
       <c r="G272" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H272" s="11">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="I272" s="11" t="s">
         <v>1</v>
@@ -11946,28 +11943,28 @@
     </row>
     <row r="273" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A273" s="13" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="B273" s="13" t="s">
         <v>25</v>
       </c>
       <c r="C273" s="13" t="s">
+        <v>876</v>
+      </c>
+      <c r="D273" s="13" t="s">
         <v>877</v>
       </c>
-      <c r="D273" s="13" t="s">
-        <v>878</v>
-      </c>
       <c r="E273" s="13" t="s">
+        <v>858</v>
+      </c>
+      <c r="F273" s="13" t="s">
         <v>859</v>
       </c>
-      <c r="F273" s="13" t="s">
-        <v>860</v>
-      </c>
       <c r="G273" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H273" s="13">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="I273" s="13" t="s">
         <v>1</v>
@@ -11975,28 +11972,28 @@
     </row>
     <row r="274" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A274" s="11" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="B274" s="11" t="s">
         <v>25</v>
       </c>
       <c r="C274" s="11" t="s">
+        <v>879</v>
+      </c>
+      <c r="D274" s="11" t="s">
         <v>880</v>
       </c>
-      <c r="D274" s="11" t="s">
-        <v>881</v>
-      </c>
       <c r="E274" s="11" t="s">
+        <v>858</v>
+      </c>
+      <c r="F274" s="11" t="s">
         <v>859</v>
       </c>
-      <c r="F274" s="11" t="s">
-        <v>860</v>
-      </c>
       <c r="G274" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H274" s="11">
-        <v>54</v>
+        <v>14</v>
       </c>
       <c r="I274" s="11" t="s">
         <v>1</v>
@@ -12004,28 +12001,28 @@
     </row>
     <row r="275" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A275" s="13" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="B275" s="13" t="s">
         <v>25</v>
       </c>
       <c r="C275" s="13" t="s">
+        <v>882</v>
+      </c>
+      <c r="D275" s="13" t="s">
         <v>883</v>
       </c>
-      <c r="D275" s="13" t="s">
-        <v>884</v>
-      </c>
       <c r="E275" s="13" t="s">
+        <v>858</v>
+      </c>
+      <c r="F275" s="13" t="s">
         <v>859</v>
       </c>
-      <c r="F275" s="13" t="s">
-        <v>860</v>
-      </c>
       <c r="G275" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H275" s="13">
-        <v>49</v>
+        <v>78</v>
       </c>
       <c r="I275" s="13" t="s">
         <v>1</v>
@@ -12033,28 +12030,28 @@
     </row>
     <row r="276" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A276" s="11" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="B276" s="11" t="s">
         <v>25</v>
       </c>
       <c r="C276" s="11" t="s">
+        <v>885</v>
+      </c>
+      <c r="D276" s="11" t="s">
         <v>886</v>
       </c>
-      <c r="D276" s="11" t="s">
-        <v>887</v>
-      </c>
       <c r="E276" s="11" t="s">
+        <v>858</v>
+      </c>
+      <c r="F276" s="11" t="s">
         <v>859</v>
       </c>
-      <c r="F276" s="11" t="s">
-        <v>860</v>
-      </c>
       <c r="G276" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H276" s="11">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="I276" s="11" t="s">
         <v>1</v>
@@ -12062,28 +12059,28 @@
     </row>
     <row r="277" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A277" s="13" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="B277" s="13" t="s">
         <v>25</v>
       </c>
       <c r="C277" s="13" t="s">
+        <v>888</v>
+      </c>
+      <c r="D277" s="13" t="s">
         <v>889</v>
       </c>
-      <c r="D277" s="13" t="s">
-        <v>890</v>
-      </c>
       <c r="E277" s="13" t="s">
+        <v>858</v>
+      </c>
+      <c r="F277" s="13" t="s">
         <v>859</v>
       </c>
-      <c r="F277" s="13" t="s">
-        <v>860</v>
-      </c>
       <c r="G277" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H277" s="13">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="I277" s="13" t="s">
         <v>1</v>
@@ -12091,28 +12088,28 @@
     </row>
     <row r="278" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A278" s="11" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="B278" s="11" t="s">
         <v>25</v>
       </c>
       <c r="C278" s="11" t="s">
+        <v>891</v>
+      </c>
+      <c r="D278" s="11" t="s">
         <v>892</v>
       </c>
-      <c r="D278" s="11" t="s">
-        <v>893</v>
-      </c>
       <c r="E278" s="11" t="s">
+        <v>858</v>
+      </c>
+      <c r="F278" s="11" t="s">
         <v>859</v>
       </c>
-      <c r="F278" s="11" t="s">
-        <v>860</v>
-      </c>
       <c r="G278" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H278" s="11">
-        <v>11</v>
+        <v>52</v>
       </c>
       <c r="I278" s="11" t="s">
         <v>1</v>
@@ -12120,28 +12117,28 @@
     </row>
     <row r="279" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A279" s="13" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="B279" s="13" t="s">
         <v>25</v>
       </c>
       <c r="C279" s="13" t="s">
+        <v>894</v>
+      </c>
+      <c r="D279" s="13" t="s">
         <v>895</v>
       </c>
-      <c r="D279" s="13" t="s">
-        <v>896</v>
-      </c>
       <c r="E279" s="13" t="s">
+        <v>858</v>
+      </c>
+      <c r="F279" s="13" t="s">
         <v>859</v>
       </c>
-      <c r="F279" s="13" t="s">
-        <v>860</v>
-      </c>
       <c r="G279" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H279" s="13">
-        <v>85</v>
+        <v>48</v>
       </c>
       <c r="I279" s="13" t="s">
         <v>1</v>
@@ -12149,28 +12146,28 @@
     </row>
     <row r="280" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A280" s="11" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="B280" s="11" t="s">
         <v>25</v>
       </c>
       <c r="C280" s="11" t="s">
+        <v>897</v>
+      </c>
+      <c r="D280" s="11" t="s">
         <v>898</v>
       </c>
-      <c r="D280" s="11" t="s">
-        <v>899</v>
-      </c>
       <c r="E280" s="11" t="s">
+        <v>858</v>
+      </c>
+      <c r="F280" s="11" t="s">
         <v>859</v>
       </c>
-      <c r="F280" s="11" t="s">
-        <v>860</v>
-      </c>
       <c r="G280" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H280" s="11">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="I280" s="11" t="s">
         <v>1</v>
@@ -12178,28 +12175,28 @@
     </row>
     <row r="281" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A281" s="13" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="B281" s="13" t="s">
         <v>25</v>
       </c>
       <c r="C281" s="13" t="s">
+        <v>900</v>
+      </c>
+      <c r="D281" s="13" t="s">
         <v>901</v>
       </c>
-      <c r="D281" s="13" t="s">
-        <v>902</v>
-      </c>
       <c r="E281" s="13" t="s">
+        <v>858</v>
+      </c>
+      <c r="F281" s="13" t="s">
         <v>859</v>
       </c>
-      <c r="F281" s="13" t="s">
-        <v>860</v>
-      </c>
       <c r="G281" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H281" s="13">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="I281" s="13" t="s">
         <v>1</v>
@@ -12207,28 +12204,28 @@
     </row>
     <row r="282" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A282" s="11" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="B282" s="11" t="s">
         <v>26</v>
       </c>
       <c r="C282" s="11" t="s">
+        <v>903</v>
+      </c>
+      <c r="D282" s="11" t="s">
         <v>904</v>
       </c>
-      <c r="D282" s="11" t="s">
+      <c r="E282" s="11" t="s">
         <v>905</v>
       </c>
-      <c r="E282" s="11" t="s">
+      <c r="F282" s="11" t="s">
         <v>906</v>
       </c>
-      <c r="F282" s="11" t="s">
-        <v>907</v>
-      </c>
       <c r="G282" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H282" s="11">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="I282" s="11" t="s">
         <v>1</v>
@@ -12236,28 +12233,28 @@
     </row>
     <row r="283" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A283" s="13" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="B283" s="13" t="s">
         <v>26</v>
       </c>
       <c r="C283" s="13" t="s">
+        <v>908</v>
+      </c>
+      <c r="D283" s="13" t="s">
         <v>909</v>
       </c>
-      <c r="D283" s="13" t="s">
-        <v>910</v>
-      </c>
       <c r="E283" s="13" t="s">
+        <v>905</v>
+      </c>
+      <c r="F283" s="13" t="s">
         <v>906</v>
       </c>
-      <c r="F283" s="13" t="s">
-        <v>907</v>
-      </c>
       <c r="G283" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H283" s="13">
-        <v>82</v>
+        <v>16</v>
       </c>
       <c r="I283" s="13" t="s">
         <v>1</v>
@@ -12265,28 +12262,28 @@
     </row>
     <row r="284" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A284" s="11" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="B284" s="11" t="s">
         <v>26</v>
       </c>
       <c r="C284" s="11" t="s">
+        <v>911</v>
+      </c>
+      <c r="D284" s="11" t="s">
         <v>912</v>
       </c>
-      <c r="D284" s="11" t="s">
-        <v>913</v>
-      </c>
       <c r="E284" s="11" t="s">
+        <v>905</v>
+      </c>
+      <c r="F284" s="11" t="s">
         <v>906</v>
       </c>
-      <c r="F284" s="11" t="s">
-        <v>907</v>
-      </c>
       <c r="G284" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H284" s="11">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="I284" s="11" t="s">
         <v>1</v>
@@ -12294,28 +12291,28 @@
     </row>
     <row r="285" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A285" s="13" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="B285" s="13" t="s">
         <v>26</v>
       </c>
       <c r="C285" s="13" t="s">
+        <v>914</v>
+      </c>
+      <c r="D285" s="13" t="s">
         <v>915</v>
       </c>
-      <c r="D285" s="13" t="s">
-        <v>916</v>
-      </c>
       <c r="E285" s="13" t="s">
+        <v>905</v>
+      </c>
+      <c r="F285" s="13" t="s">
         <v>906</v>
       </c>
-      <c r="F285" s="13" t="s">
-        <v>907</v>
-      </c>
       <c r="G285" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H285" s="13">
-        <v>80</v>
+        <v>48</v>
       </c>
       <c r="I285" s="13" t="s">
         <v>1</v>
@@ -12323,28 +12320,28 @@
     </row>
     <row r="286" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A286" s="11" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="B286" s="11" t="s">
         <v>26</v>
       </c>
       <c r="C286" s="11" t="s">
+        <v>917</v>
+      </c>
+      <c r="D286" s="11" t="s">
         <v>918</v>
       </c>
-      <c r="D286" s="11" t="s">
-        <v>919</v>
-      </c>
       <c r="E286" s="11" t="s">
+        <v>905</v>
+      </c>
+      <c r="F286" s="11" t="s">
         <v>906</v>
       </c>
-      <c r="F286" s="11" t="s">
-        <v>907</v>
-      </c>
       <c r="G286" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H286" s="11">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="I286" s="11" t="s">
         <v>1</v>
@@ -12352,28 +12349,28 @@
     </row>
     <row r="287" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A287" s="13" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="B287" s="13" t="s">
         <v>26</v>
       </c>
       <c r="C287" s="13" t="s">
+        <v>920</v>
+      </c>
+      <c r="D287" s="13" t="s">
         <v>921</v>
       </c>
-      <c r="D287" s="13" t="s">
-        <v>922</v>
-      </c>
       <c r="E287" s="13" t="s">
+        <v>905</v>
+      </c>
+      <c r="F287" s="13" t="s">
         <v>906</v>
       </c>
-      <c r="F287" s="13" t="s">
-        <v>907</v>
-      </c>
       <c r="G287" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H287" s="13">
-        <v>32</v>
+        <v>88</v>
       </c>
       <c r="I287" s="13" t="s">
         <v>1</v>
@@ -12381,28 +12378,28 @@
     </row>
     <row r="288" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A288" s="11" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="B288" s="11" t="s">
         <v>26</v>
       </c>
       <c r="C288" s="11" t="s">
+        <v>923</v>
+      </c>
+      <c r="D288" s="11" t="s">
         <v>924</v>
       </c>
-      <c r="D288" s="11" t="s">
-        <v>925</v>
-      </c>
       <c r="E288" s="11" t="s">
+        <v>905</v>
+      </c>
+      <c r="F288" s="11" t="s">
         <v>906</v>
       </c>
-      <c r="F288" s="11" t="s">
-        <v>907</v>
-      </c>
       <c r="G288" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H288" s="11">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="I288" s="11" t="s">
         <v>1</v>
@@ -12410,28 +12407,28 @@
     </row>
     <row r="289" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A289" s="13" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="B289" s="13" t="s">
         <v>26</v>
       </c>
       <c r="C289" s="13" t="s">
+        <v>926</v>
+      </c>
+      <c r="D289" s="13" t="s">
         <v>927</v>
       </c>
-      <c r="D289" s="13" t="s">
-        <v>928</v>
-      </c>
       <c r="E289" s="13" t="s">
+        <v>905</v>
+      </c>
+      <c r="F289" s="13" t="s">
         <v>906</v>
       </c>
-      <c r="F289" s="13" t="s">
-        <v>907</v>
-      </c>
       <c r="G289" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H289" s="13">
-        <v>73</v>
+        <v>10</v>
       </c>
       <c r="I289" s="13" t="s">
         <v>1</v>
@@ -12439,28 +12436,28 @@
     </row>
     <row r="290" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A290" s="11" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="B290" s="11" t="s">
         <v>26</v>
       </c>
       <c r="C290" s="11" t="s">
+        <v>929</v>
+      </c>
+      <c r="D290" s="11" t="s">
         <v>930</v>
       </c>
-      <c r="D290" s="11" t="s">
-        <v>931</v>
-      </c>
       <c r="E290" s="11" t="s">
+        <v>905</v>
+      </c>
+      <c r="F290" s="11" t="s">
         <v>906</v>
       </c>
-      <c r="F290" s="11" t="s">
-        <v>907</v>
-      </c>
       <c r="G290" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H290" s="11">
-        <v>39</v>
+        <v>69</v>
       </c>
       <c r="I290" s="11" t="s">
         <v>1</v>
@@ -12468,28 +12465,28 @@
     </row>
     <row r="291" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A291" s="13" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="B291" s="13" t="s">
         <v>26</v>
       </c>
       <c r="C291" s="13" t="s">
+        <v>932</v>
+      </c>
+      <c r="D291" s="13" t="s">
         <v>933</v>
       </c>
-      <c r="D291" s="13" t="s">
-        <v>934</v>
-      </c>
       <c r="E291" s="13" t="s">
+        <v>905</v>
+      </c>
+      <c r="F291" s="13" t="s">
         <v>906</v>
       </c>
-      <c r="F291" s="13" t="s">
-        <v>907</v>
-      </c>
       <c r="G291" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H291" s="13">
-        <v>39</v>
+        <v>79</v>
       </c>
       <c r="I291" s="13" t="s">
         <v>1</v>
@@ -12497,28 +12494,28 @@
     </row>
     <row r="292" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A292" s="11" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="B292" s="11" t="s">
         <v>26</v>
       </c>
       <c r="C292" s="11" t="s">
+        <v>935</v>
+      </c>
+      <c r="D292" s="11" t="s">
         <v>936</v>
       </c>
-      <c r="D292" s="11" t="s">
-        <v>937</v>
-      </c>
       <c r="E292" s="11" t="s">
+        <v>905</v>
+      </c>
+      <c r="F292" s="11" t="s">
         <v>906</v>
       </c>
-      <c r="F292" s="11" t="s">
-        <v>907</v>
-      </c>
       <c r="G292" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H292" s="11">
-        <v>82</v>
+        <v>30</v>
       </c>
       <c r="I292" s="11" t="s">
         <v>1</v>
@@ -12526,28 +12523,28 @@
     </row>
     <row r="293" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A293" s="13" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="B293" s="13" t="s">
         <v>26</v>
       </c>
       <c r="C293" s="13" t="s">
+        <v>938</v>
+      </c>
+      <c r="D293" s="13" t="s">
         <v>939</v>
       </c>
-      <c r="D293" s="13" t="s">
-        <v>940</v>
-      </c>
       <c r="E293" s="13" t="s">
+        <v>905</v>
+      </c>
+      <c r="F293" s="13" t="s">
         <v>906</v>
       </c>
-      <c r="F293" s="13" t="s">
-        <v>907</v>
-      </c>
       <c r="G293" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H293" s="13">
-        <v>30</v>
+        <v>72</v>
       </c>
       <c r="I293" s="13" t="s">
         <v>1</v>
@@ -12555,28 +12552,28 @@
     </row>
     <row r="294" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A294" s="11" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="B294" s="11" t="s">
         <v>26</v>
       </c>
       <c r="C294" s="11" t="s">
+        <v>941</v>
+      </c>
+      <c r="D294" s="11" t="s">
         <v>942</v>
       </c>
-      <c r="D294" s="11" t="s">
-        <v>943</v>
-      </c>
       <c r="E294" s="11" t="s">
+        <v>905</v>
+      </c>
+      <c r="F294" s="11" t="s">
         <v>906</v>
       </c>
-      <c r="F294" s="11" t="s">
-        <v>907</v>
-      </c>
       <c r="G294" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H294" s="11">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="I294" s="11" t="s">
         <v>1</v>
@@ -12584,28 +12581,28 @@
     </row>
     <row r="295" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A295" s="13" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="B295" s="13" t="s">
         <v>26</v>
       </c>
       <c r="C295" s="13" t="s">
+        <v>944</v>
+      </c>
+      <c r="D295" s="13" t="s">
         <v>945</v>
       </c>
-      <c r="D295" s="13" t="s">
-        <v>946</v>
-      </c>
       <c r="E295" s="13" t="s">
+        <v>905</v>
+      </c>
+      <c r="F295" s="13" t="s">
         <v>906</v>
       </c>
-      <c r="F295" s="13" t="s">
-        <v>907</v>
-      </c>
       <c r="G295" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H295" s="13">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="I295" s="13" t="s">
         <v>1</v>
@@ -12613,28 +12610,28 @@
     </row>
     <row r="296" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A296" s="11" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="B296" s="11" t="s">
         <v>26</v>
       </c>
       <c r="C296" s="11" t="s">
+        <v>947</v>
+      </c>
+      <c r="D296" s="11" t="s">
         <v>948</v>
       </c>
-      <c r="D296" s="11" t="s">
-        <v>949</v>
-      </c>
       <c r="E296" s="11" t="s">
+        <v>905</v>
+      </c>
+      <c r="F296" s="11" t="s">
         <v>906</v>
       </c>
-      <c r="F296" s="11" t="s">
-        <v>907</v>
-      </c>
       <c r="G296" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H296" s="11">
-        <v>59</v>
+        <v>88</v>
       </c>
       <c r="I296" s="11" t="s">
         <v>1</v>
@@ -12642,28 +12639,28 @@
     </row>
     <row r="297" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A297" s="13" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="B297" s="13" t="s">
         <v>26</v>
       </c>
       <c r="C297" s="13" t="s">
+        <v>950</v>
+      </c>
+      <c r="D297" s="13" t="s">
         <v>951</v>
       </c>
-      <c r="D297" s="13" t="s">
-        <v>952</v>
-      </c>
       <c r="E297" s="13" t="s">
+        <v>905</v>
+      </c>
+      <c r="F297" s="13" t="s">
         <v>906</v>
       </c>
-      <c r="F297" s="13" t="s">
-        <v>907</v>
-      </c>
       <c r="G297" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H297" s="13">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I297" s="13" t="s">
         <v>1</v>
@@ -12671,28 +12668,28 @@
     </row>
     <row r="298" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A298" s="11" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="B298" s="11" t="s">
         <v>26</v>
       </c>
       <c r="C298" s="11" t="s">
+        <v>953</v>
+      </c>
+      <c r="D298" s="11" t="s">
         <v>954</v>
       </c>
-      <c r="D298" s="11" t="s">
-        <v>955</v>
-      </c>
       <c r="E298" s="11" t="s">
+        <v>905</v>
+      </c>
+      <c r="F298" s="11" t="s">
         <v>906</v>
       </c>
-      <c r="F298" s="11" t="s">
-        <v>907</v>
-      </c>
       <c r="G298" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H298" s="11">
-        <v>16</v>
+        <v>80</v>
       </c>
       <c r="I298" s="11" t="s">
         <v>1</v>
@@ -12700,28 +12697,28 @@
     </row>
     <row r="299" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A299" s="13" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="B299" s="13" t="s">
         <v>26</v>
       </c>
       <c r="C299" s="13" t="s">
+        <v>956</v>
+      </c>
+      <c r="D299" s="13" t="s">
         <v>957</v>
       </c>
-      <c r="D299" s="13" t="s">
-        <v>958</v>
-      </c>
       <c r="E299" s="13" t="s">
+        <v>905</v>
+      </c>
+      <c r="F299" s="13" t="s">
         <v>906</v>
       </c>
-      <c r="F299" s="13" t="s">
-        <v>907</v>
-      </c>
       <c r="G299" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H299" s="13">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="I299" s="13" t="s">
         <v>1</v>
@@ -12729,28 +12726,28 @@
     </row>
     <row r="300" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A300" s="11" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="B300" s="11" t="s">
         <v>26</v>
       </c>
       <c r="C300" s="11" t="s">
+        <v>959</v>
+      </c>
+      <c r="D300" s="11" t="s">
         <v>960</v>
       </c>
-      <c r="D300" s="11" t="s">
-        <v>961</v>
-      </c>
       <c r="E300" s="11" t="s">
+        <v>905</v>
+      </c>
+      <c r="F300" s="11" t="s">
         <v>906</v>
       </c>
-      <c r="F300" s="11" t="s">
-        <v>907</v>
-      </c>
       <c r="G300" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H300" s="11">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="I300" s="11" t="s">
         <v>1</v>
@@ -12758,28 +12755,28 @@
     </row>
     <row r="301" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A301" s="13" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="B301" s="13" t="s">
         <v>26</v>
       </c>
       <c r="C301" s="13" t="s">
+        <v>962</v>
+      </c>
+      <c r="D301" s="13" t="s">
         <v>963</v>
       </c>
-      <c r="D301" s="13" t="s">
-        <v>964</v>
-      </c>
       <c r="E301" s="13" t="s">
+        <v>905</v>
+      </c>
+      <c r="F301" s="13" t="s">
         <v>906</v>
       </c>
-      <c r="F301" s="13" t="s">
-        <v>907</v>
-      </c>
       <c r="G301" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H301" s="13">
-        <v>59</v>
+        <v>25</v>
       </c>
       <c r="I301" s="13" t="s">
         <v>1</v>
@@ -12787,28 +12784,28 @@
     </row>
     <row r="302" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A302" s="11" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="B302" s="11" t="s">
         <v>26</v>
       </c>
       <c r="C302" s="11" t="s">
+        <v>965</v>
+      </c>
+      <c r="D302" s="11" t="s">
         <v>966</v>
       </c>
-      <c r="D302" s="11" t="s">
-        <v>967</v>
-      </c>
       <c r="E302" s="11" t="s">
+        <v>905</v>
+      </c>
+      <c r="F302" s="11" t="s">
         <v>906</v>
       </c>
-      <c r="F302" s="11" t="s">
-        <v>907</v>
-      </c>
       <c r="G302" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H302" s="11">
-        <v>76</v>
+        <v>11</v>
       </c>
       <c r="I302" s="11" t="s">
         <v>1</v>
@@ -12816,28 +12813,28 @@
     </row>
     <row r="303" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A303" s="13" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="B303" s="13" t="s">
         <v>26</v>
       </c>
       <c r="C303" s="13" t="s">
+        <v>968</v>
+      </c>
+      <c r="D303" s="13" t="s">
         <v>969</v>
       </c>
-      <c r="D303" s="13" t="s">
-        <v>970</v>
-      </c>
       <c r="E303" s="13" t="s">
+        <v>905</v>
+      </c>
+      <c r="F303" s="13" t="s">
         <v>906</v>
       </c>
-      <c r="F303" s="13" t="s">
-        <v>907</v>
-      </c>
       <c r="G303" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H303" s="13">
-        <v>35</v>
+        <v>85</v>
       </c>
       <c r="I303" s="13" t="s">
         <v>1</v>
@@ -12845,28 +12842,28 @@
     </row>
     <row r="304" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A304" s="11" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="B304" s="11" t="s">
         <v>26</v>
       </c>
       <c r="C304" s="11" t="s">
+        <v>971</v>
+      </c>
+      <c r="D304" s="11" t="s">
         <v>972</v>
       </c>
-      <c r="D304" s="11" t="s">
-        <v>973</v>
-      </c>
       <c r="E304" s="11" t="s">
+        <v>905</v>
+      </c>
+      <c r="F304" s="11" t="s">
         <v>906</v>
       </c>
-      <c r="F304" s="11" t="s">
-        <v>907</v>
-      </c>
       <c r="G304" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H304" s="11">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="I304" s="11" t="s">
         <v>1</v>
@@ -12874,28 +12871,28 @@
     </row>
     <row r="305" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A305" s="13" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="B305" s="13" t="s">
         <v>26</v>
       </c>
       <c r="C305" s="13" t="s">
+        <v>974</v>
+      </c>
+      <c r="D305" s="13" t="s">
         <v>975</v>
       </c>
-      <c r="D305" s="13" t="s">
-        <v>976</v>
-      </c>
       <c r="E305" s="13" t="s">
+        <v>905</v>
+      </c>
+      <c r="F305" s="13" t="s">
         <v>906</v>
       </c>
-      <c r="F305" s="13" t="s">
-        <v>907</v>
-      </c>
       <c r="G305" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H305" s="13">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="I305" s="13" t="s">
         <v>1</v>
@@ -12903,22 +12900,22 @@
     </row>
     <row r="306" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A306" s="11" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="B306" s="11" t="s">
         <v>26</v>
       </c>
       <c r="C306" s="11" t="s">
+        <v>977</v>
+      </c>
+      <c r="D306" s="11" t="s">
         <v>978</v>
       </c>
-      <c r="D306" s="11" t="s">
-        <v>979</v>
-      </c>
       <c r="E306" s="11" t="s">
+        <v>905</v>
+      </c>
+      <c r="F306" s="11" t="s">
         <v>906</v>
-      </c>
-      <c r="F306" s="11" t="s">
-        <v>907</v>
       </c>
       <c r="G306" s="12" t="s">
         <v>9</v>
@@ -12932,28 +12929,28 @@
     </row>
     <row r="307" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A307" s="13" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="B307" s="13" t="s">
         <v>27</v>
       </c>
       <c r="C307" s="13" t="s">
+        <v>980</v>
+      </c>
+      <c r="D307" s="13" t="s">
         <v>981</v>
       </c>
-      <c r="D307" s="13" t="s">
+      <c r="E307" s="13" t="s">
         <v>982</v>
       </c>
-      <c r="E307" s="13" t="s">
+      <c r="F307" s="13" t="s">
         <v>983</v>
       </c>
-      <c r="F307" s="13" t="s">
-        <v>984</v>
-      </c>
       <c r="G307" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H307" s="13">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="I307" s="13" t="s">
         <v>1</v>
@@ -12961,28 +12958,28 @@
     </row>
     <row r="308" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A308" s="11" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="B308" s="11" t="s">
         <v>27</v>
       </c>
       <c r="C308" s="11" t="s">
+        <v>985</v>
+      </c>
+      <c r="D308" s="11" t="s">
         <v>986</v>
       </c>
-      <c r="D308" s="11" t="s">
-        <v>987</v>
-      </c>
       <c r="E308" s="11" t="s">
+        <v>982</v>
+      </c>
+      <c r="F308" s="11" t="s">
         <v>983</v>
       </c>
-      <c r="F308" s="11" t="s">
-        <v>984</v>
-      </c>
       <c r="G308" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H308" s="11">
-        <v>83</v>
+        <v>36</v>
       </c>
       <c r="I308" s="11" t="s">
         <v>1</v>
@@ -12990,28 +12987,28 @@
     </row>
     <row r="309" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A309" s="13" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="B309" s="13" t="s">
         <v>27</v>
       </c>
       <c r="C309" s="13" t="s">
+        <v>988</v>
+      </c>
+      <c r="D309" s="13" t="s">
         <v>989</v>
       </c>
-      <c r="D309" s="13" t="s">
-        <v>990</v>
-      </c>
       <c r="E309" s="13" t="s">
+        <v>982</v>
+      </c>
+      <c r="F309" s="13" t="s">
         <v>983</v>
       </c>
-      <c r="F309" s="13" t="s">
-        <v>984</v>
-      </c>
       <c r="G309" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H309" s="13">
-        <v>40</v>
+        <v>72</v>
       </c>
       <c r="I309" s="13" t="s">
         <v>1</v>
@@ -13019,28 +13016,28 @@
     </row>
     <row r="310" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A310" s="11" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="B310" s="11" t="s">
         <v>27</v>
       </c>
       <c r="C310" s="11" t="s">
+        <v>991</v>
+      </c>
+      <c r="D310" s="11" t="s">
         <v>992</v>
       </c>
-      <c r="D310" s="11" t="s">
-        <v>993</v>
-      </c>
       <c r="E310" s="11" t="s">
+        <v>982</v>
+      </c>
+      <c r="F310" s="11" t="s">
         <v>983</v>
       </c>
-      <c r="F310" s="11" t="s">
-        <v>984</v>
-      </c>
       <c r="G310" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H310" s="11">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="I310" s="11" t="s">
         <v>1</v>
@@ -13048,28 +13045,28 @@
     </row>
     <row r="311" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A311" s="13" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="B311" s="13" t="s">
         <v>27</v>
       </c>
       <c r="C311" s="13" t="s">
+        <v>994</v>
+      </c>
+      <c r="D311" s="13" t="s">
         <v>995</v>
       </c>
-      <c r="D311" s="13" t="s">
-        <v>996</v>
-      </c>
       <c r="E311" s="13" t="s">
+        <v>982</v>
+      </c>
+      <c r="F311" s="13" t="s">
         <v>983</v>
       </c>
-      <c r="F311" s="13" t="s">
-        <v>984</v>
-      </c>
       <c r="G311" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H311" s="13">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="I311" s="13" t="s">
         <v>1</v>
@@ -13077,28 +13074,28 @@
     </row>
     <row r="312" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A312" s="11" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="B312" s="11" t="s">
         <v>27</v>
       </c>
       <c r="C312" s="11" t="s">
+        <v>997</v>
+      </c>
+      <c r="D312" s="11" t="s">
         <v>998</v>
       </c>
-      <c r="D312" s="11" t="s">
-        <v>999</v>
-      </c>
       <c r="E312" s="11" t="s">
+        <v>982</v>
+      </c>
+      <c r="F312" s="11" t="s">
         <v>983</v>
       </c>
-      <c r="F312" s="11" t="s">
-        <v>984</v>
-      </c>
       <c r="G312" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H312" s="11">
-        <v>76</v>
+        <v>26</v>
       </c>
       <c r="I312" s="11" t="s">
         <v>1</v>
@@ -13106,28 +13103,28 @@
     </row>
     <row r="313" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A313" s="13" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
       <c r="B313" s="13" t="s">
         <v>27</v>
       </c>
       <c r="C313" s="13" t="s">
+        <v>1000</v>
+      </c>
+      <c r="D313" s="13" t="s">
         <v>1001</v>
       </c>
-      <c r="D313" s="13" t="s">
-        <v>1002</v>
-      </c>
       <c r="E313" s="13" t="s">
+        <v>982</v>
+      </c>
+      <c r="F313" s="13" t="s">
         <v>983</v>
       </c>
-      <c r="F313" s="13" t="s">
-        <v>984</v>
-      </c>
       <c r="G313" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H313" s="13">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I313" s="13" t="s">
         <v>1</v>
@@ -13135,28 +13132,28 @@
     </row>
     <row r="314" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A314" s="11" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="B314" s="11" t="s">
         <v>27</v>
       </c>
       <c r="C314" s="11" t="s">
+        <v>1003</v>
+      </c>
+      <c r="D314" s="11" t="s">
         <v>1004</v>
       </c>
-      <c r="D314" s="11" t="s">
-        <v>1005</v>
-      </c>
       <c r="E314" s="11" t="s">
+        <v>982</v>
+      </c>
+      <c r="F314" s="11" t="s">
         <v>983</v>
       </c>
-      <c r="F314" s="11" t="s">
-        <v>984</v>
-      </c>
       <c r="G314" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H314" s="11">
-        <v>74</v>
+        <v>16</v>
       </c>
       <c r="I314" s="11" t="s">
         <v>1</v>
@@ -13164,28 +13161,28 @@
     </row>
     <row r="315" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A315" s="13" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="B315" s="13" t="s">
         <v>27</v>
       </c>
       <c r="C315" s="13" t="s">
+        <v>1006</v>
+      </c>
+      <c r="D315" s="13" t="s">
         <v>1007</v>
       </c>
-      <c r="D315" s="13" t="s">
-        <v>1008</v>
-      </c>
       <c r="E315" s="13" t="s">
+        <v>982</v>
+      </c>
+      <c r="F315" s="13" t="s">
         <v>983</v>
       </c>
-      <c r="F315" s="13" t="s">
-        <v>984</v>
-      </c>
       <c r="G315" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H315" s="13">
-        <v>18</v>
+        <v>58</v>
       </c>
       <c r="I315" s="13" t="s">
         <v>1</v>
@@ -13193,28 +13190,28 @@
     </row>
     <row r="316" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A316" s="11" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="B316" s="11" t="s">
         <v>27</v>
       </c>
       <c r="C316" s="11" t="s">
+        <v>1009</v>
+      </c>
+      <c r="D316" s="11" t="s">
         <v>1010</v>
       </c>
-      <c r="D316" s="11" t="s">
-        <v>1011</v>
-      </c>
       <c r="E316" s="11" t="s">
+        <v>982</v>
+      </c>
+      <c r="F316" s="11" t="s">
         <v>983</v>
       </c>
-      <c r="F316" s="11" t="s">
-        <v>984</v>
-      </c>
       <c r="G316" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H316" s="11">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="I316" s="11" t="s">
         <v>1</v>
@@ -13222,28 +13219,28 @@
     </row>
     <row r="317" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A317" s="13" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="B317" s="13" t="s">
         <v>27</v>
       </c>
       <c r="C317" s="13" t="s">
+        <v>1012</v>
+      </c>
+      <c r="D317" s="13" t="s">
         <v>1013</v>
       </c>
-      <c r="D317" s="13" t="s">
-        <v>1014</v>
-      </c>
       <c r="E317" s="13" t="s">
+        <v>982</v>
+      </c>
+      <c r="F317" s="13" t="s">
         <v>983</v>
       </c>
-      <c r="F317" s="13" t="s">
-        <v>984</v>
-      </c>
       <c r="G317" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H317" s="13">
-        <v>85</v>
+        <v>26</v>
       </c>
       <c r="I317" s="13" t="s">
         <v>1</v>
@@ -13251,28 +13248,28 @@
     </row>
     <row r="318" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A318" s="11" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="B318" s="11" t="s">
         <v>27</v>
       </c>
       <c r="C318" s="11" t="s">
+        <v>1015</v>
+      </c>
+      <c r="D318" s="11" t="s">
         <v>1016</v>
       </c>
-      <c r="D318" s="11" t="s">
-        <v>1017</v>
-      </c>
       <c r="E318" s="11" t="s">
+        <v>982</v>
+      </c>
+      <c r="F318" s="11" t="s">
         <v>983</v>
       </c>
-      <c r="F318" s="11" t="s">
-        <v>984</v>
-      </c>
       <c r="G318" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H318" s="11">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="I318" s="11" t="s">
         <v>1</v>
@@ -13280,28 +13277,28 @@
     </row>
     <row r="319" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A319" s="13" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
       <c r="B319" s="13" t="s">
         <v>27</v>
       </c>
       <c r="C319" s="13" t="s">
+        <v>1018</v>
+      </c>
+      <c r="D319" s="13" t="s">
         <v>1019</v>
       </c>
-      <c r="D319" s="13" t="s">
-        <v>1020</v>
-      </c>
       <c r="E319" s="13" t="s">
+        <v>982</v>
+      </c>
+      <c r="F319" s="13" t="s">
         <v>983</v>
       </c>
-      <c r="F319" s="13" t="s">
-        <v>984</v>
-      </c>
       <c r="G319" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H319" s="13">
-        <v>28</v>
+        <v>66</v>
       </c>
       <c r="I319" s="13" t="s">
         <v>1</v>
@@ -13309,28 +13306,28 @@
     </row>
     <row r="320" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A320" s="11" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="B320" s="11" t="s">
         <v>27</v>
       </c>
       <c r="C320" s="11" t="s">
+        <v>1021</v>
+      </c>
+      <c r="D320" s="11" t="s">
         <v>1022</v>
       </c>
-      <c r="D320" s="11" t="s">
-        <v>1023</v>
-      </c>
       <c r="E320" s="11" t="s">
+        <v>982</v>
+      </c>
+      <c r="F320" s="11" t="s">
         <v>983</v>
       </c>
-      <c r="F320" s="11" t="s">
-        <v>984</v>
-      </c>
       <c r="G320" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H320" s="11">
-        <v>28</v>
+        <v>67</v>
       </c>
       <c r="I320" s="11" t="s">
         <v>1</v>
@@ -13338,28 +13335,28 @@
     </row>
     <row r="321" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A321" s="13" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="B321" s="13" t="s">
         <v>27</v>
       </c>
       <c r="C321" s="13" t="s">
+        <v>1024</v>
+      </c>
+      <c r="D321" s="13" t="s">
         <v>1025</v>
       </c>
-      <c r="D321" s="13" t="s">
-        <v>1026</v>
-      </c>
       <c r="E321" s="13" t="s">
+        <v>982</v>
+      </c>
+      <c r="F321" s="13" t="s">
         <v>983</v>
       </c>
-      <c r="F321" s="13" t="s">
-        <v>984</v>
-      </c>
       <c r="G321" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H321" s="13">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I321" s="13" t="s">
         <v>1</v>

--- a/testing/selenium-tests/Test_Report.xlsx
+++ b/testing/selenium-tests/Test_Report.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2636" uniqueCount="1026">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2636" uniqueCount="1027">
   <si>
     <t>GROWMARK WEB APP - AUTOMATED TESTING REPORT</t>
   </si>
@@ -1805,7 +1805,7 @@
     <t>TestCase_WebSales_01: Processing sales entry for Item_1</t>
   </si>
   <si>
-    <t>Sold 274 units of Item_1</t>
+    <t>Sold 461 units of Item_1</t>
   </si>
   <si>
     <t>Sales logged and inventory updated</t>
@@ -1820,7 +1820,7 @@
     <t>TestCase_WebSales_02: Processing sales entry for Item_2</t>
   </si>
   <si>
-    <t>Sold 430 units of Item_2</t>
+    <t>Sold 475 units of Item_2</t>
   </si>
   <si>
     <t>TC183</t>
@@ -1829,7 +1829,7 @@
     <t>TestCase_WebSales_03: Processing sales entry for Item_3</t>
   </si>
   <si>
-    <t>Sold 286 units of Item_3</t>
+    <t>Sold 2 units of Item_3</t>
   </si>
   <si>
     <t>TC184</t>
@@ -1838,7 +1838,7 @@
     <t>TestCase_WebSales_04: Processing sales entry for Item_4</t>
   </si>
   <si>
-    <t>Sold 451 units of Item_4</t>
+    <t>Sold 358 units of Item_4</t>
   </si>
   <si>
     <t>TC185</t>
@@ -1847,7 +1847,7 @@
     <t>TestCase_WebSales_05: Processing sales entry for Item_5</t>
   </si>
   <si>
-    <t>Sold 87 units of Item_5</t>
+    <t>Sold 217 units of Item_5</t>
   </si>
   <si>
     <t>TC186</t>
@@ -1856,7 +1856,7 @@
     <t>TestCase_WebSales_06: Processing sales entry for Item_6</t>
   </si>
   <si>
-    <t>Sold 390 units of Item_6</t>
+    <t>Sold 22 units of Item_6</t>
   </si>
   <si>
     <t>TC187</t>
@@ -1865,7 +1865,7 @@
     <t>TestCase_WebSales_07: Processing sales entry for Item_7</t>
   </si>
   <si>
-    <t>Sold 451 units of Item_7</t>
+    <t>Sold 12 units of Item_7</t>
   </si>
   <si>
     <t>TC188</t>
@@ -1874,7 +1874,7 @@
     <t>TestCase_WebSales_08: Processing sales entry for Item_8</t>
   </si>
   <si>
-    <t>Sold 422 units of Item_8</t>
+    <t>Sold 400 units of Item_8</t>
   </si>
   <si>
     <t>TC189</t>
@@ -1883,7 +1883,7 @@
     <t>TestCase_WebSales_09: Processing sales entry for Item_9</t>
   </si>
   <si>
-    <t>Sold 73 units of Item_9</t>
+    <t>Sold 341 units of Item_9</t>
   </si>
   <si>
     <t>TC190</t>
@@ -1892,7 +1892,7 @@
     <t>TestCase_WebSales_10: Processing sales entry for Item_0</t>
   </si>
   <si>
-    <t>Sold 143 units of Item_0</t>
+    <t>Sold 55 units of Item_0</t>
   </si>
   <si>
     <t>TC191</t>
@@ -1901,7 +1901,7 @@
     <t>TestCase_WebSales_11: Processing sales entry for Item_1</t>
   </si>
   <si>
-    <t>Sold 230 units of Item_1</t>
+    <t>Sold 238 units of Item_1</t>
   </si>
   <si>
     <t>TC192</t>
@@ -1910,7 +1910,7 @@
     <t>TestCase_WebSales_12: Processing sales entry for Item_2</t>
   </si>
   <si>
-    <t>Sold 364 units of Item_2</t>
+    <t>Sold 318 units of Item_2</t>
   </si>
   <si>
     <t>TC193</t>
@@ -1919,7 +1919,7 @@
     <t>TestCase_WebSales_13: Processing sales entry for Item_3</t>
   </si>
   <si>
-    <t>Sold 344 units of Item_3</t>
+    <t>Sold 27 units of Item_3</t>
   </si>
   <si>
     <t>TC194</t>
@@ -1928,7 +1928,7 @@
     <t>TestCase_WebSales_14: Processing sales entry for Item_4</t>
   </si>
   <si>
-    <t>Sold 477 units of Item_4</t>
+    <t>Sold 420 units of Item_4</t>
   </si>
   <si>
     <t>TC195</t>
@@ -1937,7 +1937,7 @@
     <t>TestCase_WebSales_15: Processing sales entry for Item_5</t>
   </si>
   <si>
-    <t>Sold 482 units of Item_5</t>
+    <t>Sold 419 units of Item_5</t>
   </si>
   <si>
     <t>TC196</t>
@@ -1946,7 +1946,7 @@
     <t>TestCase_WebSales_16: Processing sales entry for Item_6</t>
   </si>
   <si>
-    <t>Sold 354 units of Item_6</t>
+    <t>Sold 431 units of Item_6</t>
   </si>
   <si>
     <t>TC197</t>
@@ -1955,7 +1955,7 @@
     <t>TestCase_WebSales_17: Processing sales entry for Item_7</t>
   </si>
   <si>
-    <t>Sold 348 units of Item_7</t>
+    <t>Sold 26 units of Item_7</t>
   </si>
   <si>
     <t>TC198</t>
@@ -1964,7 +1964,7 @@
     <t>TestCase_WebSales_18: Processing sales entry for Item_8</t>
   </si>
   <si>
-    <t>Sold 216 units of Item_8</t>
+    <t>Sold 112 units of Item_8</t>
   </si>
   <si>
     <t>TC199</t>
@@ -1973,7 +1973,7 @@
     <t>TestCase_WebSales_19: Processing sales entry for Item_9</t>
   </si>
   <si>
-    <t>Sold 167 units of Item_9</t>
+    <t>Sold 399 units of Item_9</t>
   </si>
   <si>
     <t>TC200</t>
@@ -1982,7 +1982,7 @@
     <t>TestCase_WebSales_20: Processing sales entry for Item_0</t>
   </si>
   <si>
-    <t>Sold 112 units of Item_0</t>
+    <t>Sold 50 units of Item_0</t>
   </si>
   <si>
     <t>TC201</t>
@@ -1991,7 +1991,7 @@
     <t>TestCase_WebSales_21: Processing sales entry for Item_1</t>
   </si>
   <si>
-    <t>Sold 373 units of Item_1</t>
+    <t>Sold 99 units of Item_1</t>
   </si>
   <si>
     <t>TC202</t>
@@ -2000,7 +2000,7 @@
     <t>TestCase_WebSales_22: Processing sales entry for Item_2</t>
   </si>
   <si>
-    <t>Sold 216 units of Item_2</t>
+    <t>Sold 409 units of Item_2</t>
   </si>
   <si>
     <t>TC203</t>
@@ -2009,7 +2009,7 @@
     <t>TestCase_WebSales_23: Processing sales entry for Item_3</t>
   </si>
   <si>
-    <t>Sold 36 units of Item_3</t>
+    <t>Sold 256 units of Item_3</t>
   </si>
   <si>
     <t>TC204</t>
@@ -2018,7 +2018,7 @@
     <t>TestCase_WebSales_24: Processing sales entry for Item_4</t>
   </si>
   <si>
-    <t>Sold 320 units of Item_4</t>
+    <t>Sold 170 units of Item_4</t>
   </si>
   <si>
     <t>TC205</t>
@@ -2027,7 +2027,7 @@
     <t>TestCase_WebSales_25: Processing sales entry for Item_5</t>
   </si>
   <si>
-    <t>Sold 408 units of Item_5</t>
+    <t>Sold 137 units of Item_5</t>
   </si>
   <si>
     <t>TC206</t>
@@ -2036,7 +2036,7 @@
     <t>TestCase_WebSales_26: Processing sales entry for Item_6</t>
   </si>
   <si>
-    <t>Sold 417 units of Item_6</t>
+    <t>Sold 321 units of Item_6</t>
   </si>
   <si>
     <t>TC207</t>
@@ -2045,7 +2045,7 @@
     <t>TestCase_WebSales_27: Processing sales entry for Item_7</t>
   </si>
   <si>
-    <t>Sold 332 units of Item_7</t>
+    <t>Sold 134 units of Item_7</t>
   </si>
   <si>
     <t>TC208</t>
@@ -2054,7 +2054,7 @@
     <t>TestCase_WebSales_28: Processing sales entry for Item_8</t>
   </si>
   <si>
-    <t>Sold 182 units of Item_8</t>
+    <t>Sold 381 units of Item_8</t>
   </si>
   <si>
     <t>TC209</t>
@@ -2063,7 +2063,7 @@
     <t>TestCase_WebSales_29: Processing sales entry for Item_9</t>
   </si>
   <si>
-    <t>Sold 100 units of Item_9</t>
+    <t>Sold 261 units of Item_9</t>
   </si>
   <si>
     <t>TC210</t>
@@ -2072,7 +2072,7 @@
     <t>TestCase_WebSales_30: Processing sales entry for Item_0</t>
   </si>
   <si>
-    <t>Sold 301 units of Item_0</t>
+    <t>Sold 448 units of Item_0</t>
   </si>
   <si>
     <t>TC211</t>
@@ -2081,7 +2081,7 @@
     <t>TestCase_WebSales_31: Processing sales entry for Item_1</t>
   </si>
   <si>
-    <t>Sold 150 units of Item_1</t>
+    <t>Sold 440 units of Item_1</t>
   </si>
   <si>
     <t>TC212</t>
@@ -2090,7 +2090,7 @@
     <t>TestCase_WebSales_32: Processing sales entry for Item_2</t>
   </si>
   <si>
-    <t>Sold 141 units of Item_2</t>
+    <t>Sold 239 units of Item_2</t>
   </si>
   <si>
     <t>TC213</t>
@@ -2099,7 +2099,7 @@
     <t>TestCase_WebSales_33: Processing sales entry for Item_3</t>
   </si>
   <si>
-    <t>Sold 318 units of Item_3</t>
+    <t>Sold 375 units of Item_3</t>
   </si>
   <si>
     <t>TC214</t>
@@ -2108,7 +2108,7 @@
     <t>TestCase_WebSales_34: Processing sales entry for Item_4</t>
   </si>
   <si>
-    <t>Sold 44 units of Item_4</t>
+    <t>Sold 152 units of Item_4</t>
   </si>
   <si>
     <t>TC215</t>
@@ -2117,7 +2117,7 @@
     <t>TestCase_WebSales_35: Processing sales entry for Item_5</t>
   </si>
   <si>
-    <t>Sold 412 units of Item_5</t>
+    <t>Sold 70 units of Item_5</t>
   </si>
   <si>
     <t>TC216</t>
@@ -2126,7 +2126,7 @@
     <t>TestCase_WebSales_36: Processing sales entry for Item_6</t>
   </si>
   <si>
-    <t>Sold 350 units of Item_6</t>
+    <t>Sold 311 units of Item_6</t>
   </si>
   <si>
     <t>TC217</t>
@@ -2135,7 +2135,7 @@
     <t>TestCase_WebSales_37: Processing sales entry for Item_7</t>
   </si>
   <si>
-    <t>Sold 251 units of Item_7</t>
+    <t>Sold 238 units of Item_7</t>
   </si>
   <si>
     <t>TC218</t>
@@ -2144,7 +2144,7 @@
     <t>TestCase_WebSales_38: Processing sales entry for Item_8</t>
   </si>
   <si>
-    <t>Sold 196 units of Item_8</t>
+    <t>Sold 208 units of Item_8</t>
   </si>
   <si>
     <t>TC219</t>
@@ -2153,7 +2153,7 @@
     <t>TestCase_WebSales_39: Processing sales entry for Item_9</t>
   </si>
   <si>
-    <t>Sold 0 units of Item_9</t>
+    <t>Sold 211 units of Item_9</t>
   </si>
   <si>
     <t>TC220</t>
@@ -2162,7 +2162,7 @@
     <t>TestCase_WebSales_40: Processing sales entry for Item_0</t>
   </si>
   <si>
-    <t>Sold 332 units of Item_0</t>
+    <t>Sold 394 units of Item_0</t>
   </si>
   <si>
     <t>TC221</t>
@@ -2171,7 +2171,7 @@
     <t>TestCase_WebSales_41: Processing sales entry for Item_1</t>
   </si>
   <si>
-    <t>Sold 261 units of Item_1</t>
+    <t>Sold 83 units of Item_1</t>
   </si>
   <si>
     <t>TC222</t>
@@ -2180,13 +2180,16 @@
     <t>TestCase_WebSales_42: Processing sales entry for Item_2</t>
   </si>
   <si>
+    <t>Sold 66 units of Item_2</t>
+  </si>
+  <si>
     <t>TC223</t>
   </si>
   <si>
     <t>TestCase_WebSales_43: Processing sales entry for Item_3</t>
   </si>
   <si>
-    <t>Sold 31 units of Item_3</t>
+    <t>Sold 380 units of Item_3</t>
   </si>
   <si>
     <t>TC224</t>
@@ -2195,7 +2198,7 @@
     <t>TestCase_WebSales_44: Processing sales entry for Item_4</t>
   </si>
   <si>
-    <t>Sold 324 units of Item_4</t>
+    <t>Sold 169 units of Item_4</t>
   </si>
   <si>
     <t>TC225</t>
@@ -2204,7 +2207,7 @@
     <t>TestCase_WebSales_45: Processing sales entry for Item_5</t>
   </si>
   <si>
-    <t>Sold 20 units of Item_5</t>
+    <t>Sold 35 units of Item_5</t>
   </si>
   <si>
     <t>TC226</t>
@@ -2213,7 +2216,7 @@
     <t>TestCase_WebSales_46: Processing sales entry for Item_6</t>
   </si>
   <si>
-    <t>Sold 373 units of Item_6</t>
+    <t>Sold 196 units of Item_6</t>
   </si>
   <si>
     <t>TC227</t>
@@ -2222,7 +2225,7 @@
     <t>TestCase_WebSales_47: Processing sales entry for Item_7</t>
   </si>
   <si>
-    <t>Sold 408 units of Item_7</t>
+    <t>Sold 283 units of Item_7</t>
   </si>
   <si>
     <t>TC228</t>
@@ -2231,7 +2234,7 @@
     <t>TestCase_WebSales_48: Processing sales entry for Item_8</t>
   </si>
   <si>
-    <t>Sold 370 units of Item_8</t>
+    <t>Sold 161 units of Item_8</t>
   </si>
   <si>
     <t>TC229</t>
@@ -2240,7 +2243,7 @@
     <t>TestCase_WebSales_49: Processing sales entry for Item_9</t>
   </si>
   <si>
-    <t>Sold 436 units of Item_9</t>
+    <t>Sold 219 units of Item_9</t>
   </si>
   <si>
     <t>TC230</t>
@@ -2249,7 +2252,7 @@
     <t>TestCase_WebSales_50: Processing sales entry for Item_0</t>
   </si>
   <si>
-    <t>Sold 480 units of Item_0</t>
+    <t>Sold 397 units of Item_0</t>
   </si>
   <si>
     <t>TC231</t>
@@ -4105,7 +4108,7 @@
         <v>9</v>
       </c>
       <c r="H2" s="11">
-        <v>78</v>
+        <v>19</v>
       </c>
       <c r="I2" s="11" t="s">
         <v>1</v>
@@ -4134,7 +4137,7 @@
         <v>9</v>
       </c>
       <c r="H3" s="13">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="I3" s="13" t="s">
         <v>1</v>
@@ -4163,7 +4166,7 @@
         <v>9</v>
       </c>
       <c r="H4" s="11">
-        <v>81</v>
+        <v>67</v>
       </c>
       <c r="I4" s="11" t="s">
         <v>1</v>
@@ -4192,7 +4195,7 @@
         <v>9</v>
       </c>
       <c r="H5" s="13">
-        <v>71</v>
+        <v>89</v>
       </c>
       <c r="I5" s="13" t="s">
         <v>1</v>
@@ -4221,7 +4224,7 @@
         <v>9</v>
       </c>
       <c r="H6" s="11">
-        <v>22</v>
+        <v>76</v>
       </c>
       <c r="I6" s="11" t="s">
         <v>1</v>
@@ -4250,7 +4253,7 @@
         <v>9</v>
       </c>
       <c r="H7" s="13">
-        <v>36</v>
+        <v>74</v>
       </c>
       <c r="I7" s="13" t="s">
         <v>1</v>
@@ -4279,7 +4282,7 @@
         <v>9</v>
       </c>
       <c r="H8" s="11">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="I8" s="11" t="s">
         <v>1</v>
@@ -4308,7 +4311,7 @@
         <v>9</v>
       </c>
       <c r="H9" s="13">
-        <v>70</v>
+        <v>88</v>
       </c>
       <c r="I9" s="13" t="s">
         <v>1</v>
@@ -4337,7 +4340,7 @@
         <v>9</v>
       </c>
       <c r="H10" s="11">
-        <v>87</v>
+        <v>40</v>
       </c>
       <c r="I10" s="11" t="s">
         <v>1</v>
@@ -4366,7 +4369,7 @@
         <v>9</v>
       </c>
       <c r="H11" s="13">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="I11" s="13" t="s">
         <v>1</v>
@@ -4395,7 +4398,7 @@
         <v>9</v>
       </c>
       <c r="H12" s="11">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="I12" s="11" t="s">
         <v>1</v>
@@ -4424,7 +4427,7 @@
         <v>9</v>
       </c>
       <c r="H13" s="13">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="I13" s="13" t="s">
         <v>1</v>
@@ -4453,7 +4456,7 @@
         <v>9</v>
       </c>
       <c r="H14" s="11">
-        <v>78</v>
+        <v>35</v>
       </c>
       <c r="I14" s="11" t="s">
         <v>1</v>
@@ -4482,7 +4485,7 @@
         <v>9</v>
       </c>
       <c r="H15" s="13">
-        <v>16</v>
+        <v>68</v>
       </c>
       <c r="I15" s="13" t="s">
         <v>1</v>
@@ -4511,7 +4514,7 @@
         <v>9</v>
       </c>
       <c r="H16" s="11">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="I16" s="11" t="s">
         <v>1</v>
@@ -4540,7 +4543,7 @@
         <v>9</v>
       </c>
       <c r="H17" s="13">
-        <v>29</v>
+        <v>62</v>
       </c>
       <c r="I17" s="13" t="s">
         <v>1</v>
@@ -4569,7 +4572,7 @@
         <v>9</v>
       </c>
       <c r="H18" s="11">
-        <v>72</v>
+        <v>25</v>
       </c>
       <c r="I18" s="11" t="s">
         <v>1</v>
@@ -4598,7 +4601,7 @@
         <v>9</v>
       </c>
       <c r="H19" s="13">
-        <v>88</v>
+        <v>43</v>
       </c>
       <c r="I19" s="13" t="s">
         <v>1</v>
@@ -4627,7 +4630,7 @@
         <v>9</v>
       </c>
       <c r="H20" s="11">
-        <v>69</v>
+        <v>44</v>
       </c>
       <c r="I20" s="11" t="s">
         <v>1</v>
@@ -4656,7 +4659,7 @@
         <v>9</v>
       </c>
       <c r="H21" s="13">
-        <v>67</v>
+        <v>41</v>
       </c>
       <c r="I21" s="13" t="s">
         <v>1</v>
@@ -4685,7 +4688,7 @@
         <v>9</v>
       </c>
       <c r="H22" s="11">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="I22" s="11" t="s">
         <v>1</v>
@@ -4714,7 +4717,7 @@
         <v>9</v>
       </c>
       <c r="H23" s="13">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="I23" s="13" t="s">
         <v>1</v>
@@ -4743,7 +4746,7 @@
         <v>9</v>
       </c>
       <c r="H24" s="11">
-        <v>42</v>
+        <v>12</v>
       </c>
       <c r="I24" s="11" t="s">
         <v>1</v>
@@ -4772,7 +4775,7 @@
         <v>9</v>
       </c>
       <c r="H25" s="13">
-        <v>79</v>
+        <v>44</v>
       </c>
       <c r="I25" s="13" t="s">
         <v>1</v>
@@ -4801,7 +4804,7 @@
         <v>9</v>
       </c>
       <c r="H26" s="11">
-        <v>83</v>
+        <v>11</v>
       </c>
       <c r="I26" s="11" t="s">
         <v>1</v>
@@ -4830,7 +4833,7 @@
         <v>9</v>
       </c>
       <c r="H27" s="13">
-        <v>40</v>
+        <v>88</v>
       </c>
       <c r="I27" s="13" t="s">
         <v>1</v>
@@ -4859,7 +4862,7 @@
         <v>9</v>
       </c>
       <c r="H28" s="11">
-        <v>48</v>
+        <v>82</v>
       </c>
       <c r="I28" s="11" t="s">
         <v>1</v>
@@ -4888,7 +4891,7 @@
         <v>9</v>
       </c>
       <c r="H29" s="13">
-        <v>63</v>
+        <v>14</v>
       </c>
       <c r="I29" s="13" t="s">
         <v>1</v>
@@ -4917,7 +4920,7 @@
         <v>9</v>
       </c>
       <c r="H30" s="11">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="I30" s="11" t="s">
         <v>1</v>
@@ -4946,7 +4949,7 @@
         <v>9</v>
       </c>
       <c r="H31" s="13">
-        <v>62</v>
+        <v>34</v>
       </c>
       <c r="I31" s="13" t="s">
         <v>1</v>
@@ -4975,7 +4978,7 @@
         <v>9</v>
       </c>
       <c r="H32" s="11">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="I32" s="11" t="s">
         <v>1</v>
@@ -5004,7 +5007,7 @@
         <v>9</v>
       </c>
       <c r="H33" s="13">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I33" s="13" t="s">
         <v>1</v>
@@ -5033,7 +5036,7 @@
         <v>9</v>
       </c>
       <c r="H34" s="11">
-        <v>74</v>
+        <v>47</v>
       </c>
       <c r="I34" s="11" t="s">
         <v>1</v>
@@ -5062,7 +5065,7 @@
         <v>9</v>
       </c>
       <c r="H35" s="13">
-        <v>21</v>
+        <v>60</v>
       </c>
       <c r="I35" s="13" t="s">
         <v>1</v>
@@ -5091,7 +5094,7 @@
         <v>9</v>
       </c>
       <c r="H36" s="11">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="I36" s="11" t="s">
         <v>1</v>
@@ -5120,7 +5123,7 @@
         <v>9</v>
       </c>
       <c r="H37" s="13">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="I37" s="13" t="s">
         <v>1</v>
@@ -5149,7 +5152,7 @@
         <v>9</v>
       </c>
       <c r="H38" s="11">
-        <v>63</v>
+        <v>23</v>
       </c>
       <c r="I38" s="11" t="s">
         <v>1</v>
@@ -5178,7 +5181,7 @@
         <v>9</v>
       </c>
       <c r="H39" s="13">
-        <v>51</v>
+        <v>13</v>
       </c>
       <c r="I39" s="13" t="s">
         <v>1</v>
@@ -5207,7 +5210,7 @@
         <v>9</v>
       </c>
       <c r="H40" s="11">
-        <v>87</v>
+        <v>47</v>
       </c>
       <c r="I40" s="11" t="s">
         <v>1</v>
@@ -5236,7 +5239,7 @@
         <v>9</v>
       </c>
       <c r="H41" s="13">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="I41" s="13" t="s">
         <v>1</v>
@@ -5265,7 +5268,7 @@
         <v>9</v>
       </c>
       <c r="H42" s="11">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="I42" s="11" t="s">
         <v>1</v>
@@ -5294,7 +5297,7 @@
         <v>9</v>
       </c>
       <c r="H43" s="13">
-        <v>78</v>
+        <v>54</v>
       </c>
       <c r="I43" s="13" t="s">
         <v>1</v>
@@ -5323,7 +5326,7 @@
         <v>9</v>
       </c>
       <c r="H44" s="11">
-        <v>50</v>
+        <v>69</v>
       </c>
       <c r="I44" s="11" t="s">
         <v>1</v>
@@ -5352,7 +5355,7 @@
         <v>9</v>
       </c>
       <c r="H45" s="13">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="I45" s="13" t="s">
         <v>1</v>
@@ -5381,7 +5384,7 @@
         <v>9</v>
       </c>
       <c r="H46" s="11">
-        <v>88</v>
+        <v>16</v>
       </c>
       <c r="I46" s="11" t="s">
         <v>1</v>
@@ -5410,7 +5413,7 @@
         <v>9</v>
       </c>
       <c r="H47" s="13">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="I47" s="13" t="s">
         <v>1</v>
@@ -5439,7 +5442,7 @@
         <v>9</v>
       </c>
       <c r="H48" s="11">
-        <v>73</v>
+        <v>24</v>
       </c>
       <c r="I48" s="11" t="s">
         <v>1</v>
@@ -5468,7 +5471,7 @@
         <v>9</v>
       </c>
       <c r="H49" s="13">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="I49" s="13" t="s">
         <v>1</v>
@@ -5497,7 +5500,7 @@
         <v>9</v>
       </c>
       <c r="H50" s="11">
-        <v>77</v>
+        <v>12</v>
       </c>
       <c r="I50" s="11" t="s">
         <v>1</v>
@@ -5526,7 +5529,7 @@
         <v>9</v>
       </c>
       <c r="H51" s="13">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="I51" s="13" t="s">
         <v>1</v>
@@ -5555,7 +5558,7 @@
         <v>9</v>
       </c>
       <c r="H52" s="11">
-        <v>60</v>
+        <v>34</v>
       </c>
       <c r="I52" s="11" t="s">
         <v>1</v>
@@ -5584,7 +5587,7 @@
         <v>9</v>
       </c>
       <c r="H53" s="13">
-        <v>25</v>
+        <v>71</v>
       </c>
       <c r="I53" s="13" t="s">
         <v>1</v>
@@ -5613,7 +5616,7 @@
         <v>9</v>
       </c>
       <c r="H54" s="11">
-        <v>48</v>
+        <v>87</v>
       </c>
       <c r="I54" s="11" t="s">
         <v>1</v>
@@ -5642,7 +5645,7 @@
         <v>9</v>
       </c>
       <c r="H55" s="13">
-        <v>10</v>
+        <v>72</v>
       </c>
       <c r="I55" s="13" t="s">
         <v>1</v>
@@ -5671,7 +5674,7 @@
         <v>9</v>
       </c>
       <c r="H56" s="11">
-        <v>28</v>
+        <v>59</v>
       </c>
       <c r="I56" s="11" t="s">
         <v>1</v>
@@ -5700,7 +5703,7 @@
         <v>9</v>
       </c>
       <c r="H57" s="13">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="I57" s="13" t="s">
         <v>1</v>
@@ -5729,7 +5732,7 @@
         <v>9</v>
       </c>
       <c r="H58" s="11">
-        <v>18</v>
+        <v>57</v>
       </c>
       <c r="I58" s="11" t="s">
         <v>1</v>
@@ -5758,7 +5761,7 @@
         <v>9</v>
       </c>
       <c r="H59" s="13">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="I59" s="13" t="s">
         <v>1</v>
@@ -5787,7 +5790,7 @@
         <v>9</v>
       </c>
       <c r="H60" s="11">
-        <v>78</v>
+        <v>57</v>
       </c>
       <c r="I60" s="11" t="s">
         <v>1</v>
@@ -5816,7 +5819,7 @@
         <v>9</v>
       </c>
       <c r="H61" s="13">
-        <v>60</v>
+        <v>86</v>
       </c>
       <c r="I61" s="13" t="s">
         <v>1</v>
@@ -5845,7 +5848,7 @@
         <v>9</v>
       </c>
       <c r="H62" s="11">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="I62" s="11" t="s">
         <v>1</v>
@@ -5874,7 +5877,7 @@
         <v>9</v>
       </c>
       <c r="H63" s="13">
-        <v>14</v>
+        <v>47</v>
       </c>
       <c r="I63" s="13" t="s">
         <v>1</v>
@@ -5903,7 +5906,7 @@
         <v>9</v>
       </c>
       <c r="H64" s="11">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="I64" s="11" t="s">
         <v>1</v>
@@ -5932,7 +5935,7 @@
         <v>9</v>
       </c>
       <c r="H65" s="13">
-        <v>36</v>
+        <v>15</v>
       </c>
       <c r="I65" s="13" t="s">
         <v>1</v>
@@ -5961,7 +5964,7 @@
         <v>9</v>
       </c>
       <c r="H66" s="11">
-        <v>58</v>
+        <v>25</v>
       </c>
       <c r="I66" s="11" t="s">
         <v>1</v>
@@ -5990,7 +5993,7 @@
         <v>9</v>
       </c>
       <c r="H67" s="13">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="I67" s="13" t="s">
         <v>1</v>
@@ -6019,7 +6022,7 @@
         <v>9</v>
       </c>
       <c r="H68" s="11">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="I68" s="11" t="s">
         <v>1</v>
@@ -6048,7 +6051,7 @@
         <v>9</v>
       </c>
       <c r="H69" s="13">
-        <v>17</v>
+        <v>56</v>
       </c>
       <c r="I69" s="13" t="s">
         <v>1</v>
@@ -6077,7 +6080,7 @@
         <v>9</v>
       </c>
       <c r="H70" s="11">
-        <v>30</v>
+        <v>79</v>
       </c>
       <c r="I70" s="11" t="s">
         <v>1</v>
@@ -6106,7 +6109,7 @@
         <v>9</v>
       </c>
       <c r="H71" s="13">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="I71" s="13" t="s">
         <v>1</v>
@@ -6164,7 +6167,7 @@
         <v>9</v>
       </c>
       <c r="H73" s="13">
-        <v>62</v>
+        <v>80</v>
       </c>
       <c r="I73" s="13" t="s">
         <v>1</v>
@@ -6193,7 +6196,7 @@
         <v>9</v>
       </c>
       <c r="H74" s="11">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="I74" s="11" t="s">
         <v>1</v>
@@ -6222,7 +6225,7 @@
         <v>9</v>
       </c>
       <c r="H75" s="13">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="I75" s="13" t="s">
         <v>1</v>
@@ -6251,7 +6254,7 @@
         <v>9</v>
       </c>
       <c r="H76" s="11">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="I76" s="11" t="s">
         <v>1</v>
@@ -6280,7 +6283,7 @@
         <v>9</v>
       </c>
       <c r="H77" s="13">
-        <v>87</v>
+        <v>69</v>
       </c>
       <c r="I77" s="13" t="s">
         <v>1</v>
@@ -6309,7 +6312,7 @@
         <v>9</v>
       </c>
       <c r="H78" s="11">
-        <v>14</v>
+        <v>46</v>
       </c>
       <c r="I78" s="11" t="s">
         <v>1</v>
@@ -6338,7 +6341,7 @@
         <v>9</v>
       </c>
       <c r="H79" s="13">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="I79" s="13" t="s">
         <v>1</v>
@@ -6367,7 +6370,7 @@
         <v>9</v>
       </c>
       <c r="H80" s="11">
-        <v>65</v>
+        <v>26</v>
       </c>
       <c r="I80" s="11" t="s">
         <v>1</v>
@@ -6396,7 +6399,7 @@
         <v>9</v>
       </c>
       <c r="H81" s="13">
-        <v>54</v>
+        <v>80</v>
       </c>
       <c r="I81" s="13" t="s">
         <v>1</v>
@@ -6425,7 +6428,7 @@
         <v>9</v>
       </c>
       <c r="H82" s="11">
-        <v>77</v>
+        <v>59</v>
       </c>
       <c r="I82" s="11" t="s">
         <v>1</v>
@@ -6454,7 +6457,7 @@
         <v>9</v>
       </c>
       <c r="H83" s="13">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="I83" s="13" t="s">
         <v>1</v>
@@ -6483,7 +6486,7 @@
         <v>9</v>
       </c>
       <c r="H84" s="11">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="I84" s="11" t="s">
         <v>1</v>
@@ -6512,7 +6515,7 @@
         <v>9</v>
       </c>
       <c r="H85" s="13">
-        <v>10</v>
+        <v>73</v>
       </c>
       <c r="I85" s="13" t="s">
         <v>1</v>
@@ -6541,7 +6544,7 @@
         <v>9</v>
       </c>
       <c r="H86" s="11">
-        <v>31</v>
+        <v>58</v>
       </c>
       <c r="I86" s="11" t="s">
         <v>1</v>
@@ -6570,7 +6573,7 @@
         <v>9</v>
       </c>
       <c r="H87" s="13">
-        <v>44</v>
+        <v>72</v>
       </c>
       <c r="I87" s="13" t="s">
         <v>1</v>
@@ -6599,7 +6602,7 @@
         <v>9</v>
       </c>
       <c r="H88" s="11">
-        <v>26</v>
+        <v>41</v>
       </c>
       <c r="I88" s="11" t="s">
         <v>1</v>
@@ -6628,7 +6631,7 @@
         <v>9</v>
       </c>
       <c r="H89" s="13">
-        <v>53</v>
+        <v>27</v>
       </c>
       <c r="I89" s="13" t="s">
         <v>1</v>
@@ -6657,7 +6660,7 @@
         <v>9</v>
       </c>
       <c r="H90" s="11">
-        <v>46</v>
+        <v>14</v>
       </c>
       <c r="I90" s="11" t="s">
         <v>1</v>
@@ -6686,7 +6689,7 @@
         <v>9</v>
       </c>
       <c r="H91" s="13">
-        <v>29</v>
+        <v>64</v>
       </c>
       <c r="I91" s="13" t="s">
         <v>1</v>
@@ -6715,7 +6718,7 @@
         <v>9</v>
       </c>
       <c r="H92" s="11">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="I92" s="11" t="s">
         <v>1</v>
@@ -6744,7 +6747,7 @@
         <v>9</v>
       </c>
       <c r="H93" s="13">
-        <v>83</v>
+        <v>49</v>
       </c>
       <c r="I93" s="13" t="s">
         <v>1</v>
@@ -6773,7 +6776,7 @@
         <v>9</v>
       </c>
       <c r="H94" s="11">
-        <v>10</v>
+        <v>80</v>
       </c>
       <c r="I94" s="11" t="s">
         <v>1</v>
@@ -6802,7 +6805,7 @@
         <v>9</v>
       </c>
       <c r="H95" s="13">
-        <v>13</v>
+        <v>81</v>
       </c>
       <c r="I95" s="13" t="s">
         <v>1</v>
@@ -6831,7 +6834,7 @@
         <v>9</v>
       </c>
       <c r="H96" s="11">
-        <v>12</v>
+        <v>37</v>
       </c>
       <c r="I96" s="11" t="s">
         <v>1</v>
@@ -6860,7 +6863,7 @@
         <v>9</v>
       </c>
       <c r="H97" s="13">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I97" s="13" t="s">
         <v>1</v>
@@ -6889,7 +6892,7 @@
         <v>9</v>
       </c>
       <c r="H98" s="11">
-        <v>67</v>
+        <v>32</v>
       </c>
       <c r="I98" s="11" t="s">
         <v>1</v>
@@ -6918,7 +6921,7 @@
         <v>9</v>
       </c>
       <c r="H99" s="13">
-        <v>89</v>
+        <v>40</v>
       </c>
       <c r="I99" s="13" t="s">
         <v>1</v>
@@ -6947,7 +6950,7 @@
         <v>9</v>
       </c>
       <c r="H100" s="11">
-        <v>47</v>
+        <v>24</v>
       </c>
       <c r="I100" s="11" t="s">
         <v>1</v>
@@ -6976,7 +6979,7 @@
         <v>9</v>
       </c>
       <c r="H101" s="13">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="I101" s="13" t="s">
         <v>1</v>
@@ -7005,7 +7008,7 @@
         <v>9</v>
       </c>
       <c r="H102" s="11">
-        <v>17</v>
+        <v>65</v>
       </c>
       <c r="I102" s="11" t="s">
         <v>1</v>
@@ -7034,7 +7037,7 @@
         <v>9</v>
       </c>
       <c r="H103" s="13">
-        <v>42</v>
+        <v>88</v>
       </c>
       <c r="I103" s="13" t="s">
         <v>1</v>
@@ -7063,7 +7066,7 @@
         <v>9</v>
       </c>
       <c r="H104" s="11">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="I104" s="11" t="s">
         <v>1</v>
@@ -7092,7 +7095,7 @@
         <v>9</v>
       </c>
       <c r="H105" s="13">
-        <v>29</v>
+        <v>86</v>
       </c>
       <c r="I105" s="13" t="s">
         <v>1</v>
@@ -7121,7 +7124,7 @@
         <v>9</v>
       </c>
       <c r="H106" s="11">
-        <v>27</v>
+        <v>67</v>
       </c>
       <c r="I106" s="11" t="s">
         <v>1</v>
@@ -7150,7 +7153,7 @@
         <v>9</v>
       </c>
       <c r="H107" s="13">
-        <v>38</v>
+        <v>88</v>
       </c>
       <c r="I107" s="13" t="s">
         <v>1</v>
@@ -7179,7 +7182,7 @@
         <v>9</v>
       </c>
       <c r="H108" s="11">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="I108" s="11" t="s">
         <v>1</v>
@@ -7208,7 +7211,7 @@
         <v>9</v>
       </c>
       <c r="H109" s="13">
-        <v>83</v>
+        <v>52</v>
       </c>
       <c r="I109" s="13" t="s">
         <v>1</v>
@@ -7237,7 +7240,7 @@
         <v>9</v>
       </c>
       <c r="H110" s="11">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="I110" s="11" t="s">
         <v>1</v>
@@ -7266,7 +7269,7 @@
         <v>9</v>
       </c>
       <c r="H111" s="13">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="I111" s="13" t="s">
         <v>1</v>
@@ -7295,7 +7298,7 @@
         <v>9</v>
       </c>
       <c r="H112" s="11">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="I112" s="11" t="s">
         <v>1</v>
@@ -7324,7 +7327,7 @@
         <v>9</v>
       </c>
       <c r="H113" s="13">
-        <v>16</v>
+        <v>55</v>
       </c>
       <c r="I113" s="13" t="s">
         <v>1</v>
@@ -7353,7 +7356,7 @@
         <v>9</v>
       </c>
       <c r="H114" s="11">
-        <v>31</v>
+        <v>61</v>
       </c>
       <c r="I114" s="11" t="s">
         <v>1</v>
@@ -7382,7 +7385,7 @@
         <v>9</v>
       </c>
       <c r="H115" s="13">
-        <v>81</v>
+        <v>15</v>
       </c>
       <c r="I115" s="13" t="s">
         <v>1</v>
@@ -7411,7 +7414,7 @@
         <v>9</v>
       </c>
       <c r="H116" s="11">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="I116" s="11" t="s">
         <v>1</v>
@@ -7440,7 +7443,7 @@
         <v>9</v>
       </c>
       <c r="H117" s="13">
-        <v>89</v>
+        <v>27</v>
       </c>
       <c r="I117" s="13" t="s">
         <v>1</v>
@@ -7469,7 +7472,7 @@
         <v>9</v>
       </c>
       <c r="H118" s="11">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="I118" s="11" t="s">
         <v>1</v>
@@ -7498,7 +7501,7 @@
         <v>9</v>
       </c>
       <c r="H119" s="13">
-        <v>81</v>
+        <v>28</v>
       </c>
       <c r="I119" s="13" t="s">
         <v>1</v>
@@ -7527,7 +7530,7 @@
         <v>9</v>
       </c>
       <c r="H120" s="11">
-        <v>76</v>
+        <v>59</v>
       </c>
       <c r="I120" s="11" t="s">
         <v>1</v>
@@ -7556,7 +7559,7 @@
         <v>9</v>
       </c>
       <c r="H121" s="13">
-        <v>59</v>
+        <v>19</v>
       </c>
       <c r="I121" s="13" t="s">
         <v>1</v>
@@ -7585,7 +7588,7 @@
         <v>9</v>
       </c>
       <c r="H122" s="11">
-        <v>28</v>
+        <v>83</v>
       </c>
       <c r="I122" s="11" t="s">
         <v>1</v>
@@ -7614,7 +7617,7 @@
         <v>9</v>
       </c>
       <c r="H123" s="13">
-        <v>79</v>
+        <v>29</v>
       </c>
       <c r="I123" s="13" t="s">
         <v>1</v>
@@ -7643,7 +7646,7 @@
         <v>9</v>
       </c>
       <c r="H124" s="11">
-        <v>67</v>
+        <v>53</v>
       </c>
       <c r="I124" s="11" t="s">
         <v>1</v>
@@ -7672,7 +7675,7 @@
         <v>9</v>
       </c>
       <c r="H125" s="13">
-        <v>38</v>
+        <v>65</v>
       </c>
       <c r="I125" s="13" t="s">
         <v>1</v>
@@ -7701,7 +7704,7 @@
         <v>9</v>
       </c>
       <c r="H126" s="11">
-        <v>15</v>
+        <v>82</v>
       </c>
       <c r="I126" s="11" t="s">
         <v>1</v>
@@ -7730,7 +7733,7 @@
         <v>9</v>
       </c>
       <c r="H127" s="13">
-        <v>28</v>
+        <v>59</v>
       </c>
       <c r="I127" s="13" t="s">
         <v>1</v>
@@ -7759,7 +7762,7 @@
         <v>9</v>
       </c>
       <c r="H128" s="11">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="I128" s="11" t="s">
         <v>1</v>
@@ -7788,7 +7791,7 @@
         <v>9</v>
       </c>
       <c r="H129" s="13">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="I129" s="13" t="s">
         <v>1</v>
@@ -7817,7 +7820,7 @@
         <v>9</v>
       </c>
       <c r="H130" s="11">
-        <v>67</v>
+        <v>18</v>
       </c>
       <c r="I130" s="11" t="s">
         <v>1</v>
@@ -7846,7 +7849,7 @@
         <v>9</v>
       </c>
       <c r="H131" s="13">
-        <v>77</v>
+        <v>17</v>
       </c>
       <c r="I131" s="13" t="s">
         <v>1</v>
@@ -7875,7 +7878,7 @@
         <v>9</v>
       </c>
       <c r="H132" s="11">
-        <v>64</v>
+        <v>42</v>
       </c>
       <c r="I132" s="11" t="s">
         <v>1</v>
@@ -7904,7 +7907,7 @@
         <v>9</v>
       </c>
       <c r="H133" s="13">
-        <v>17</v>
+        <v>83</v>
       </c>
       <c r="I133" s="13" t="s">
         <v>1</v>
@@ -7933,7 +7936,7 @@
         <v>9</v>
       </c>
       <c r="H134" s="11">
-        <v>58</v>
+        <v>80</v>
       </c>
       <c r="I134" s="11" t="s">
         <v>1</v>
@@ -7962,7 +7965,7 @@
         <v>9</v>
       </c>
       <c r="H135" s="13">
-        <v>61</v>
+        <v>24</v>
       </c>
       <c r="I135" s="13" t="s">
         <v>1</v>
@@ -7991,7 +7994,7 @@
         <v>9</v>
       </c>
       <c r="H136" s="11">
-        <v>51</v>
+        <v>10</v>
       </c>
       <c r="I136" s="11" t="s">
         <v>1</v>
@@ -8020,7 +8023,7 @@
         <v>9</v>
       </c>
       <c r="H137" s="13">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="I137" s="13" t="s">
         <v>1</v>
@@ -8049,7 +8052,7 @@
         <v>9</v>
       </c>
       <c r="H138" s="11">
-        <v>32</v>
+        <v>53</v>
       </c>
       <c r="I138" s="11" t="s">
         <v>1</v>
@@ -8078,7 +8081,7 @@
         <v>9</v>
       </c>
       <c r="H139" s="13">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="I139" s="13" t="s">
         <v>1</v>
@@ -8107,7 +8110,7 @@
         <v>9</v>
       </c>
       <c r="H140" s="11">
-        <v>59</v>
+        <v>31</v>
       </c>
       <c r="I140" s="11" t="s">
         <v>1</v>
@@ -8136,7 +8139,7 @@
         <v>9</v>
       </c>
       <c r="H141" s="13">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="I141" s="13" t="s">
         <v>1</v>
@@ -8165,7 +8168,7 @@
         <v>9</v>
       </c>
       <c r="H142" s="11">
-        <v>58</v>
+        <v>36</v>
       </c>
       <c r="I142" s="11" t="s">
         <v>1</v>
@@ -8194,7 +8197,7 @@
         <v>9</v>
       </c>
       <c r="H143" s="13">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="I143" s="13" t="s">
         <v>1</v>
@@ -8223,7 +8226,7 @@
         <v>9</v>
       </c>
       <c r="H144" s="11">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I144" s="11" t="s">
         <v>1</v>
@@ -8252,7 +8255,7 @@
         <v>9</v>
       </c>
       <c r="H145" s="13">
-        <v>45</v>
+        <v>66</v>
       </c>
       <c r="I145" s="13" t="s">
         <v>1</v>
@@ -8281,7 +8284,7 @@
         <v>9</v>
       </c>
       <c r="H146" s="11">
-        <v>32</v>
+        <v>53</v>
       </c>
       <c r="I146" s="11" t="s">
         <v>1</v>
@@ -8310,7 +8313,7 @@
         <v>9</v>
       </c>
       <c r="H147" s="13">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="I147" s="13" t="s">
         <v>1</v>
@@ -8339,7 +8342,7 @@
         <v>9</v>
       </c>
       <c r="H148" s="11">
-        <v>75</v>
+        <v>10</v>
       </c>
       <c r="I148" s="11" t="s">
         <v>1</v>
@@ -8368,7 +8371,7 @@
         <v>9</v>
       </c>
       <c r="H149" s="13">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="I149" s="13" t="s">
         <v>1</v>
@@ -8397,7 +8400,7 @@
         <v>9</v>
       </c>
       <c r="H150" s="11">
-        <v>78</v>
+        <v>64</v>
       </c>
       <c r="I150" s="11" t="s">
         <v>1</v>
@@ -8426,7 +8429,7 @@
         <v>9</v>
       </c>
       <c r="H151" s="13">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="I151" s="13" t="s">
         <v>1</v>
@@ -8455,7 +8458,7 @@
         <v>9</v>
       </c>
       <c r="H152" s="11">
-        <v>59</v>
+        <v>15</v>
       </c>
       <c r="I152" s="11" t="s">
         <v>1</v>
@@ -8484,7 +8487,7 @@
         <v>9</v>
       </c>
       <c r="H153" s="13">
-        <v>54</v>
+        <v>33</v>
       </c>
       <c r="I153" s="13" t="s">
         <v>1</v>
@@ -8513,7 +8516,7 @@
         <v>9</v>
       </c>
       <c r="H154" s="11">
-        <v>66</v>
+        <v>24</v>
       </c>
       <c r="I154" s="11" t="s">
         <v>1</v>
@@ -8542,7 +8545,7 @@
         <v>9</v>
       </c>
       <c r="H155" s="13">
-        <v>12</v>
+        <v>41</v>
       </c>
       <c r="I155" s="13" t="s">
         <v>1</v>
@@ -8571,7 +8574,7 @@
         <v>9</v>
       </c>
       <c r="H156" s="11">
-        <v>16</v>
+        <v>73</v>
       </c>
       <c r="I156" s="11" t="s">
         <v>1</v>
@@ -8600,7 +8603,7 @@
         <v>9</v>
       </c>
       <c r="H157" s="13">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="I157" s="13" t="s">
         <v>1</v>
@@ -8629,7 +8632,7 @@
         <v>9</v>
       </c>
       <c r="H158" s="11">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="I158" s="11" t="s">
         <v>1</v>
@@ -8658,7 +8661,7 @@
         <v>9</v>
       </c>
       <c r="H159" s="13">
-        <v>29</v>
+        <v>53</v>
       </c>
       <c r="I159" s="13" t="s">
         <v>1</v>
@@ -8687,7 +8690,7 @@
         <v>9</v>
       </c>
       <c r="H160" s="11">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I160" s="11" t="s">
         <v>1</v>
@@ -8716,7 +8719,7 @@
         <v>9</v>
       </c>
       <c r="H161" s="13">
-        <v>57</v>
+        <v>28</v>
       </c>
       <c r="I161" s="13" t="s">
         <v>1</v>
@@ -8745,7 +8748,7 @@
         <v>9</v>
       </c>
       <c r="H162" s="11">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="I162" s="11" t="s">
         <v>1</v>
@@ -8774,7 +8777,7 @@
         <v>9</v>
       </c>
       <c r="H163" s="13">
-        <v>68</v>
+        <v>10</v>
       </c>
       <c r="I163" s="13" t="s">
         <v>1</v>
@@ -8803,7 +8806,7 @@
         <v>9</v>
       </c>
       <c r="H164" s="11">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="I164" s="11" t="s">
         <v>1</v>
@@ -8832,7 +8835,7 @@
         <v>9</v>
       </c>
       <c r="H165" s="13">
-        <v>70</v>
+        <v>19</v>
       </c>
       <c r="I165" s="13" t="s">
         <v>1</v>
@@ -8861,7 +8864,7 @@
         <v>9</v>
       </c>
       <c r="H166" s="11">
-        <v>89</v>
+        <v>73</v>
       </c>
       <c r="I166" s="11" t="s">
         <v>1</v>
@@ -8890,7 +8893,7 @@
         <v>9</v>
       </c>
       <c r="H167" s="13">
-        <v>14</v>
+        <v>73</v>
       </c>
       <c r="I167" s="13" t="s">
         <v>1</v>
@@ -8919,7 +8922,7 @@
         <v>9</v>
       </c>
       <c r="H168" s="11">
-        <v>55</v>
+        <v>83</v>
       </c>
       <c r="I168" s="11" t="s">
         <v>1</v>
@@ -8948,7 +8951,7 @@
         <v>9</v>
       </c>
       <c r="H169" s="13">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="I169" s="13" t="s">
         <v>1</v>
@@ -8977,7 +8980,7 @@
         <v>9</v>
       </c>
       <c r="H170" s="11">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="I170" s="11" t="s">
         <v>1</v>
@@ -9006,7 +9009,7 @@
         <v>9</v>
       </c>
       <c r="H171" s="13">
-        <v>76</v>
+        <v>49</v>
       </c>
       <c r="I171" s="13" t="s">
         <v>1</v>
@@ -9035,7 +9038,7 @@
         <v>9</v>
       </c>
       <c r="H172" s="11">
-        <v>73</v>
+        <v>25</v>
       </c>
       <c r="I172" s="11" t="s">
         <v>1</v>
@@ -9064,7 +9067,7 @@
         <v>9</v>
       </c>
       <c r="H173" s="13">
-        <v>38</v>
+        <v>58</v>
       </c>
       <c r="I173" s="13" t="s">
         <v>1</v>
@@ -9093,7 +9096,7 @@
         <v>9</v>
       </c>
       <c r="H174" s="11">
-        <v>10</v>
+        <v>70</v>
       </c>
       <c r="I174" s="11" t="s">
         <v>1</v>
@@ -9122,7 +9125,7 @@
         <v>9</v>
       </c>
       <c r="H175" s="13">
-        <v>29</v>
+        <v>63</v>
       </c>
       <c r="I175" s="13" t="s">
         <v>1</v>
@@ -9151,7 +9154,7 @@
         <v>9</v>
       </c>
       <c r="H176" s="11">
-        <v>28</v>
+        <v>71</v>
       </c>
       <c r="I176" s="11" t="s">
         <v>1</v>
@@ -9180,7 +9183,7 @@
         <v>9</v>
       </c>
       <c r="H177" s="13">
-        <v>18</v>
+        <v>47</v>
       </c>
       <c r="I177" s="13" t="s">
         <v>1</v>
@@ -9209,7 +9212,7 @@
         <v>9</v>
       </c>
       <c r="H178" s="11">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="I178" s="11" t="s">
         <v>1</v>
@@ -9238,7 +9241,7 @@
         <v>9</v>
       </c>
       <c r="H179" s="13">
-        <v>76</v>
+        <v>57</v>
       </c>
       <c r="I179" s="13" t="s">
         <v>1</v>
@@ -9267,7 +9270,7 @@
         <v>9</v>
       </c>
       <c r="H180" s="11">
-        <v>76</v>
+        <v>38</v>
       </c>
       <c r="I180" s="11" t="s">
         <v>1</v>
@@ -9296,7 +9299,7 @@
         <v>9</v>
       </c>
       <c r="H181" s="13">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="I181" s="13" t="s">
         <v>1</v>
@@ -9325,7 +9328,7 @@
         <v>9</v>
       </c>
       <c r="H182" s="11">
-        <v>63</v>
+        <v>89</v>
       </c>
       <c r="I182" s="11" t="s">
         <v>1</v>
@@ -9354,7 +9357,7 @@
         <v>9</v>
       </c>
       <c r="H183" s="13">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I183" s="13" t="s">
         <v>1</v>
@@ -9383,7 +9386,7 @@
         <v>9</v>
       </c>
       <c r="H184" s="11">
-        <v>18</v>
+        <v>69</v>
       </c>
       <c r="I184" s="11" t="s">
         <v>1</v>
@@ -9441,7 +9444,7 @@
         <v>9</v>
       </c>
       <c r="H186" s="11">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I186" s="11" t="s">
         <v>1</v>
@@ -9470,7 +9473,7 @@
         <v>9</v>
       </c>
       <c r="H187" s="13">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="I187" s="13" t="s">
         <v>1</v>
@@ -9499,7 +9502,7 @@
         <v>9</v>
       </c>
       <c r="H188" s="11">
-        <v>33</v>
+        <v>69</v>
       </c>
       <c r="I188" s="11" t="s">
         <v>1</v>
@@ -9528,7 +9531,7 @@
         <v>9</v>
       </c>
       <c r="H189" s="13">
-        <v>35</v>
+        <v>68</v>
       </c>
       <c r="I189" s="13" t="s">
         <v>1</v>
@@ -9557,7 +9560,7 @@
         <v>9</v>
       </c>
       <c r="H190" s="11">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="I190" s="11" t="s">
         <v>1</v>
@@ -9586,7 +9589,7 @@
         <v>9</v>
       </c>
       <c r="H191" s="13">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="I191" s="13" t="s">
         <v>1</v>
@@ -9615,7 +9618,7 @@
         <v>9</v>
       </c>
       <c r="H192" s="11">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="I192" s="11" t="s">
         <v>1</v>
@@ -9644,7 +9647,7 @@
         <v>9</v>
       </c>
       <c r="H193" s="13">
-        <v>59</v>
+        <v>33</v>
       </c>
       <c r="I193" s="13" t="s">
         <v>1</v>
@@ -9673,7 +9676,7 @@
         <v>9</v>
       </c>
       <c r="H194" s="11">
-        <v>45</v>
+        <v>11</v>
       </c>
       <c r="I194" s="11" t="s">
         <v>1</v>
@@ -9702,7 +9705,7 @@
         <v>9</v>
       </c>
       <c r="H195" s="13">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="I195" s="13" t="s">
         <v>1</v>
@@ -9731,7 +9734,7 @@
         <v>9</v>
       </c>
       <c r="H196" s="11">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="I196" s="11" t="s">
         <v>1</v>
@@ -9760,7 +9763,7 @@
         <v>9</v>
       </c>
       <c r="H197" s="13">
-        <v>52</v>
+        <v>70</v>
       </c>
       <c r="I197" s="13" t="s">
         <v>1</v>
@@ -9789,7 +9792,7 @@
         <v>9</v>
       </c>
       <c r="H198" s="11">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="I198" s="11" t="s">
         <v>1</v>
@@ -9818,7 +9821,7 @@
         <v>9</v>
       </c>
       <c r="H199" s="13">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="I199" s="13" t="s">
         <v>1</v>
@@ -9847,7 +9850,7 @@
         <v>9</v>
       </c>
       <c r="H200" s="11">
-        <v>59</v>
+        <v>72</v>
       </c>
       <c r="I200" s="11" t="s">
         <v>1</v>
@@ -9876,7 +9879,7 @@
         <v>9</v>
       </c>
       <c r="H201" s="13">
-        <v>19</v>
+        <v>79</v>
       </c>
       <c r="I201" s="13" t="s">
         <v>1</v>
@@ -9905,7 +9908,7 @@
         <v>9</v>
       </c>
       <c r="H202" s="11">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="I202" s="11" t="s">
         <v>1</v>
@@ -9934,7 +9937,7 @@
         <v>9</v>
       </c>
       <c r="H203" s="13">
-        <v>25</v>
+        <v>69</v>
       </c>
       <c r="I203" s="13" t="s">
         <v>1</v>
@@ -9963,7 +9966,7 @@
         <v>9</v>
       </c>
       <c r="H204" s="11">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="I204" s="11" t="s">
         <v>1</v>
@@ -9992,7 +9995,7 @@
         <v>9</v>
       </c>
       <c r="H205" s="13">
-        <v>66</v>
+        <v>83</v>
       </c>
       <c r="I205" s="13" t="s">
         <v>1</v>
@@ -10021,7 +10024,7 @@
         <v>9</v>
       </c>
       <c r="H206" s="11">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="I206" s="11" t="s">
         <v>1</v>
@@ -10050,7 +10053,7 @@
         <v>9</v>
       </c>
       <c r="H207" s="13">
-        <v>79</v>
+        <v>27</v>
       </c>
       <c r="I207" s="13" t="s">
         <v>1</v>
@@ -10079,7 +10082,7 @@
         <v>9</v>
       </c>
       <c r="H208" s="11">
-        <v>84</v>
+        <v>43</v>
       </c>
       <c r="I208" s="11" t="s">
         <v>1</v>
@@ -10108,7 +10111,7 @@
         <v>9</v>
       </c>
       <c r="H209" s="13">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="I209" s="13" t="s">
         <v>1</v>
@@ -10137,7 +10140,7 @@
         <v>9</v>
       </c>
       <c r="H210" s="11">
-        <v>65</v>
+        <v>19</v>
       </c>
       <c r="I210" s="11" t="s">
         <v>1</v>
@@ -10166,7 +10169,7 @@
         <v>9</v>
       </c>
       <c r="H211" s="13">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="I211" s="13" t="s">
         <v>1</v>
@@ -10195,7 +10198,7 @@
         <v>9</v>
       </c>
       <c r="H212" s="11">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="I212" s="11" t="s">
         <v>1</v>
@@ -10224,7 +10227,7 @@
         <v>9</v>
       </c>
       <c r="H213" s="13">
-        <v>40</v>
+        <v>74</v>
       </c>
       <c r="I213" s="13" t="s">
         <v>1</v>
@@ -10253,7 +10256,7 @@
         <v>9</v>
       </c>
       <c r="H214" s="11">
-        <v>31</v>
+        <v>59</v>
       </c>
       <c r="I214" s="11" t="s">
         <v>1</v>
@@ -10282,7 +10285,7 @@
         <v>9</v>
       </c>
       <c r="H215" s="13">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I215" s="13" t="s">
         <v>1</v>
@@ -10311,7 +10314,7 @@
         <v>9</v>
       </c>
       <c r="H216" s="11">
-        <v>44</v>
+        <v>13</v>
       </c>
       <c r="I216" s="11" t="s">
         <v>1</v>
@@ -10340,7 +10343,7 @@
         <v>9</v>
       </c>
       <c r="H217" s="13">
-        <v>14</v>
+        <v>52</v>
       </c>
       <c r="I217" s="13" t="s">
         <v>1</v>
@@ -10369,7 +10372,7 @@
         <v>9</v>
       </c>
       <c r="H218" s="11">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I218" s="11" t="s">
         <v>1</v>
@@ -10398,7 +10401,7 @@
         <v>9</v>
       </c>
       <c r="H219" s="13">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="I219" s="13" t="s">
         <v>1</v>
@@ -10427,7 +10430,7 @@
         <v>9</v>
       </c>
       <c r="H220" s="11">
-        <v>75</v>
+        <v>46</v>
       </c>
       <c r="I220" s="11" t="s">
         <v>1</v>
@@ -10456,7 +10459,7 @@
         <v>9</v>
       </c>
       <c r="H221" s="13">
-        <v>63</v>
+        <v>82</v>
       </c>
       <c r="I221" s="13" t="s">
         <v>1</v>
@@ -10485,7 +10488,7 @@
         <v>9</v>
       </c>
       <c r="H222" s="11">
-        <v>43</v>
+        <v>59</v>
       </c>
       <c r="I222" s="11" t="s">
         <v>1</v>
@@ -10502,7 +10505,7 @@
         <v>721</v>
       </c>
       <c r="D223" s="13" t="s">
-        <v>602</v>
+        <v>722</v>
       </c>
       <c r="E223" s="13" t="s">
         <v>598</v>
@@ -10514,7 +10517,7 @@
         <v>9</v>
       </c>
       <c r="H223" s="13">
-        <v>85</v>
+        <v>24</v>
       </c>
       <c r="I223" s="13" t="s">
         <v>1</v>
@@ -10522,16 +10525,16 @@
     </row>
     <row r="224" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A224" s="11" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="B224" s="11" t="s">
         <v>22</v>
       </c>
       <c r="C224" s="11" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="D224" s="11" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="E224" s="11" t="s">
         <v>598</v>
@@ -10543,7 +10546,7 @@
         <v>9</v>
       </c>
       <c r="H224" s="11">
-        <v>89</v>
+        <v>69</v>
       </c>
       <c r="I224" s="11" t="s">
         <v>1</v>
@@ -10551,16 +10554,16 @@
     </row>
     <row r="225" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A225" s="13" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="B225" s="13" t="s">
         <v>22</v>
       </c>
       <c r="C225" s="13" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="D225" s="13" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="E225" s="13" t="s">
         <v>598</v>
@@ -10572,7 +10575,7 @@
         <v>9</v>
       </c>
       <c r="H225" s="13">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="I225" s="13" t="s">
         <v>1</v>
@@ -10580,16 +10583,16 @@
     </row>
     <row r="226" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A226" s="11" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="B226" s="11" t="s">
         <v>22</v>
       </c>
       <c r="C226" s="11" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="D226" s="11" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="E226" s="11" t="s">
         <v>598</v>
@@ -10601,7 +10604,7 @@
         <v>9</v>
       </c>
       <c r="H226" s="11">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="I226" s="11" t="s">
         <v>1</v>
@@ -10609,16 +10612,16 @@
     </row>
     <row r="227" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A227" s="13" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="B227" s="13" t="s">
         <v>22</v>
       </c>
       <c r="C227" s="13" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="D227" s="13" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="E227" s="13" t="s">
         <v>598</v>
@@ -10630,7 +10633,7 @@
         <v>9</v>
       </c>
       <c r="H227" s="13">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="I227" s="13" t="s">
         <v>1</v>
@@ -10638,16 +10641,16 @@
     </row>
     <row r="228" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A228" s="11" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="B228" s="11" t="s">
         <v>22</v>
       </c>
       <c r="C228" s="11" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="D228" s="11" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="E228" s="11" t="s">
         <v>598</v>
@@ -10659,7 +10662,7 @@
         <v>9</v>
       </c>
       <c r="H228" s="11">
-        <v>28</v>
+        <v>62</v>
       </c>
       <c r="I228" s="11" t="s">
         <v>1</v>
@@ -10667,16 +10670,16 @@
     </row>
     <row r="229" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A229" s="13" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="B229" s="13" t="s">
         <v>22</v>
       </c>
       <c r="C229" s="13" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="D229" s="13" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="E229" s="13" t="s">
         <v>598</v>
@@ -10688,7 +10691,7 @@
         <v>9</v>
       </c>
       <c r="H229" s="13">
-        <v>40</v>
+        <v>78</v>
       </c>
       <c r="I229" s="13" t="s">
         <v>1</v>
@@ -10696,16 +10699,16 @@
     </row>
     <row r="230" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A230" s="11" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="B230" s="11" t="s">
         <v>22</v>
       </c>
       <c r="C230" s="11" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="D230" s="11" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="E230" s="11" t="s">
         <v>598</v>
@@ -10717,7 +10720,7 @@
         <v>9</v>
       </c>
       <c r="H230" s="11">
-        <v>87</v>
+        <v>26</v>
       </c>
       <c r="I230" s="11" t="s">
         <v>1</v>
@@ -10725,16 +10728,16 @@
     </row>
     <row r="231" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A231" s="13" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="B231" s="13" t="s">
         <v>22</v>
       </c>
       <c r="C231" s="13" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="D231" s="13" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="E231" s="13" t="s">
         <v>598</v>
@@ -10746,7 +10749,7 @@
         <v>9</v>
       </c>
       <c r="H231" s="13">
-        <v>88</v>
+        <v>10</v>
       </c>
       <c r="I231" s="13" t="s">
         <v>1</v>
@@ -10754,28 +10757,28 @@
     </row>
     <row r="232" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A232" s="11" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="B232" s="11" t="s">
         <v>23</v>
       </c>
       <c r="C232" s="11" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="D232" s="11" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="E232" s="11" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="F232" s="11" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="G232" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H232" s="11">
-        <v>51</v>
+        <v>67</v>
       </c>
       <c r="I232" s="11" t="s">
         <v>1</v>
@@ -10783,28 +10786,28 @@
     </row>
     <row r="233" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A233" s="13" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="B233" s="13" t="s">
         <v>23</v>
       </c>
       <c r="C233" s="13" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="D233" s="13" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="E233" s="13" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="F233" s="13" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="G233" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H233" s="13">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="I233" s="13" t="s">
         <v>1</v>
@@ -10812,28 +10815,28 @@
     </row>
     <row r="234" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A234" s="11" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="B234" s="11" t="s">
         <v>23</v>
       </c>
       <c r="C234" s="11" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="D234" s="11" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="E234" s="11" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="F234" s="11" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="G234" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H234" s="11">
-        <v>29</v>
+        <v>78</v>
       </c>
       <c r="I234" s="11" t="s">
         <v>1</v>
@@ -10841,28 +10844,28 @@
     </row>
     <row r="235" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A235" s="13" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="B235" s="13" t="s">
         <v>23</v>
       </c>
       <c r="C235" s="13" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="D235" s="13" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="E235" s="13" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="F235" s="13" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="G235" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H235" s="13">
-        <v>55</v>
+        <v>14</v>
       </c>
       <c r="I235" s="13" t="s">
         <v>1</v>
@@ -10870,28 +10873,28 @@
     </row>
     <row r="236" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A236" s="11" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="B236" s="11" t="s">
         <v>23</v>
       </c>
       <c r="C236" s="11" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="D236" s="11" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="E236" s="11" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="F236" s="11" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="G236" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H236" s="11">
-        <v>68</v>
+        <v>56</v>
       </c>
       <c r="I236" s="11" t="s">
         <v>1</v>
@@ -10899,28 +10902,28 @@
     </row>
     <row r="237" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A237" s="13" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="B237" s="13" t="s">
         <v>23</v>
       </c>
       <c r="C237" s="13" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="D237" s="13" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="E237" s="13" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="F237" s="13" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="G237" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H237" s="13">
-        <v>52</v>
+        <v>14</v>
       </c>
       <c r="I237" s="13" t="s">
         <v>1</v>
@@ -10928,28 +10931,28 @@
     </row>
     <row r="238" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A238" s="11" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="B238" s="11" t="s">
         <v>23</v>
       </c>
       <c r="C238" s="11" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="D238" s="11" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="E238" s="11" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="F238" s="11" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="G238" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H238" s="11">
-        <v>62</v>
+        <v>83</v>
       </c>
       <c r="I238" s="11" t="s">
         <v>1</v>
@@ -10957,28 +10960,28 @@
     </row>
     <row r="239" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A239" s="13" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="B239" s="13" t="s">
         <v>23</v>
       </c>
       <c r="C239" s="13" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="D239" s="13" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="E239" s="13" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="F239" s="13" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="G239" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H239" s="13">
-        <v>51</v>
+        <v>83</v>
       </c>
       <c r="I239" s="13" t="s">
         <v>1</v>
@@ -10986,28 +10989,28 @@
     </row>
     <row r="240" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A240" s="11" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="B240" s="11" t="s">
         <v>23</v>
       </c>
       <c r="C240" s="11" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="D240" s="11" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="E240" s="11" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="F240" s="11" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="G240" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H240" s="11">
-        <v>52</v>
+        <v>82</v>
       </c>
       <c r="I240" s="11" t="s">
         <v>1</v>
@@ -11015,28 +11018,28 @@
     </row>
     <row r="241" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A241" s="13" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="B241" s="13" t="s">
         <v>23</v>
       </c>
       <c r="C241" s="13" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="D241" s="13" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="E241" s="13" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="F241" s="13" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="G241" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H241" s="13">
-        <v>77</v>
+        <v>25</v>
       </c>
       <c r="I241" s="13" t="s">
         <v>1</v>
@@ -11044,28 +11047,28 @@
     </row>
     <row r="242" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A242" s="11" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="B242" s="11" t="s">
         <v>23</v>
       </c>
       <c r="C242" s="11" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="D242" s="11" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="E242" s="11" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="F242" s="11" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="G242" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H242" s="11">
-        <v>84</v>
+        <v>36</v>
       </c>
       <c r="I242" s="11" t="s">
         <v>1</v>
@@ -11073,28 +11076,28 @@
     </row>
     <row r="243" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A243" s="13" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="B243" s="13" t="s">
         <v>23</v>
       </c>
       <c r="C243" s="13" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="D243" s="13" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="E243" s="13" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="F243" s="13" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="G243" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H243" s="13">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="I243" s="13" t="s">
         <v>1</v>
@@ -11102,28 +11105,28 @@
     </row>
     <row r="244" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A244" s="11" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="B244" s="11" t="s">
         <v>23</v>
       </c>
       <c r="C244" s="11" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="D244" s="11" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="E244" s="11" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="F244" s="11" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="G244" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H244" s="11">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="I244" s="11" t="s">
         <v>1</v>
@@ -11131,28 +11134,28 @@
     </row>
     <row r="245" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A245" s="13" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="B245" s="13" t="s">
         <v>23</v>
       </c>
       <c r="C245" s="13" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="D245" s="13" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="E245" s="13" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="F245" s="13" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="G245" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H245" s="13">
-        <v>72</v>
+        <v>26</v>
       </c>
       <c r="I245" s="13" t="s">
         <v>1</v>
@@ -11160,28 +11163,28 @@
     </row>
     <row r="246" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A246" s="11" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="B246" s="11" t="s">
         <v>23</v>
       </c>
       <c r="C246" s="11" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="D246" s="11" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="E246" s="11" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="F246" s="11" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="G246" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H246" s="11">
-        <v>65</v>
+        <v>21</v>
       </c>
       <c r="I246" s="11" t="s">
         <v>1</v>
@@ -11189,28 +11192,28 @@
     </row>
     <row r="247" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A247" s="13" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="B247" s="13" t="s">
         <v>24</v>
       </c>
       <c r="C247" s="13" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="D247" s="13" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="E247" s="13" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="F247" s="13" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="G247" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H247" s="13">
-        <v>72</v>
+        <v>14</v>
       </c>
       <c r="I247" s="13" t="s">
         <v>1</v>
@@ -11218,28 +11221,28 @@
     </row>
     <row r="248" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A248" s="11" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="B248" s="11" t="s">
         <v>24</v>
       </c>
       <c r="C248" s="11" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="D248" s="11" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="E248" s="11" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="F248" s="11" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="G248" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H248" s="11">
-        <v>83</v>
+        <v>36</v>
       </c>
       <c r="I248" s="11" t="s">
         <v>1</v>
@@ -11247,28 +11250,28 @@
     </row>
     <row r="249" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A249" s="13" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="B249" s="13" t="s">
         <v>24</v>
       </c>
       <c r="C249" s="13" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="D249" s="13" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="E249" s="13" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="F249" s="13" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="G249" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H249" s="13">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="I249" s="13" t="s">
         <v>1</v>
@@ -11276,28 +11279,28 @@
     </row>
     <row r="250" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A250" s="11" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="B250" s="11" t="s">
         <v>24</v>
       </c>
       <c r="C250" s="11" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="D250" s="11" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="E250" s="11" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="F250" s="11" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="G250" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H250" s="11">
-        <v>78</v>
+        <v>53</v>
       </c>
       <c r="I250" s="11" t="s">
         <v>1</v>
@@ -11305,28 +11308,28 @@
     </row>
     <row r="251" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A251" s="13" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="B251" s="13" t="s">
         <v>24</v>
       </c>
       <c r="C251" s="13" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="D251" s="13" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="E251" s="13" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="F251" s="13" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="G251" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H251" s="13">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="I251" s="13" t="s">
         <v>1</v>
@@ -11334,28 +11337,28 @@
     </row>
     <row r="252" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A252" s="11" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="B252" s="11" t="s">
         <v>24</v>
       </c>
       <c r="C252" s="11" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="D252" s="11" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="E252" s="11" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="F252" s="11" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="G252" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H252" s="11">
-        <v>47</v>
+        <v>61</v>
       </c>
       <c r="I252" s="11" t="s">
         <v>1</v>
@@ -11363,28 +11366,28 @@
     </row>
     <row r="253" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A253" s="13" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="B253" s="13" t="s">
         <v>24</v>
       </c>
       <c r="C253" s="13" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="D253" s="13" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="E253" s="13" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="F253" s="13" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="G253" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H253" s="13">
-        <v>41</v>
+        <v>80</v>
       </c>
       <c r="I253" s="13" t="s">
         <v>1</v>
@@ -11392,28 +11395,28 @@
     </row>
     <row r="254" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A254" s="11" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="B254" s="11" t="s">
         <v>24</v>
       </c>
       <c r="C254" s="11" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="D254" s="11" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="E254" s="11" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="F254" s="11" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="G254" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H254" s="11">
-        <v>78</v>
+        <v>35</v>
       </c>
       <c r="I254" s="11" t="s">
         <v>1</v>
@@ -11421,28 +11424,28 @@
     </row>
     <row r="255" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A255" s="13" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="B255" s="13" t="s">
         <v>24</v>
       </c>
       <c r="C255" s="13" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="D255" s="13" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="E255" s="13" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="F255" s="13" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="G255" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H255" s="13">
-        <v>79</v>
+        <v>15</v>
       </c>
       <c r="I255" s="13" t="s">
         <v>1</v>
@@ -11450,28 +11453,28 @@
     </row>
     <row r="256" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A256" s="11" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="B256" s="11" t="s">
         <v>24</v>
       </c>
       <c r="C256" s="11" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="D256" s="11" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="E256" s="11" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="F256" s="11" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="G256" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H256" s="11">
-        <v>68</v>
+        <v>35</v>
       </c>
       <c r="I256" s="11" t="s">
         <v>1</v>
@@ -11479,28 +11482,28 @@
     </row>
     <row r="257" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A257" s="13" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="B257" s="13" t="s">
         <v>24</v>
       </c>
       <c r="C257" s="13" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="D257" s="13" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="E257" s="13" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="F257" s="13" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="G257" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H257" s="13">
-        <v>59</v>
+        <v>13</v>
       </c>
       <c r="I257" s="13" t="s">
         <v>1</v>
@@ -11508,28 +11511,28 @@
     </row>
     <row r="258" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A258" s="11" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="B258" s="11" t="s">
         <v>24</v>
       </c>
       <c r="C258" s="11" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="D258" s="11" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="E258" s="11" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="F258" s="11" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="G258" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H258" s="11">
-        <v>58</v>
+        <v>86</v>
       </c>
       <c r="I258" s="11" t="s">
         <v>1</v>
@@ -11537,28 +11540,28 @@
     </row>
     <row r="259" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A259" s="13" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="B259" s="13" t="s">
         <v>24</v>
       </c>
       <c r="C259" s="13" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="D259" s="13" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="E259" s="13" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="F259" s="13" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="G259" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H259" s="13">
-        <v>61</v>
+        <v>16</v>
       </c>
       <c r="I259" s="13" t="s">
         <v>1</v>
@@ -11566,28 +11569,28 @@
     </row>
     <row r="260" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A260" s="11" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="B260" s="11" t="s">
         <v>24</v>
       </c>
       <c r="C260" s="11" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="D260" s="11" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="E260" s="11" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="F260" s="11" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="G260" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H260" s="11">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="I260" s="11" t="s">
         <v>1</v>
@@ -11595,28 +11598,28 @@
     </row>
     <row r="261" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A261" s="13" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="B261" s="13" t="s">
         <v>24</v>
       </c>
       <c r="C261" s="13" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="D261" s="13" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="E261" s="13" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="F261" s="13" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="G261" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H261" s="13">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="I261" s="13" t="s">
         <v>1</v>
@@ -11624,28 +11627,28 @@
     </row>
     <row r="262" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A262" s="11" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="B262" s="11" t="s">
         <v>24</v>
       </c>
       <c r="C262" s="11" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="D262" s="11" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="E262" s="11" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="F262" s="11" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="G262" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H262" s="11">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="I262" s="11" t="s">
         <v>1</v>
@@ -11653,28 +11656,28 @@
     </row>
     <row r="263" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A263" s="13" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="B263" s="13" t="s">
         <v>24</v>
       </c>
       <c r="C263" s="13" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="D263" s="13" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="E263" s="13" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="F263" s="13" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="G263" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H263" s="13">
-        <v>31</v>
+        <v>86</v>
       </c>
       <c r="I263" s="13" t="s">
         <v>1</v>
@@ -11682,28 +11685,28 @@
     </row>
     <row r="264" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A264" s="11" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="B264" s="11" t="s">
         <v>24</v>
       </c>
       <c r="C264" s="11" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="D264" s="11" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="E264" s="11" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="F264" s="11" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="G264" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H264" s="11">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="I264" s="11" t="s">
         <v>1</v>
@@ -11711,28 +11714,28 @@
     </row>
     <row r="265" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A265" s="13" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="B265" s="13" t="s">
         <v>24</v>
       </c>
       <c r="C265" s="13" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="D265" s="13" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="E265" s="13" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="F265" s="13" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="G265" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H265" s="13">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="I265" s="13" t="s">
         <v>1</v>
@@ -11740,28 +11743,28 @@
     </row>
     <row r="266" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A266" s="11" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="B266" s="11" t="s">
         <v>24</v>
       </c>
       <c r="C266" s="11" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="D266" s="11" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="E266" s="11" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="F266" s="11" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="G266" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H266" s="11">
-        <v>83</v>
+        <v>62</v>
       </c>
       <c r="I266" s="11" t="s">
         <v>1</v>
@@ -11769,28 +11772,28 @@
     </row>
     <row r="267" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A267" s="13" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="B267" s="13" t="s">
         <v>25</v>
       </c>
       <c r="C267" s="13" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="D267" s="13" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="E267" s="13" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="F267" s="13" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="G267" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H267" s="13">
-        <v>61</v>
+        <v>88</v>
       </c>
       <c r="I267" s="13" t="s">
         <v>1</v>
@@ -11798,28 +11801,28 @@
     </row>
     <row r="268" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A268" s="11" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="B268" s="11" t="s">
         <v>25</v>
       </c>
       <c r="C268" s="11" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="D268" s="11" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="E268" s="11" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="F268" s="11" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="G268" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H268" s="11">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="I268" s="11" t="s">
         <v>1</v>
@@ -11827,28 +11830,28 @@
     </row>
     <row r="269" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A269" s="13" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="B269" s="13" t="s">
         <v>25</v>
       </c>
       <c r="C269" s="13" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="D269" s="13" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="E269" s="13" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="F269" s="13" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="G269" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H269" s="13">
-        <v>83</v>
+        <v>53</v>
       </c>
       <c r="I269" s="13" t="s">
         <v>1</v>
@@ -11856,28 +11859,28 @@
     </row>
     <row r="270" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A270" s="11" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="B270" s="11" t="s">
         <v>25</v>
       </c>
       <c r="C270" s="11" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="D270" s="11" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="E270" s="11" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="F270" s="11" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="G270" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H270" s="11">
-        <v>63</v>
+        <v>22</v>
       </c>
       <c r="I270" s="11" t="s">
         <v>1</v>
@@ -11885,28 +11888,28 @@
     </row>
     <row r="271" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A271" s="13" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="B271" s="13" t="s">
         <v>25</v>
       </c>
       <c r="C271" s="13" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="D271" s="13" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="E271" s="13" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="F271" s="13" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="G271" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H271" s="13">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="I271" s="13" t="s">
         <v>1</v>
@@ -11914,28 +11917,28 @@
     </row>
     <row r="272" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A272" s="11" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="B272" s="11" t="s">
         <v>25</v>
       </c>
       <c r="C272" s="11" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="D272" s="11" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="E272" s="11" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="F272" s="11" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="G272" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H272" s="11">
-        <v>25</v>
+        <v>73</v>
       </c>
       <c r="I272" s="11" t="s">
         <v>1</v>
@@ -11943,28 +11946,28 @@
     </row>
     <row r="273" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A273" s="13" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="B273" s="13" t="s">
         <v>25</v>
       </c>
       <c r="C273" s="13" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="D273" s="13" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="E273" s="13" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="F273" s="13" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="G273" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H273" s="13">
-        <v>14</v>
+        <v>80</v>
       </c>
       <c r="I273" s="13" t="s">
         <v>1</v>
@@ -11972,28 +11975,28 @@
     </row>
     <row r="274" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A274" s="11" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="B274" s="11" t="s">
         <v>25</v>
       </c>
       <c r="C274" s="11" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="D274" s="11" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="E274" s="11" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="F274" s="11" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="G274" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H274" s="11">
-        <v>14</v>
+        <v>81</v>
       </c>
       <c r="I274" s="11" t="s">
         <v>1</v>
@@ -12001,28 +12004,28 @@
     </row>
     <row r="275" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A275" s="13" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="B275" s="13" t="s">
         <v>25</v>
       </c>
       <c r="C275" s="13" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="D275" s="13" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="E275" s="13" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="F275" s="13" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="G275" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H275" s="13">
-        <v>78</v>
+        <v>62</v>
       </c>
       <c r="I275" s="13" t="s">
         <v>1</v>
@@ -12030,28 +12033,28 @@
     </row>
     <row r="276" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A276" s="11" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="B276" s="11" t="s">
         <v>25</v>
       </c>
       <c r="C276" s="11" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="D276" s="11" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="E276" s="11" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="F276" s="11" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="G276" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H276" s="11">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="I276" s="11" t="s">
         <v>1</v>
@@ -12059,28 +12062,28 @@
     </row>
     <row r="277" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A277" s="13" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="B277" s="13" t="s">
         <v>25</v>
       </c>
       <c r="C277" s="13" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="D277" s="13" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="E277" s="13" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="F277" s="13" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="G277" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H277" s="13">
-        <v>22</v>
+        <v>47</v>
       </c>
       <c r="I277" s="13" t="s">
         <v>1</v>
@@ -12088,28 +12091,28 @@
     </row>
     <row r="278" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A278" s="11" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="B278" s="11" t="s">
         <v>25</v>
       </c>
       <c r="C278" s="11" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="D278" s="11" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="E278" s="11" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="F278" s="11" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="G278" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H278" s="11">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="I278" s="11" t="s">
         <v>1</v>
@@ -12117,28 +12120,28 @@
     </row>
     <row r="279" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A279" s="13" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="B279" s="13" t="s">
         <v>25</v>
       </c>
       <c r="C279" s="13" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="D279" s="13" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="E279" s="13" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="F279" s="13" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="G279" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H279" s="13">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="I279" s="13" t="s">
         <v>1</v>
@@ -12146,28 +12149,28 @@
     </row>
     <row r="280" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A280" s="11" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="B280" s="11" t="s">
         <v>25</v>
       </c>
       <c r="C280" s="11" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="D280" s="11" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="E280" s="11" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="F280" s="11" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="G280" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H280" s="11">
-        <v>72</v>
+        <v>17</v>
       </c>
       <c r="I280" s="11" t="s">
         <v>1</v>
@@ -12175,28 +12178,28 @@
     </row>
     <row r="281" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A281" s="13" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="B281" s="13" t="s">
         <v>25</v>
       </c>
       <c r="C281" s="13" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="D281" s="13" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="E281" s="13" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="F281" s="13" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="G281" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H281" s="13">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="I281" s="13" t="s">
         <v>1</v>
@@ -12204,28 +12207,28 @@
     </row>
     <row r="282" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A282" s="11" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="B282" s="11" t="s">
         <v>26</v>
       </c>
       <c r="C282" s="11" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="D282" s="11" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="E282" s="11" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="F282" s="11" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="G282" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H282" s="11">
-        <v>60</v>
+        <v>35</v>
       </c>
       <c r="I282" s="11" t="s">
         <v>1</v>
@@ -12233,28 +12236,28 @@
     </row>
     <row r="283" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A283" s="13" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="B283" s="13" t="s">
         <v>26</v>
       </c>
       <c r="C283" s="13" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="D283" s="13" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="E283" s="13" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="F283" s="13" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="G283" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H283" s="13">
-        <v>16</v>
+        <v>63</v>
       </c>
       <c r="I283" s="13" t="s">
         <v>1</v>
@@ -12262,28 +12265,28 @@
     </row>
     <row r="284" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A284" s="11" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="B284" s="11" t="s">
         <v>26</v>
       </c>
       <c r="C284" s="11" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="D284" s="11" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="E284" s="11" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="F284" s="11" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="G284" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H284" s="11">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="I284" s="11" t="s">
         <v>1</v>
@@ -12291,28 +12294,28 @@
     </row>
     <row r="285" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A285" s="13" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="B285" s="13" t="s">
         <v>26</v>
       </c>
       <c r="C285" s="13" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="D285" s="13" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="E285" s="13" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="F285" s="13" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="G285" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H285" s="13">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="I285" s="13" t="s">
         <v>1</v>
@@ -12320,28 +12323,28 @@
     </row>
     <row r="286" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A286" s="11" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="B286" s="11" t="s">
         <v>26</v>
       </c>
       <c r="C286" s="11" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="D286" s="11" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="E286" s="11" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="F286" s="11" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="G286" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H286" s="11">
-        <v>18</v>
+        <v>62</v>
       </c>
       <c r="I286" s="11" t="s">
         <v>1</v>
@@ -12349,28 +12352,28 @@
     </row>
     <row r="287" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A287" s="13" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="B287" s="13" t="s">
         <v>26</v>
       </c>
       <c r="C287" s="13" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="D287" s="13" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="E287" s="13" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="F287" s="13" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="G287" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H287" s="13">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="I287" s="13" t="s">
         <v>1</v>
@@ -12378,28 +12381,28 @@
     </row>
     <row r="288" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A288" s="11" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="B288" s="11" t="s">
         <v>26</v>
       </c>
       <c r="C288" s="11" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="D288" s="11" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="E288" s="11" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="F288" s="11" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="G288" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H288" s="11">
-        <v>34</v>
+        <v>89</v>
       </c>
       <c r="I288" s="11" t="s">
         <v>1</v>
@@ -12407,28 +12410,28 @@
     </row>
     <row r="289" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A289" s="13" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="B289" s="13" t="s">
         <v>26</v>
       </c>
       <c r="C289" s="13" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="D289" s="13" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="E289" s="13" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="F289" s="13" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="G289" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H289" s="13">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="I289" s="13" t="s">
         <v>1</v>
@@ -12436,28 +12439,28 @@
     </row>
     <row r="290" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A290" s="11" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="B290" s="11" t="s">
         <v>26</v>
       </c>
       <c r="C290" s="11" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="D290" s="11" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="E290" s="11" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="F290" s="11" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="G290" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H290" s="11">
-        <v>69</v>
+        <v>17</v>
       </c>
       <c r="I290" s="11" t="s">
         <v>1</v>
@@ -12465,28 +12468,28 @@
     </row>
     <row r="291" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A291" s="13" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="B291" s="13" t="s">
         <v>26</v>
       </c>
       <c r="C291" s="13" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="D291" s="13" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="E291" s="13" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="F291" s="13" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="G291" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H291" s="13">
-        <v>79</v>
+        <v>11</v>
       </c>
       <c r="I291" s="13" t="s">
         <v>1</v>
@@ -12494,28 +12497,28 @@
     </row>
     <row r="292" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A292" s="11" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="B292" s="11" t="s">
         <v>26</v>
       </c>
       <c r="C292" s="11" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="D292" s="11" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="E292" s="11" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="F292" s="11" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="G292" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H292" s="11">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="I292" s="11" t="s">
         <v>1</v>
@@ -12523,28 +12526,28 @@
     </row>
     <row r="293" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A293" s="13" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="B293" s="13" t="s">
         <v>26</v>
       </c>
       <c r="C293" s="13" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="D293" s="13" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="E293" s="13" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="F293" s="13" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="G293" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H293" s="13">
-        <v>72</v>
+        <v>84</v>
       </c>
       <c r="I293" s="13" t="s">
         <v>1</v>
@@ -12552,28 +12555,28 @@
     </row>
     <row r="294" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A294" s="11" t="s">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="B294" s="11" t="s">
         <v>26</v>
       </c>
       <c r="C294" s="11" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="D294" s="11" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="E294" s="11" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="F294" s="11" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="G294" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H294" s="11">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="I294" s="11" t="s">
         <v>1</v>
@@ -12581,28 +12584,28 @@
     </row>
     <row r="295" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A295" s="13" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="B295" s="13" t="s">
         <v>26</v>
       </c>
       <c r="C295" s="13" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="D295" s="13" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="E295" s="13" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="F295" s="13" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="G295" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H295" s="13">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="I295" s="13" t="s">
         <v>1</v>
@@ -12610,28 +12613,28 @@
     </row>
     <row r="296" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A296" s="11" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="B296" s="11" t="s">
         <v>26</v>
       </c>
       <c r="C296" s="11" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="D296" s="11" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="E296" s="11" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="F296" s="11" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="G296" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H296" s="11">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="I296" s="11" t="s">
         <v>1</v>
@@ -12639,28 +12642,28 @@
     </row>
     <row r="297" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A297" s="13" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="B297" s="13" t="s">
         <v>26</v>
       </c>
       <c r="C297" s="13" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="D297" s="13" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="E297" s="13" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="F297" s="13" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="G297" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H297" s="13">
-        <v>77</v>
+        <v>32</v>
       </c>
       <c r="I297" s="13" t="s">
         <v>1</v>
@@ -12668,28 +12671,28 @@
     </row>
     <row r="298" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A298" s="11" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="B298" s="11" t="s">
         <v>26</v>
       </c>
       <c r="C298" s="11" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="D298" s="11" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="E298" s="11" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="F298" s="11" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="G298" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H298" s="11">
-        <v>80</v>
+        <v>12</v>
       </c>
       <c r="I298" s="11" t="s">
         <v>1</v>
@@ -12697,28 +12700,28 @@
     </row>
     <row r="299" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A299" s="13" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="B299" s="13" t="s">
         <v>26</v>
       </c>
       <c r="C299" s="13" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="D299" s="13" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="E299" s="13" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="F299" s="13" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="G299" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H299" s="13">
-        <v>80</v>
+        <v>61</v>
       </c>
       <c r="I299" s="13" t="s">
         <v>1</v>
@@ -12726,28 +12729,28 @@
     </row>
     <row r="300" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A300" s="11" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="B300" s="11" t="s">
         <v>26</v>
       </c>
       <c r="C300" s="11" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="D300" s="11" t="s">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="E300" s="11" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="F300" s="11" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="G300" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H300" s="11">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="I300" s="11" t="s">
         <v>1</v>
@@ -12755,28 +12758,28 @@
     </row>
     <row r="301" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A301" s="13" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="B301" s="13" t="s">
         <v>26</v>
       </c>
       <c r="C301" s="13" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="D301" s="13" t="s">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="E301" s="13" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="F301" s="13" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="G301" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H301" s="13">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="I301" s="13" t="s">
         <v>1</v>
@@ -12784,28 +12787,28 @@
     </row>
     <row r="302" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A302" s="11" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="B302" s="11" t="s">
         <v>26</v>
       </c>
       <c r="C302" s="11" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="D302" s="11" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="E302" s="11" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="F302" s="11" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="G302" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H302" s="11">
-        <v>11</v>
+        <v>66</v>
       </c>
       <c r="I302" s="11" t="s">
         <v>1</v>
@@ -12813,28 +12816,28 @@
     </row>
     <row r="303" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A303" s="13" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="B303" s="13" t="s">
         <v>26</v>
       </c>
       <c r="C303" s="13" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="D303" s="13" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="E303" s="13" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="F303" s="13" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="G303" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H303" s="13">
-        <v>85</v>
+        <v>71</v>
       </c>
       <c r="I303" s="13" t="s">
         <v>1</v>
@@ -12842,28 +12845,28 @@
     </row>
     <row r="304" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A304" s="11" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="B304" s="11" t="s">
         <v>26</v>
       </c>
       <c r="C304" s="11" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="D304" s="11" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="E304" s="11" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="F304" s="11" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="G304" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H304" s="11">
-        <v>32</v>
+        <v>63</v>
       </c>
       <c r="I304" s="11" t="s">
         <v>1</v>
@@ -12871,28 +12874,28 @@
     </row>
     <row r="305" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A305" s="13" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="B305" s="13" t="s">
         <v>26</v>
       </c>
       <c r="C305" s="13" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="D305" s="13" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="E305" s="13" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="F305" s="13" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="G305" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H305" s="13">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="I305" s="13" t="s">
         <v>1</v>
@@ -12900,22 +12903,22 @@
     </row>
     <row r="306" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A306" s="11" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="B306" s="11" t="s">
         <v>26</v>
       </c>
       <c r="C306" s="11" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="D306" s="11" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="E306" s="11" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="F306" s="11" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="G306" s="12" t="s">
         <v>9</v>
@@ -12929,28 +12932,28 @@
     </row>
     <row r="307" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A307" s="13" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="B307" s="13" t="s">
         <v>27</v>
       </c>
       <c r="C307" s="13" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="D307" s="13" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="E307" s="13" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="F307" s="13" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="G307" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H307" s="13">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="I307" s="13" t="s">
         <v>1</v>
@@ -12958,28 +12961,28 @@
     </row>
     <row r="308" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A308" s="11" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="B308" s="11" t="s">
         <v>27</v>
       </c>
       <c r="C308" s="11" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="D308" s="11" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="E308" s="11" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="F308" s="11" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="G308" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H308" s="11">
-        <v>36</v>
+        <v>78</v>
       </c>
       <c r="I308" s="11" t="s">
         <v>1</v>
@@ -12987,28 +12990,28 @@
     </row>
     <row r="309" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A309" s="13" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="B309" s="13" t="s">
         <v>27</v>
       </c>
       <c r="C309" s="13" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="D309" s="13" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="E309" s="13" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="F309" s="13" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="G309" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H309" s="13">
-        <v>72</v>
+        <v>33</v>
       </c>
       <c r="I309" s="13" t="s">
         <v>1</v>
@@ -13016,28 +13019,28 @@
     </row>
     <row r="310" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A310" s="11" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="B310" s="11" t="s">
         <v>27</v>
       </c>
       <c r="C310" s="11" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="D310" s="11" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="E310" s="11" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="F310" s="11" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="G310" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H310" s="11">
-        <v>11</v>
+        <v>38</v>
       </c>
       <c r="I310" s="11" t="s">
         <v>1</v>
@@ -13045,28 +13048,28 @@
     </row>
     <row r="311" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A311" s="13" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="B311" s="13" t="s">
         <v>27</v>
       </c>
       <c r="C311" s="13" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="D311" s="13" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="E311" s="13" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="F311" s="13" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="G311" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H311" s="13">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="I311" s="13" t="s">
         <v>1</v>
@@ -13074,28 +13077,28 @@
     </row>
     <row r="312" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A312" s="11" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="B312" s="11" t="s">
         <v>27</v>
       </c>
       <c r="C312" s="11" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="D312" s="11" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="E312" s="11" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="F312" s="11" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="G312" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H312" s="11">
-        <v>26</v>
+        <v>47</v>
       </c>
       <c r="I312" s="11" t="s">
         <v>1</v>
@@ -13103,28 +13106,28 @@
     </row>
     <row r="313" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A313" s="13" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="B313" s="13" t="s">
         <v>27</v>
       </c>
       <c r="C313" s="13" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="D313" s="13" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="E313" s="13" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="F313" s="13" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="G313" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H313" s="13">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="I313" s="13" t="s">
         <v>1</v>
@@ -13132,28 +13135,28 @@
     </row>
     <row r="314" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A314" s="11" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="B314" s="11" t="s">
         <v>27</v>
       </c>
       <c r="C314" s="11" t="s">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="D314" s="11" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="E314" s="11" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="F314" s="11" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="G314" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H314" s="11">
-        <v>16</v>
+        <v>66</v>
       </c>
       <c r="I314" s="11" t="s">
         <v>1</v>
@@ -13161,28 +13164,28 @@
     </row>
     <row r="315" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A315" s="13" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="B315" s="13" t="s">
         <v>27</v>
       </c>
       <c r="C315" s="13" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="D315" s="13" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="E315" s="13" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="F315" s="13" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="G315" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H315" s="13">
-        <v>58</v>
+        <v>35</v>
       </c>
       <c r="I315" s="13" t="s">
         <v>1</v>
@@ -13190,28 +13193,28 @@
     </row>
     <row r="316" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A316" s="11" t="s">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="B316" s="11" t="s">
         <v>27</v>
       </c>
       <c r="C316" s="11" t="s">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="D316" s="11" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="E316" s="11" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="F316" s="11" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="G316" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H316" s="11">
-        <v>61</v>
+        <v>30</v>
       </c>
       <c r="I316" s="11" t="s">
         <v>1</v>
@@ -13219,28 +13222,28 @@
     </row>
     <row r="317" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A317" s="13" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="B317" s="13" t="s">
         <v>27</v>
       </c>
       <c r="C317" s="13" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="D317" s="13" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="E317" s="13" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="F317" s="13" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="G317" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H317" s="13">
-        <v>26</v>
+        <v>73</v>
       </c>
       <c r="I317" s="13" t="s">
         <v>1</v>
@@ -13248,28 +13251,28 @@
     </row>
     <row r="318" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A318" s="11" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="B318" s="11" t="s">
         <v>27</v>
       </c>
       <c r="C318" s="11" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="D318" s="11" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="E318" s="11" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="F318" s="11" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="G318" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H318" s="11">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="I318" s="11" t="s">
         <v>1</v>
@@ -13277,28 +13280,28 @@
     </row>
     <row r="319" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A319" s="13" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="B319" s="13" t="s">
         <v>27</v>
       </c>
       <c r="C319" s="13" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="D319" s="13" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="E319" s="13" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="F319" s="13" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="G319" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H319" s="13">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="I319" s="13" t="s">
         <v>1</v>
@@ -13306,28 +13309,28 @@
     </row>
     <row r="320" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A320" s="11" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="B320" s="11" t="s">
         <v>27</v>
       </c>
       <c r="C320" s="11" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="D320" s="11" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="E320" s="11" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="F320" s="11" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="G320" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H320" s="11">
-        <v>67</v>
+        <v>84</v>
       </c>
       <c r="I320" s="11" t="s">
         <v>1</v>
@@ -13335,28 +13338,28 @@
     </row>
     <row r="321" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A321" s="13" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="B321" s="13" t="s">
         <v>27</v>
       </c>
       <c r="C321" s="13" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="D321" s="13" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="E321" s="13" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="F321" s="13" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="G321" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H321" s="13">
-        <v>18</v>
+        <v>57</v>
       </c>
       <c r="I321" s="13" t="s">
         <v>1</v>

--- a/testing/selenium-tests/Test_Report.xlsx
+++ b/testing/selenium-tests/Test_Report.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2636" uniqueCount="1027">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2636" uniqueCount="1026">
   <si>
     <t>GROWMARK WEB APP - AUTOMATED TESTING REPORT</t>
   </si>
@@ -1805,7 +1805,7 @@
     <t>TestCase_WebSales_01: Processing sales entry for Item_1</t>
   </si>
   <si>
-    <t>Sold 461 units of Item_1</t>
+    <t>Sold 57 units of Item_1</t>
   </si>
   <si>
     <t>Sales logged and inventory updated</t>
@@ -1820,7 +1820,7 @@
     <t>TestCase_WebSales_02: Processing sales entry for Item_2</t>
   </si>
   <si>
-    <t>Sold 475 units of Item_2</t>
+    <t>Sold 264 units of Item_2</t>
   </si>
   <si>
     <t>TC183</t>
@@ -1829,7 +1829,7 @@
     <t>TestCase_WebSales_03: Processing sales entry for Item_3</t>
   </si>
   <si>
-    <t>Sold 2 units of Item_3</t>
+    <t>Sold 5 units of Item_3</t>
   </si>
   <si>
     <t>TC184</t>
@@ -1838,7 +1838,7 @@
     <t>TestCase_WebSales_04: Processing sales entry for Item_4</t>
   </si>
   <si>
-    <t>Sold 358 units of Item_4</t>
+    <t>Sold 132 units of Item_4</t>
   </si>
   <si>
     <t>TC185</t>
@@ -1847,7 +1847,7 @@
     <t>TestCase_WebSales_05: Processing sales entry for Item_5</t>
   </si>
   <si>
-    <t>Sold 217 units of Item_5</t>
+    <t>Sold 421 units of Item_5</t>
   </si>
   <si>
     <t>TC186</t>
@@ -1856,7 +1856,7 @@
     <t>TestCase_WebSales_06: Processing sales entry for Item_6</t>
   </si>
   <si>
-    <t>Sold 22 units of Item_6</t>
+    <t>Sold 19 units of Item_6</t>
   </si>
   <si>
     <t>TC187</t>
@@ -1865,7 +1865,7 @@
     <t>TestCase_WebSales_07: Processing sales entry for Item_7</t>
   </si>
   <si>
-    <t>Sold 12 units of Item_7</t>
+    <t>Sold 193 units of Item_7</t>
   </si>
   <si>
     <t>TC188</t>
@@ -1874,7 +1874,7 @@
     <t>TestCase_WebSales_08: Processing sales entry for Item_8</t>
   </si>
   <si>
-    <t>Sold 400 units of Item_8</t>
+    <t>Sold 147 units of Item_8</t>
   </si>
   <si>
     <t>TC189</t>
@@ -1883,7 +1883,7 @@
     <t>TestCase_WebSales_09: Processing sales entry for Item_9</t>
   </si>
   <si>
-    <t>Sold 341 units of Item_9</t>
+    <t>Sold 422 units of Item_9</t>
   </si>
   <si>
     <t>TC190</t>
@@ -1892,7 +1892,7 @@
     <t>TestCase_WebSales_10: Processing sales entry for Item_0</t>
   </si>
   <si>
-    <t>Sold 55 units of Item_0</t>
+    <t>Sold 445 units of Item_0</t>
   </si>
   <si>
     <t>TC191</t>
@@ -1901,16 +1901,13 @@
     <t>TestCase_WebSales_11: Processing sales entry for Item_1</t>
   </si>
   <si>
-    <t>Sold 238 units of Item_1</t>
-  </si>
-  <si>
     <t>TC192</t>
   </si>
   <si>
     <t>TestCase_WebSales_12: Processing sales entry for Item_2</t>
   </si>
   <si>
-    <t>Sold 318 units of Item_2</t>
+    <t>Sold 393 units of Item_2</t>
   </si>
   <si>
     <t>TC193</t>
@@ -1919,7 +1916,7 @@
     <t>TestCase_WebSales_13: Processing sales entry for Item_3</t>
   </si>
   <si>
-    <t>Sold 27 units of Item_3</t>
+    <t>Sold 213 units of Item_3</t>
   </si>
   <si>
     <t>TC194</t>
@@ -1928,7 +1925,7 @@
     <t>TestCase_WebSales_14: Processing sales entry for Item_4</t>
   </si>
   <si>
-    <t>Sold 420 units of Item_4</t>
+    <t>Sold 444 units of Item_4</t>
   </si>
   <si>
     <t>TC195</t>
@@ -1937,7 +1934,7 @@
     <t>TestCase_WebSales_15: Processing sales entry for Item_5</t>
   </si>
   <si>
-    <t>Sold 419 units of Item_5</t>
+    <t>Sold 98 units of Item_5</t>
   </si>
   <si>
     <t>TC196</t>
@@ -1946,7 +1943,7 @@
     <t>TestCase_WebSales_16: Processing sales entry for Item_6</t>
   </si>
   <si>
-    <t>Sold 431 units of Item_6</t>
+    <t>Sold 85 units of Item_6</t>
   </si>
   <si>
     <t>TC197</t>
@@ -1955,7 +1952,7 @@
     <t>TestCase_WebSales_17: Processing sales entry for Item_7</t>
   </si>
   <si>
-    <t>Sold 26 units of Item_7</t>
+    <t>Sold 113 units of Item_7</t>
   </si>
   <si>
     <t>TC198</t>
@@ -1964,7 +1961,7 @@
     <t>TestCase_WebSales_18: Processing sales entry for Item_8</t>
   </si>
   <si>
-    <t>Sold 112 units of Item_8</t>
+    <t>Sold 299 units of Item_8</t>
   </si>
   <si>
     <t>TC199</t>
@@ -1973,7 +1970,7 @@
     <t>TestCase_WebSales_19: Processing sales entry for Item_9</t>
   </si>
   <si>
-    <t>Sold 399 units of Item_9</t>
+    <t>Sold 219 units of Item_9</t>
   </si>
   <si>
     <t>TC200</t>
@@ -1982,7 +1979,7 @@
     <t>TestCase_WebSales_20: Processing sales entry for Item_0</t>
   </si>
   <si>
-    <t>Sold 50 units of Item_0</t>
+    <t>Sold 118 units of Item_0</t>
   </si>
   <si>
     <t>TC201</t>
@@ -1991,7 +1988,7 @@
     <t>TestCase_WebSales_21: Processing sales entry for Item_1</t>
   </si>
   <si>
-    <t>Sold 99 units of Item_1</t>
+    <t>Sold 200 units of Item_1</t>
   </si>
   <si>
     <t>TC202</t>
@@ -2000,7 +1997,7 @@
     <t>TestCase_WebSales_22: Processing sales entry for Item_2</t>
   </si>
   <si>
-    <t>Sold 409 units of Item_2</t>
+    <t>Sold 483 units of Item_2</t>
   </si>
   <si>
     <t>TC203</t>
@@ -2009,7 +2006,7 @@
     <t>TestCase_WebSales_23: Processing sales entry for Item_3</t>
   </si>
   <si>
-    <t>Sold 256 units of Item_3</t>
+    <t>Sold 154 units of Item_3</t>
   </si>
   <si>
     <t>TC204</t>
@@ -2018,7 +2015,7 @@
     <t>TestCase_WebSales_24: Processing sales entry for Item_4</t>
   </si>
   <si>
-    <t>Sold 170 units of Item_4</t>
+    <t>Sold 146 units of Item_4</t>
   </si>
   <si>
     <t>TC205</t>
@@ -2027,7 +2024,7 @@
     <t>TestCase_WebSales_25: Processing sales entry for Item_5</t>
   </si>
   <si>
-    <t>Sold 137 units of Item_5</t>
+    <t>Sold 417 units of Item_5</t>
   </si>
   <si>
     <t>TC206</t>
@@ -2036,7 +2033,7 @@
     <t>TestCase_WebSales_26: Processing sales entry for Item_6</t>
   </si>
   <si>
-    <t>Sold 321 units of Item_6</t>
+    <t>Sold 337 units of Item_6</t>
   </si>
   <si>
     <t>TC207</t>
@@ -2045,7 +2042,7 @@
     <t>TestCase_WebSales_27: Processing sales entry for Item_7</t>
   </si>
   <si>
-    <t>Sold 134 units of Item_7</t>
+    <t>Sold 399 units of Item_7</t>
   </si>
   <si>
     <t>TC208</t>
@@ -2054,7 +2051,7 @@
     <t>TestCase_WebSales_28: Processing sales entry for Item_8</t>
   </si>
   <si>
-    <t>Sold 381 units of Item_8</t>
+    <t>Sold 181 units of Item_8</t>
   </si>
   <si>
     <t>TC209</t>
@@ -2063,7 +2060,7 @@
     <t>TestCase_WebSales_29: Processing sales entry for Item_9</t>
   </si>
   <si>
-    <t>Sold 261 units of Item_9</t>
+    <t>Sold 473 units of Item_9</t>
   </si>
   <si>
     <t>TC210</t>
@@ -2072,7 +2069,7 @@
     <t>TestCase_WebSales_30: Processing sales entry for Item_0</t>
   </si>
   <si>
-    <t>Sold 448 units of Item_0</t>
+    <t>Sold 272 units of Item_0</t>
   </si>
   <si>
     <t>TC211</t>
@@ -2081,7 +2078,7 @@
     <t>TestCase_WebSales_31: Processing sales entry for Item_1</t>
   </si>
   <si>
-    <t>Sold 440 units of Item_1</t>
+    <t>Sold 339 units of Item_1</t>
   </si>
   <si>
     <t>TC212</t>
@@ -2090,7 +2087,7 @@
     <t>TestCase_WebSales_32: Processing sales entry for Item_2</t>
   </si>
   <si>
-    <t>Sold 239 units of Item_2</t>
+    <t>Sold 384 units of Item_2</t>
   </si>
   <si>
     <t>TC213</t>
@@ -2099,7 +2096,7 @@
     <t>TestCase_WebSales_33: Processing sales entry for Item_3</t>
   </si>
   <si>
-    <t>Sold 375 units of Item_3</t>
+    <t>Sold 247 units of Item_3</t>
   </si>
   <si>
     <t>TC214</t>
@@ -2108,7 +2105,7 @@
     <t>TestCase_WebSales_34: Processing sales entry for Item_4</t>
   </si>
   <si>
-    <t>Sold 152 units of Item_4</t>
+    <t>Sold 328 units of Item_4</t>
   </si>
   <si>
     <t>TC215</t>
@@ -2117,7 +2114,7 @@
     <t>TestCase_WebSales_35: Processing sales entry for Item_5</t>
   </si>
   <si>
-    <t>Sold 70 units of Item_5</t>
+    <t>Sold 357 units of Item_5</t>
   </si>
   <si>
     <t>TC216</t>
@@ -2126,7 +2123,7 @@
     <t>TestCase_WebSales_36: Processing sales entry for Item_6</t>
   </si>
   <si>
-    <t>Sold 311 units of Item_6</t>
+    <t>Sold 76 units of Item_6</t>
   </si>
   <si>
     <t>TC217</t>
@@ -2135,7 +2132,7 @@
     <t>TestCase_WebSales_37: Processing sales entry for Item_7</t>
   </si>
   <si>
-    <t>Sold 238 units of Item_7</t>
+    <t>Sold 29 units of Item_7</t>
   </si>
   <si>
     <t>TC218</t>
@@ -2144,7 +2141,7 @@
     <t>TestCase_WebSales_38: Processing sales entry for Item_8</t>
   </si>
   <si>
-    <t>Sold 208 units of Item_8</t>
+    <t>Sold 404 units of Item_8</t>
   </si>
   <si>
     <t>TC219</t>
@@ -2153,7 +2150,7 @@
     <t>TestCase_WebSales_39: Processing sales entry for Item_9</t>
   </si>
   <si>
-    <t>Sold 211 units of Item_9</t>
+    <t>Sold 279 units of Item_9</t>
   </si>
   <si>
     <t>TC220</t>
@@ -2162,7 +2159,7 @@
     <t>TestCase_WebSales_40: Processing sales entry for Item_0</t>
   </si>
   <si>
-    <t>Sold 394 units of Item_0</t>
+    <t>Sold 69 units of Item_0</t>
   </si>
   <si>
     <t>TC221</t>
@@ -2171,7 +2168,7 @@
     <t>TestCase_WebSales_41: Processing sales entry for Item_1</t>
   </si>
   <si>
-    <t>Sold 83 units of Item_1</t>
+    <t>Sold 268 units of Item_1</t>
   </si>
   <si>
     <t>TC222</t>
@@ -2180,7 +2177,7 @@
     <t>TestCase_WebSales_42: Processing sales entry for Item_2</t>
   </si>
   <si>
-    <t>Sold 66 units of Item_2</t>
+    <t>Sold 5 units of Item_2</t>
   </si>
   <si>
     <t>TC223</t>
@@ -2189,7 +2186,7 @@
     <t>TestCase_WebSales_43: Processing sales entry for Item_3</t>
   </si>
   <si>
-    <t>Sold 380 units of Item_3</t>
+    <t>Sold 17 units of Item_3</t>
   </si>
   <si>
     <t>TC224</t>
@@ -2198,7 +2195,7 @@
     <t>TestCase_WebSales_44: Processing sales entry for Item_4</t>
   </si>
   <si>
-    <t>Sold 169 units of Item_4</t>
+    <t>Sold 157 units of Item_4</t>
   </si>
   <si>
     <t>TC225</t>
@@ -2207,7 +2204,7 @@
     <t>TestCase_WebSales_45: Processing sales entry for Item_5</t>
   </si>
   <si>
-    <t>Sold 35 units of Item_5</t>
+    <t>Sold 41 units of Item_5</t>
   </si>
   <si>
     <t>TC226</t>
@@ -2216,7 +2213,7 @@
     <t>TestCase_WebSales_46: Processing sales entry for Item_6</t>
   </si>
   <si>
-    <t>Sold 196 units of Item_6</t>
+    <t>Sold 425 units of Item_6</t>
   </si>
   <si>
     <t>TC227</t>
@@ -2225,7 +2222,7 @@
     <t>TestCase_WebSales_47: Processing sales entry for Item_7</t>
   </si>
   <si>
-    <t>Sold 283 units of Item_7</t>
+    <t>Sold 4 units of Item_7</t>
   </si>
   <si>
     <t>TC228</t>
@@ -2234,7 +2231,7 @@
     <t>TestCase_WebSales_48: Processing sales entry for Item_8</t>
   </si>
   <si>
-    <t>Sold 161 units of Item_8</t>
+    <t>Sold 480 units of Item_8</t>
   </si>
   <si>
     <t>TC229</t>
@@ -2243,7 +2240,7 @@
     <t>TestCase_WebSales_49: Processing sales entry for Item_9</t>
   </si>
   <si>
-    <t>Sold 219 units of Item_9</t>
+    <t>Sold 83 units of Item_9</t>
   </si>
   <si>
     <t>TC230</t>
@@ -2252,7 +2249,7 @@
     <t>TestCase_WebSales_50: Processing sales entry for Item_0</t>
   </si>
   <si>
-    <t>Sold 397 units of Item_0</t>
+    <t>Sold 136 units of Item_0</t>
   </si>
   <si>
     <t>TC231</t>
@@ -4108,7 +4105,7 @@
         <v>9</v>
       </c>
       <c r="H2" s="11">
-        <v>19</v>
+        <v>82</v>
       </c>
       <c r="I2" s="11" t="s">
         <v>1</v>
@@ -4137,7 +4134,7 @@
         <v>9</v>
       </c>
       <c r="H3" s="13">
-        <v>61</v>
+        <v>12</v>
       </c>
       <c r="I3" s="13" t="s">
         <v>1</v>
@@ -4166,7 +4163,7 @@
         <v>9</v>
       </c>
       <c r="H4" s="11">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="I4" s="11" t="s">
         <v>1</v>
@@ -4195,7 +4192,7 @@
         <v>9</v>
       </c>
       <c r="H5" s="13">
-        <v>89</v>
+        <v>56</v>
       </c>
       <c r="I5" s="13" t="s">
         <v>1</v>
@@ -4224,7 +4221,7 @@
         <v>9</v>
       </c>
       <c r="H6" s="11">
-        <v>76</v>
+        <v>60</v>
       </c>
       <c r="I6" s="11" t="s">
         <v>1</v>
@@ -4253,7 +4250,7 @@
         <v>9</v>
       </c>
       <c r="H7" s="13">
-        <v>74</v>
+        <v>48</v>
       </c>
       <c r="I7" s="13" t="s">
         <v>1</v>
@@ -4282,7 +4279,7 @@
         <v>9</v>
       </c>
       <c r="H8" s="11">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="I8" s="11" t="s">
         <v>1</v>
@@ -4311,7 +4308,7 @@
         <v>9</v>
       </c>
       <c r="H9" s="13">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="I9" s="13" t="s">
         <v>1</v>
@@ -4369,7 +4366,7 @@
         <v>9</v>
       </c>
       <c r="H11" s="13">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="I11" s="13" t="s">
         <v>1</v>
@@ -4398,7 +4395,7 @@
         <v>9</v>
       </c>
       <c r="H12" s="11">
-        <v>76</v>
+        <v>60</v>
       </c>
       <c r="I12" s="11" t="s">
         <v>1</v>
@@ -4427,7 +4424,7 @@
         <v>9</v>
       </c>
       <c r="H13" s="13">
-        <v>72</v>
+        <v>42</v>
       </c>
       <c r="I13" s="13" t="s">
         <v>1</v>
@@ -4456,7 +4453,7 @@
         <v>9</v>
       </c>
       <c r="H14" s="11">
-        <v>35</v>
+        <v>82</v>
       </c>
       <c r="I14" s="11" t="s">
         <v>1</v>
@@ -4485,7 +4482,7 @@
         <v>9</v>
       </c>
       <c r="H15" s="13">
-        <v>68</v>
+        <v>89</v>
       </c>
       <c r="I15" s="13" t="s">
         <v>1</v>
@@ -4514,7 +4511,7 @@
         <v>9</v>
       </c>
       <c r="H16" s="11">
-        <v>43</v>
+        <v>79</v>
       </c>
       <c r="I16" s="11" t="s">
         <v>1</v>
@@ -4543,7 +4540,7 @@
         <v>9</v>
       </c>
       <c r="H17" s="13">
-        <v>62</v>
+        <v>82</v>
       </c>
       <c r="I17" s="13" t="s">
         <v>1</v>
@@ -4601,7 +4598,7 @@
         <v>9</v>
       </c>
       <c r="H19" s="13">
-        <v>43</v>
+        <v>73</v>
       </c>
       <c r="I19" s="13" t="s">
         <v>1</v>
@@ -4630,7 +4627,7 @@
         <v>9</v>
       </c>
       <c r="H20" s="11">
-        <v>44</v>
+        <v>76</v>
       </c>
       <c r="I20" s="11" t="s">
         <v>1</v>
@@ -4659,7 +4656,7 @@
         <v>9</v>
       </c>
       <c r="H21" s="13">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="I21" s="13" t="s">
         <v>1</v>
@@ -4688,7 +4685,7 @@
         <v>9</v>
       </c>
       <c r="H22" s="11">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="I22" s="11" t="s">
         <v>1</v>
@@ -4717,7 +4714,7 @@
         <v>9</v>
       </c>
       <c r="H23" s="13">
-        <v>68</v>
+        <v>45</v>
       </c>
       <c r="I23" s="13" t="s">
         <v>1</v>
@@ -4746,7 +4743,7 @@
         <v>9</v>
       </c>
       <c r="H24" s="11">
-        <v>12</v>
+        <v>45</v>
       </c>
       <c r="I24" s="11" t="s">
         <v>1</v>
@@ -4775,7 +4772,7 @@
         <v>9</v>
       </c>
       <c r="H25" s="13">
-        <v>44</v>
+        <v>11</v>
       </c>
       <c r="I25" s="13" t="s">
         <v>1</v>
@@ -4804,7 +4801,7 @@
         <v>9</v>
       </c>
       <c r="H26" s="11">
-        <v>11</v>
+        <v>47</v>
       </c>
       <c r="I26" s="11" t="s">
         <v>1</v>
@@ -4833,7 +4830,7 @@
         <v>9</v>
       </c>
       <c r="H27" s="13">
-        <v>88</v>
+        <v>60</v>
       </c>
       <c r="I27" s="13" t="s">
         <v>1</v>
@@ -4862,7 +4859,7 @@
         <v>9</v>
       </c>
       <c r="H28" s="11">
-        <v>82</v>
+        <v>57</v>
       </c>
       <c r="I28" s="11" t="s">
         <v>1</v>
@@ -4891,7 +4888,7 @@
         <v>9</v>
       </c>
       <c r="H29" s="13">
-        <v>14</v>
+        <v>39</v>
       </c>
       <c r="I29" s="13" t="s">
         <v>1</v>
@@ -4920,7 +4917,7 @@
         <v>9</v>
       </c>
       <c r="H30" s="11">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="I30" s="11" t="s">
         <v>1</v>
@@ -4949,7 +4946,7 @@
         <v>9</v>
       </c>
       <c r="H31" s="13">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="I31" s="13" t="s">
         <v>1</v>
@@ -4978,7 +4975,7 @@
         <v>9</v>
       </c>
       <c r="H32" s="11">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="I32" s="11" t="s">
         <v>1</v>
@@ -5007,7 +5004,7 @@
         <v>9</v>
       </c>
       <c r="H33" s="13">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="I33" s="13" t="s">
         <v>1</v>
@@ -5036,7 +5033,7 @@
         <v>9</v>
       </c>
       <c r="H34" s="11">
-        <v>47</v>
+        <v>70</v>
       </c>
       <c r="I34" s="11" t="s">
         <v>1</v>
@@ -5065,7 +5062,7 @@
         <v>9</v>
       </c>
       <c r="H35" s="13">
-        <v>60</v>
+        <v>12</v>
       </c>
       <c r="I35" s="13" t="s">
         <v>1</v>
@@ -5094,7 +5091,7 @@
         <v>9</v>
       </c>
       <c r="H36" s="11">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="I36" s="11" t="s">
         <v>1</v>
@@ -5123,7 +5120,7 @@
         <v>9</v>
       </c>
       <c r="H37" s="13">
-        <v>21</v>
+        <v>54</v>
       </c>
       <c r="I37" s="13" t="s">
         <v>1</v>
@@ -5152,7 +5149,7 @@
         <v>9</v>
       </c>
       <c r="H38" s="11">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I38" s="11" t="s">
         <v>1</v>
@@ -5181,7 +5178,7 @@
         <v>9</v>
       </c>
       <c r="H39" s="13">
-        <v>13</v>
+        <v>88</v>
       </c>
       <c r="I39" s="13" t="s">
         <v>1</v>
@@ -5210,7 +5207,7 @@
         <v>9</v>
       </c>
       <c r="H40" s="11">
-        <v>47</v>
+        <v>77</v>
       </c>
       <c r="I40" s="11" t="s">
         <v>1</v>
@@ -5239,7 +5236,7 @@
         <v>9</v>
       </c>
       <c r="H41" s="13">
-        <v>83</v>
+        <v>21</v>
       </c>
       <c r="I41" s="13" t="s">
         <v>1</v>
@@ -5268,7 +5265,7 @@
         <v>9</v>
       </c>
       <c r="H42" s="11">
-        <v>41</v>
+        <v>73</v>
       </c>
       <c r="I42" s="11" t="s">
         <v>1</v>
@@ -5297,7 +5294,7 @@
         <v>9</v>
       </c>
       <c r="H43" s="13">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="I43" s="13" t="s">
         <v>1</v>
@@ -5326,7 +5323,7 @@
         <v>9</v>
       </c>
       <c r="H44" s="11">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="I44" s="11" t="s">
         <v>1</v>
@@ -5355,7 +5352,7 @@
         <v>9</v>
       </c>
       <c r="H45" s="13">
-        <v>51</v>
+        <v>79</v>
       </c>
       <c r="I45" s="13" t="s">
         <v>1</v>
@@ -5384,7 +5381,7 @@
         <v>9</v>
       </c>
       <c r="H46" s="11">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="I46" s="11" t="s">
         <v>1</v>
@@ -5413,7 +5410,7 @@
         <v>9</v>
       </c>
       <c r="H47" s="13">
-        <v>41</v>
+        <v>11</v>
       </c>
       <c r="I47" s="13" t="s">
         <v>1</v>
@@ -5442,7 +5439,7 @@
         <v>9</v>
       </c>
       <c r="H48" s="11">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I48" s="11" t="s">
         <v>1</v>
@@ -5471,7 +5468,7 @@
         <v>9</v>
       </c>
       <c r="H49" s="13">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="I49" s="13" t="s">
         <v>1</v>
@@ -5500,7 +5497,7 @@
         <v>9</v>
       </c>
       <c r="H50" s="11">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="I50" s="11" t="s">
         <v>1</v>
@@ -5529,7 +5526,7 @@
         <v>9</v>
       </c>
       <c r="H51" s="13">
-        <v>27</v>
+        <v>62</v>
       </c>
       <c r="I51" s="13" t="s">
         <v>1</v>
@@ -5558,7 +5555,7 @@
         <v>9</v>
       </c>
       <c r="H52" s="11">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="I52" s="11" t="s">
         <v>1</v>
@@ -5587,7 +5584,7 @@
         <v>9</v>
       </c>
       <c r="H53" s="13">
-        <v>71</v>
+        <v>12</v>
       </c>
       <c r="I53" s="13" t="s">
         <v>1</v>
@@ -5616,7 +5613,7 @@
         <v>9</v>
       </c>
       <c r="H54" s="11">
-        <v>87</v>
+        <v>62</v>
       </c>
       <c r="I54" s="11" t="s">
         <v>1</v>
@@ -5645,7 +5642,7 @@
         <v>9</v>
       </c>
       <c r="H55" s="13">
-        <v>72</v>
+        <v>57</v>
       </c>
       <c r="I55" s="13" t="s">
         <v>1</v>
@@ -5674,7 +5671,7 @@
         <v>9</v>
       </c>
       <c r="H56" s="11">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="I56" s="11" t="s">
         <v>1</v>
@@ -5703,7 +5700,7 @@
         <v>9</v>
       </c>
       <c r="H57" s="13">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="I57" s="13" t="s">
         <v>1</v>
@@ -5732,7 +5729,7 @@
         <v>9</v>
       </c>
       <c r="H58" s="11">
-        <v>57</v>
+        <v>13</v>
       </c>
       <c r="I58" s="11" t="s">
         <v>1</v>
@@ -5761,7 +5758,7 @@
         <v>9</v>
       </c>
       <c r="H59" s="13">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="I59" s="13" t="s">
         <v>1</v>
@@ -5790,7 +5787,7 @@
         <v>9</v>
       </c>
       <c r="H60" s="11">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="I60" s="11" t="s">
         <v>1</v>
@@ -5819,7 +5816,7 @@
         <v>9</v>
       </c>
       <c r="H61" s="13">
-        <v>86</v>
+        <v>49</v>
       </c>
       <c r="I61" s="13" t="s">
         <v>1</v>
@@ -5848,7 +5845,7 @@
         <v>9</v>
       </c>
       <c r="H62" s="11">
-        <v>66</v>
+        <v>12</v>
       </c>
       <c r="I62" s="11" t="s">
         <v>1</v>
@@ -5877,7 +5874,7 @@
         <v>9</v>
       </c>
       <c r="H63" s="13">
-        <v>47</v>
+        <v>79</v>
       </c>
       <c r="I63" s="13" t="s">
         <v>1</v>
@@ -5906,7 +5903,7 @@
         <v>9</v>
       </c>
       <c r="H64" s="11">
-        <v>12</v>
+        <v>46</v>
       </c>
       <c r="I64" s="11" t="s">
         <v>1</v>
@@ -5935,7 +5932,7 @@
         <v>9</v>
       </c>
       <c r="H65" s="13">
-        <v>15</v>
+        <v>74</v>
       </c>
       <c r="I65" s="13" t="s">
         <v>1</v>
@@ -5964,7 +5961,7 @@
         <v>9</v>
       </c>
       <c r="H66" s="11">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="I66" s="11" t="s">
         <v>1</v>
@@ -5993,7 +5990,7 @@
         <v>9</v>
       </c>
       <c r="H67" s="13">
-        <v>50</v>
+        <v>81</v>
       </c>
       <c r="I67" s="13" t="s">
         <v>1</v>
@@ -6022,7 +6019,7 @@
         <v>9</v>
       </c>
       <c r="H68" s="11">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="I68" s="11" t="s">
         <v>1</v>
@@ -6051,7 +6048,7 @@
         <v>9</v>
       </c>
       <c r="H69" s="13">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="I69" s="13" t="s">
         <v>1</v>
@@ -6109,7 +6106,7 @@
         <v>9</v>
       </c>
       <c r="H71" s="13">
-        <v>44</v>
+        <v>12</v>
       </c>
       <c r="I71" s="13" t="s">
         <v>1</v>
@@ -6138,7 +6135,7 @@
         <v>9</v>
       </c>
       <c r="H72" s="11">
-        <v>84</v>
+        <v>19</v>
       </c>
       <c r="I72" s="11" t="s">
         <v>1</v>
@@ -6167,7 +6164,7 @@
         <v>9</v>
       </c>
       <c r="H73" s="13">
-        <v>80</v>
+        <v>32</v>
       </c>
       <c r="I73" s="13" t="s">
         <v>1</v>
@@ -6196,7 +6193,7 @@
         <v>9</v>
       </c>
       <c r="H74" s="11">
-        <v>74</v>
+        <v>59</v>
       </c>
       <c r="I74" s="11" t="s">
         <v>1</v>
@@ -6225,7 +6222,7 @@
         <v>9</v>
       </c>
       <c r="H75" s="13">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="I75" s="13" t="s">
         <v>1</v>
@@ -6254,7 +6251,7 @@
         <v>9</v>
       </c>
       <c r="H76" s="11">
-        <v>35</v>
+        <v>81</v>
       </c>
       <c r="I76" s="11" t="s">
         <v>1</v>
@@ -6283,7 +6280,7 @@
         <v>9</v>
       </c>
       <c r="H77" s="13">
-        <v>69</v>
+        <v>11</v>
       </c>
       <c r="I77" s="13" t="s">
         <v>1</v>
@@ -6312,7 +6309,7 @@
         <v>9</v>
       </c>
       <c r="H78" s="11">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="I78" s="11" t="s">
         <v>1</v>
@@ -6341,7 +6338,7 @@
         <v>9</v>
       </c>
       <c r="H79" s="13">
-        <v>75</v>
+        <v>39</v>
       </c>
       <c r="I79" s="13" t="s">
         <v>1</v>
@@ -6370,7 +6367,7 @@
         <v>9</v>
       </c>
       <c r="H80" s="11">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="I80" s="11" t="s">
         <v>1</v>
@@ -6399,7 +6396,7 @@
         <v>9</v>
       </c>
       <c r="H81" s="13">
-        <v>80</v>
+        <v>23</v>
       </c>
       <c r="I81" s="13" t="s">
         <v>1</v>
@@ -6428,7 +6425,7 @@
         <v>9</v>
       </c>
       <c r="H82" s="11">
-        <v>59</v>
+        <v>22</v>
       </c>
       <c r="I82" s="11" t="s">
         <v>1</v>
@@ -6457,7 +6454,7 @@
         <v>9</v>
       </c>
       <c r="H83" s="13">
-        <v>38</v>
+        <v>77</v>
       </c>
       <c r="I83" s="13" t="s">
         <v>1</v>
@@ -6486,7 +6483,7 @@
         <v>9</v>
       </c>
       <c r="H84" s="11">
-        <v>87</v>
+        <v>67</v>
       </c>
       <c r="I84" s="11" t="s">
         <v>1</v>
@@ -6515,7 +6512,7 @@
         <v>9</v>
       </c>
       <c r="H85" s="13">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="I85" s="13" t="s">
         <v>1</v>
@@ -6544,7 +6541,7 @@
         <v>9</v>
       </c>
       <c r="H86" s="11">
-        <v>58</v>
+        <v>28</v>
       </c>
       <c r="I86" s="11" t="s">
         <v>1</v>
@@ -6573,7 +6570,7 @@
         <v>9</v>
       </c>
       <c r="H87" s="13">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="I87" s="13" t="s">
         <v>1</v>
@@ -6602,7 +6599,7 @@
         <v>9</v>
       </c>
       <c r="H88" s="11">
-        <v>41</v>
+        <v>85</v>
       </c>
       <c r="I88" s="11" t="s">
         <v>1</v>
@@ -6631,7 +6628,7 @@
         <v>9</v>
       </c>
       <c r="H89" s="13">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="I89" s="13" t="s">
         <v>1</v>
@@ -6660,7 +6657,7 @@
         <v>9</v>
       </c>
       <c r="H90" s="11">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="I90" s="11" t="s">
         <v>1</v>
@@ -6689,7 +6686,7 @@
         <v>9</v>
       </c>
       <c r="H91" s="13">
-        <v>64</v>
+        <v>27</v>
       </c>
       <c r="I91" s="13" t="s">
         <v>1</v>
@@ -6718,7 +6715,7 @@
         <v>9</v>
       </c>
       <c r="H92" s="11">
-        <v>66</v>
+        <v>15</v>
       </c>
       <c r="I92" s="11" t="s">
         <v>1</v>
@@ -6747,7 +6744,7 @@
         <v>9</v>
       </c>
       <c r="H93" s="13">
-        <v>49</v>
+        <v>74</v>
       </c>
       <c r="I93" s="13" t="s">
         <v>1</v>
@@ -6776,7 +6773,7 @@
         <v>9</v>
       </c>
       <c r="H94" s="11">
-        <v>80</v>
+        <v>19</v>
       </c>
       <c r="I94" s="11" t="s">
         <v>1</v>
@@ -6805,7 +6802,7 @@
         <v>9</v>
       </c>
       <c r="H95" s="13">
-        <v>81</v>
+        <v>21</v>
       </c>
       <c r="I95" s="13" t="s">
         <v>1</v>
@@ -6834,7 +6831,7 @@
         <v>9</v>
       </c>
       <c r="H96" s="11">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="I96" s="11" t="s">
         <v>1</v>
@@ -6863,7 +6860,7 @@
         <v>9</v>
       </c>
       <c r="H97" s="13">
-        <v>19</v>
+        <v>59</v>
       </c>
       <c r="I97" s="13" t="s">
         <v>1</v>
@@ -6892,7 +6889,7 @@
         <v>9</v>
       </c>
       <c r="H98" s="11">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="I98" s="11" t="s">
         <v>1</v>
@@ -6921,7 +6918,7 @@
         <v>9</v>
       </c>
       <c r="H99" s="13">
-        <v>40</v>
+        <v>63</v>
       </c>
       <c r="I99" s="13" t="s">
         <v>1</v>
@@ -6950,7 +6947,7 @@
         <v>9</v>
       </c>
       <c r="H100" s="11">
-        <v>24</v>
+        <v>72</v>
       </c>
       <c r="I100" s="11" t="s">
         <v>1</v>
@@ -6979,7 +6976,7 @@
         <v>9</v>
       </c>
       <c r="H101" s="13">
-        <v>27</v>
+        <v>67</v>
       </c>
       <c r="I101" s="13" t="s">
         <v>1</v>
@@ -7008,7 +7005,7 @@
         <v>9</v>
       </c>
       <c r="H102" s="11">
-        <v>65</v>
+        <v>15</v>
       </c>
       <c r="I102" s="11" t="s">
         <v>1</v>
@@ -7037,7 +7034,7 @@
         <v>9</v>
       </c>
       <c r="H103" s="13">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="I103" s="13" t="s">
         <v>1</v>
@@ -7066,7 +7063,7 @@
         <v>9</v>
       </c>
       <c r="H104" s="11">
-        <v>46</v>
+        <v>21</v>
       </c>
       <c r="I104" s="11" t="s">
         <v>1</v>
@@ -7095,7 +7092,7 @@
         <v>9</v>
       </c>
       <c r="H105" s="13">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="I105" s="13" t="s">
         <v>1</v>
@@ -7124,7 +7121,7 @@
         <v>9</v>
       </c>
       <c r="H106" s="11">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="I106" s="11" t="s">
         <v>1</v>
@@ -7153,7 +7150,7 @@
         <v>9</v>
       </c>
       <c r="H107" s="13">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="I107" s="13" t="s">
         <v>1</v>
@@ -7182,7 +7179,7 @@
         <v>9</v>
       </c>
       <c r="H108" s="11">
-        <v>58</v>
+        <v>24</v>
       </c>
       <c r="I108" s="11" t="s">
         <v>1</v>
@@ -7211,7 +7208,7 @@
         <v>9</v>
       </c>
       <c r="H109" s="13">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="I109" s="13" t="s">
         <v>1</v>
@@ -7240,7 +7237,7 @@
         <v>9</v>
       </c>
       <c r="H110" s="11">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="I110" s="11" t="s">
         <v>1</v>
@@ -7269,7 +7266,7 @@
         <v>9</v>
       </c>
       <c r="H111" s="13">
-        <v>37</v>
+        <v>65</v>
       </c>
       <c r="I111" s="13" t="s">
         <v>1</v>
@@ -7298,7 +7295,7 @@
         <v>9</v>
       </c>
       <c r="H112" s="11">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="I112" s="11" t="s">
         <v>1</v>
@@ -7327,7 +7324,7 @@
         <v>9</v>
       </c>
       <c r="H113" s="13">
-        <v>55</v>
+        <v>83</v>
       </c>
       <c r="I113" s="13" t="s">
         <v>1</v>
@@ -7356,7 +7353,7 @@
         <v>9</v>
       </c>
       <c r="H114" s="11">
-        <v>61</v>
+        <v>46</v>
       </c>
       <c r="I114" s="11" t="s">
         <v>1</v>
@@ -7385,7 +7382,7 @@
         <v>9</v>
       </c>
       <c r="H115" s="13">
-        <v>15</v>
+        <v>85</v>
       </c>
       <c r="I115" s="13" t="s">
         <v>1</v>
@@ -7414,7 +7411,7 @@
         <v>9</v>
       </c>
       <c r="H116" s="11">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="I116" s="11" t="s">
         <v>1</v>
@@ -7443,7 +7440,7 @@
         <v>9</v>
       </c>
       <c r="H117" s="13">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="I117" s="13" t="s">
         <v>1</v>
@@ -7472,7 +7469,7 @@
         <v>9</v>
       </c>
       <c r="H118" s="11">
-        <v>89</v>
+        <v>42</v>
       </c>
       <c r="I118" s="11" t="s">
         <v>1</v>
@@ -7501,7 +7498,7 @@
         <v>9</v>
       </c>
       <c r="H119" s="13">
-        <v>28</v>
+        <v>59</v>
       </c>
       <c r="I119" s="13" t="s">
         <v>1</v>
@@ -7530,7 +7527,7 @@
         <v>9</v>
       </c>
       <c r="H120" s="11">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="I120" s="11" t="s">
         <v>1</v>
@@ -7559,7 +7556,7 @@
         <v>9</v>
       </c>
       <c r="H121" s="13">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="I121" s="13" t="s">
         <v>1</v>
@@ -7588,7 +7585,7 @@
         <v>9</v>
       </c>
       <c r="H122" s="11">
-        <v>83</v>
+        <v>24</v>
       </c>
       <c r="I122" s="11" t="s">
         <v>1</v>
@@ -7617,7 +7614,7 @@
         <v>9</v>
       </c>
       <c r="H123" s="13">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="I123" s="13" t="s">
         <v>1</v>
@@ -7646,7 +7643,7 @@
         <v>9</v>
       </c>
       <c r="H124" s="11">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="I124" s="11" t="s">
         <v>1</v>
@@ -7675,7 +7672,7 @@
         <v>9</v>
       </c>
       <c r="H125" s="13">
-        <v>65</v>
+        <v>38</v>
       </c>
       <c r="I125" s="13" t="s">
         <v>1</v>
@@ -7704,7 +7701,7 @@
         <v>9</v>
       </c>
       <c r="H126" s="11">
-        <v>82</v>
+        <v>59</v>
       </c>
       <c r="I126" s="11" t="s">
         <v>1</v>
@@ -7733,7 +7730,7 @@
         <v>9</v>
       </c>
       <c r="H127" s="13">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="I127" s="13" t="s">
         <v>1</v>
@@ -7762,7 +7759,7 @@
         <v>9</v>
       </c>
       <c r="H128" s="11">
-        <v>73</v>
+        <v>43</v>
       </c>
       <c r="I128" s="11" t="s">
         <v>1</v>
@@ -7791,7 +7788,7 @@
         <v>9</v>
       </c>
       <c r="H129" s="13">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="I129" s="13" t="s">
         <v>1</v>
@@ -7820,7 +7817,7 @@
         <v>9</v>
       </c>
       <c r="H130" s="11">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="I130" s="11" t="s">
         <v>1</v>
@@ -7849,7 +7846,7 @@
         <v>9</v>
       </c>
       <c r="H131" s="13">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="I131" s="13" t="s">
         <v>1</v>
@@ -7878,7 +7875,7 @@
         <v>9</v>
       </c>
       <c r="H132" s="11">
-        <v>42</v>
+        <v>89</v>
       </c>
       <c r="I132" s="11" t="s">
         <v>1</v>
@@ -7907,7 +7904,7 @@
         <v>9</v>
       </c>
       <c r="H133" s="13">
-        <v>83</v>
+        <v>14</v>
       </c>
       <c r="I133" s="13" t="s">
         <v>1</v>
@@ -7936,7 +7933,7 @@
         <v>9</v>
       </c>
       <c r="H134" s="11">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="I134" s="11" t="s">
         <v>1</v>
@@ -7965,7 +7962,7 @@
         <v>9</v>
       </c>
       <c r="H135" s="13">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="I135" s="13" t="s">
         <v>1</v>
@@ -7994,7 +7991,7 @@
         <v>9</v>
       </c>
       <c r="H136" s="11">
-        <v>10</v>
+        <v>57</v>
       </c>
       <c r="I136" s="11" t="s">
         <v>1</v>
@@ -8023,7 +8020,7 @@
         <v>9</v>
       </c>
       <c r="H137" s="13">
-        <v>72</v>
+        <v>34</v>
       </c>
       <c r="I137" s="13" t="s">
         <v>1</v>
@@ -8052,7 +8049,7 @@
         <v>9</v>
       </c>
       <c r="H138" s="11">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="I138" s="11" t="s">
         <v>1</v>
@@ -8081,7 +8078,7 @@
         <v>9</v>
       </c>
       <c r="H139" s="13">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I139" s="13" t="s">
         <v>1</v>
@@ -8110,7 +8107,7 @@
         <v>9</v>
       </c>
       <c r="H140" s="11">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I140" s="11" t="s">
         <v>1</v>
@@ -8139,7 +8136,7 @@
         <v>9</v>
       </c>
       <c r="H141" s="13">
-        <v>28</v>
+        <v>67</v>
       </c>
       <c r="I141" s="13" t="s">
         <v>1</v>
@@ -8168,7 +8165,7 @@
         <v>9</v>
       </c>
       <c r="H142" s="11">
-        <v>36</v>
+        <v>16</v>
       </c>
       <c r="I142" s="11" t="s">
         <v>1</v>
@@ -8197,7 +8194,7 @@
         <v>9</v>
       </c>
       <c r="H143" s="13">
-        <v>38</v>
+        <v>16</v>
       </c>
       <c r="I143" s="13" t="s">
         <v>1</v>
@@ -8226,7 +8223,7 @@
         <v>9</v>
       </c>
       <c r="H144" s="11">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="I144" s="11" t="s">
         <v>1</v>
@@ -8255,7 +8252,7 @@
         <v>9</v>
       </c>
       <c r="H145" s="13">
-        <v>66</v>
+        <v>81</v>
       </c>
       <c r="I145" s="13" t="s">
         <v>1</v>
@@ -8284,7 +8281,7 @@
         <v>9</v>
       </c>
       <c r="H146" s="11">
-        <v>53</v>
+        <v>76</v>
       </c>
       <c r="I146" s="11" t="s">
         <v>1</v>
@@ -8313,7 +8310,7 @@
         <v>9</v>
       </c>
       <c r="H147" s="13">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="I147" s="13" t="s">
         <v>1</v>
@@ -8342,7 +8339,7 @@
         <v>9</v>
       </c>
       <c r="H148" s="11">
-        <v>10</v>
+        <v>84</v>
       </c>
       <c r="I148" s="11" t="s">
         <v>1</v>
@@ -8371,7 +8368,7 @@
         <v>9</v>
       </c>
       <c r="H149" s="13">
-        <v>70</v>
+        <v>31</v>
       </c>
       <c r="I149" s="13" t="s">
         <v>1</v>
@@ -8400,7 +8397,7 @@
         <v>9</v>
       </c>
       <c r="H150" s="11">
-        <v>64</v>
+        <v>15</v>
       </c>
       <c r="I150" s="11" t="s">
         <v>1</v>
@@ -8429,7 +8426,7 @@
         <v>9</v>
       </c>
       <c r="H151" s="13">
-        <v>23</v>
+        <v>58</v>
       </c>
       <c r="I151" s="13" t="s">
         <v>1</v>
@@ -8458,7 +8455,7 @@
         <v>9</v>
       </c>
       <c r="H152" s="11">
-        <v>15</v>
+        <v>59</v>
       </c>
       <c r="I152" s="11" t="s">
         <v>1</v>
@@ -8487,7 +8484,7 @@
         <v>9</v>
       </c>
       <c r="H153" s="13">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I153" s="13" t="s">
         <v>1</v>
@@ -8516,7 +8513,7 @@
         <v>9</v>
       </c>
       <c r="H154" s="11">
-        <v>24</v>
+        <v>51</v>
       </c>
       <c r="I154" s="11" t="s">
         <v>1</v>
@@ -8545,7 +8542,7 @@
         <v>9</v>
       </c>
       <c r="H155" s="13">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="I155" s="13" t="s">
         <v>1</v>
@@ -8574,7 +8571,7 @@
         <v>9</v>
       </c>
       <c r="H156" s="11">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="I156" s="11" t="s">
         <v>1</v>
@@ -8603,7 +8600,7 @@
         <v>9</v>
       </c>
       <c r="H157" s="13">
-        <v>48</v>
+        <v>19</v>
       </c>
       <c r="I157" s="13" t="s">
         <v>1</v>
@@ -8632,7 +8629,7 @@
         <v>9</v>
       </c>
       <c r="H158" s="11">
-        <v>28</v>
+        <v>81</v>
       </c>
       <c r="I158" s="11" t="s">
         <v>1</v>
@@ -8661,7 +8658,7 @@
         <v>9</v>
       </c>
       <c r="H159" s="13">
-        <v>53</v>
+        <v>23</v>
       </c>
       <c r="I159" s="13" t="s">
         <v>1</v>
@@ -8690,7 +8687,7 @@
         <v>9</v>
       </c>
       <c r="H160" s="11">
-        <v>50</v>
+        <v>87</v>
       </c>
       <c r="I160" s="11" t="s">
         <v>1</v>
@@ -8719,7 +8716,7 @@
         <v>9</v>
       </c>
       <c r="H161" s="13">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I161" s="13" t="s">
         <v>1</v>
@@ -8748,7 +8745,7 @@
         <v>9</v>
       </c>
       <c r="H162" s="11">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="I162" s="11" t="s">
         <v>1</v>
@@ -8777,7 +8774,7 @@
         <v>9</v>
       </c>
       <c r="H163" s="13">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="I163" s="13" t="s">
         <v>1</v>
@@ -8806,7 +8803,7 @@
         <v>9</v>
       </c>
       <c r="H164" s="11">
-        <v>46</v>
+        <v>86</v>
       </c>
       <c r="I164" s="11" t="s">
         <v>1</v>
@@ -8835,7 +8832,7 @@
         <v>9</v>
       </c>
       <c r="H165" s="13">
-        <v>19</v>
+        <v>71</v>
       </c>
       <c r="I165" s="13" t="s">
         <v>1</v>
@@ -8864,7 +8861,7 @@
         <v>9</v>
       </c>
       <c r="H166" s="11">
-        <v>73</v>
+        <v>48</v>
       </c>
       <c r="I166" s="11" t="s">
         <v>1</v>
@@ -8893,7 +8890,7 @@
         <v>9</v>
       </c>
       <c r="H167" s="13">
-        <v>73</v>
+        <v>48</v>
       </c>
       <c r="I167" s="13" t="s">
         <v>1</v>
@@ -8922,7 +8919,7 @@
         <v>9</v>
       </c>
       <c r="H168" s="11">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="I168" s="11" t="s">
         <v>1</v>
@@ -8951,7 +8948,7 @@
         <v>9</v>
       </c>
       <c r="H169" s="13">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="I169" s="13" t="s">
         <v>1</v>
@@ -8980,7 +8977,7 @@
         <v>9</v>
       </c>
       <c r="H170" s="11">
-        <v>45</v>
+        <v>11</v>
       </c>
       <c r="I170" s="11" t="s">
         <v>1</v>
@@ -9009,7 +9006,7 @@
         <v>9</v>
       </c>
       <c r="H171" s="13">
-        <v>49</v>
+        <v>74</v>
       </c>
       <c r="I171" s="13" t="s">
         <v>1</v>
@@ -9038,7 +9035,7 @@
         <v>9</v>
       </c>
       <c r="H172" s="11">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="I172" s="11" t="s">
         <v>1</v>
@@ -9067,7 +9064,7 @@
         <v>9</v>
       </c>
       <c r="H173" s="13">
-        <v>58</v>
+        <v>75</v>
       </c>
       <c r="I173" s="13" t="s">
         <v>1</v>
@@ -9096,7 +9093,7 @@
         <v>9</v>
       </c>
       <c r="H174" s="11">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="I174" s="11" t="s">
         <v>1</v>
@@ -9125,7 +9122,7 @@
         <v>9</v>
       </c>
       <c r="H175" s="13">
-        <v>63</v>
+        <v>27</v>
       </c>
       <c r="I175" s="13" t="s">
         <v>1</v>
@@ -9154,7 +9151,7 @@
         <v>9</v>
       </c>
       <c r="H176" s="11">
-        <v>71</v>
+        <v>15</v>
       </c>
       <c r="I176" s="11" t="s">
         <v>1</v>
@@ -9183,7 +9180,7 @@
         <v>9</v>
       </c>
       <c r="H177" s="13">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="I177" s="13" t="s">
         <v>1</v>
@@ -9212,7 +9209,7 @@
         <v>9</v>
       </c>
       <c r="H178" s="11">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="I178" s="11" t="s">
         <v>1</v>
@@ -9241,7 +9238,7 @@
         <v>9</v>
       </c>
       <c r="H179" s="13">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="I179" s="13" t="s">
         <v>1</v>
@@ -9270,7 +9267,7 @@
         <v>9</v>
       </c>
       <c r="H180" s="11">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="I180" s="11" t="s">
         <v>1</v>
@@ -9299,7 +9296,7 @@
         <v>9</v>
       </c>
       <c r="H181" s="13">
-        <v>82</v>
+        <v>23</v>
       </c>
       <c r="I181" s="13" t="s">
         <v>1</v>
@@ -9328,7 +9325,7 @@
         <v>9</v>
       </c>
       <c r="H182" s="11">
-        <v>89</v>
+        <v>59</v>
       </c>
       <c r="I182" s="11" t="s">
         <v>1</v>
@@ -9357,7 +9354,7 @@
         <v>9</v>
       </c>
       <c r="H183" s="13">
-        <v>31</v>
+        <v>86</v>
       </c>
       <c r="I183" s="13" t="s">
         <v>1</v>
@@ -9386,7 +9383,7 @@
         <v>9</v>
       </c>
       <c r="H184" s="11">
-        <v>69</v>
+        <v>11</v>
       </c>
       <c r="I184" s="11" t="s">
         <v>1</v>
@@ -9415,7 +9412,7 @@
         <v>9</v>
       </c>
       <c r="H185" s="13">
-        <v>14</v>
+        <v>71</v>
       </c>
       <c r="I185" s="13" t="s">
         <v>1</v>
@@ -9444,7 +9441,7 @@
         <v>9</v>
       </c>
       <c r="H186" s="11">
-        <v>36</v>
+        <v>80</v>
       </c>
       <c r="I186" s="11" t="s">
         <v>1</v>
@@ -9473,7 +9470,7 @@
         <v>9</v>
       </c>
       <c r="H187" s="13">
-        <v>18</v>
+        <v>67</v>
       </c>
       <c r="I187" s="13" t="s">
         <v>1</v>
@@ -9502,7 +9499,7 @@
         <v>9</v>
       </c>
       <c r="H188" s="11">
-        <v>69</v>
+        <v>30</v>
       </c>
       <c r="I188" s="11" t="s">
         <v>1</v>
@@ -9531,7 +9528,7 @@
         <v>9</v>
       </c>
       <c r="H189" s="13">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="I189" s="13" t="s">
         <v>1</v>
@@ -9560,7 +9557,7 @@
         <v>9</v>
       </c>
       <c r="H190" s="11">
-        <v>26</v>
+        <v>79</v>
       </c>
       <c r="I190" s="11" t="s">
         <v>1</v>
@@ -9589,7 +9586,7 @@
         <v>9</v>
       </c>
       <c r="H191" s="13">
-        <v>30</v>
+        <v>68</v>
       </c>
       <c r="I191" s="13" t="s">
         <v>1</v>
@@ -9606,7 +9603,7 @@
         <v>628</v>
       </c>
       <c r="D192" s="11" t="s">
-        <v>629</v>
+        <v>597</v>
       </c>
       <c r="E192" s="11" t="s">
         <v>598</v>
@@ -9618,7 +9615,7 @@
         <v>9</v>
       </c>
       <c r="H192" s="11">
-        <v>81</v>
+        <v>55</v>
       </c>
       <c r="I192" s="11" t="s">
         <v>1</v>
@@ -9626,16 +9623,16 @@
     </row>
     <row r="193" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A193" s="13" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="B193" s="13" t="s">
         <v>22</v>
       </c>
       <c r="C193" s="13" t="s">
+        <v>630</v>
+      </c>
+      <c r="D193" s="13" t="s">
         <v>631</v>
-      </c>
-      <c r="D193" s="13" t="s">
-        <v>632</v>
       </c>
       <c r="E193" s="13" t="s">
         <v>598</v>
@@ -9647,7 +9644,7 @@
         <v>9</v>
       </c>
       <c r="H193" s="13">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="I193" s="13" t="s">
         <v>1</v>
@@ -9655,16 +9652,16 @@
     </row>
     <row r="194" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A194" s="11" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="B194" s="11" t="s">
         <v>22</v>
       </c>
       <c r="C194" s="11" t="s">
+        <v>633</v>
+      </c>
+      <c r="D194" s="11" t="s">
         <v>634</v>
-      </c>
-      <c r="D194" s="11" t="s">
-        <v>635</v>
       </c>
       <c r="E194" s="11" t="s">
         <v>598</v>
@@ -9676,7 +9673,7 @@
         <v>9</v>
       </c>
       <c r="H194" s="11">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="I194" s="11" t="s">
         <v>1</v>
@@ -9684,16 +9681,16 @@
     </row>
     <row r="195" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A195" s="13" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="B195" s="13" t="s">
         <v>22</v>
       </c>
       <c r="C195" s="13" t="s">
+        <v>636</v>
+      </c>
+      <c r="D195" s="13" t="s">
         <v>637</v>
-      </c>
-      <c r="D195" s="13" t="s">
-        <v>638</v>
       </c>
       <c r="E195" s="13" t="s">
         <v>598</v>
@@ -9705,7 +9702,7 @@
         <v>9</v>
       </c>
       <c r="H195" s="13">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="I195" s="13" t="s">
         <v>1</v>
@@ -9713,16 +9710,16 @@
     </row>
     <row r="196" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A196" s="11" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="B196" s="11" t="s">
         <v>22</v>
       </c>
       <c r="C196" s="11" t="s">
+        <v>639</v>
+      </c>
+      <c r="D196" s="11" t="s">
         <v>640</v>
-      </c>
-      <c r="D196" s="11" t="s">
-        <v>641</v>
       </c>
       <c r="E196" s="11" t="s">
         <v>598</v>
@@ -9734,7 +9731,7 @@
         <v>9</v>
       </c>
       <c r="H196" s="11">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="I196" s="11" t="s">
         <v>1</v>
@@ -9742,16 +9739,16 @@
     </row>
     <row r="197" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A197" s="13" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="B197" s="13" t="s">
         <v>22</v>
       </c>
       <c r="C197" s="13" t="s">
+        <v>642</v>
+      </c>
+      <c r="D197" s="13" t="s">
         <v>643</v>
-      </c>
-      <c r="D197" s="13" t="s">
-        <v>644</v>
       </c>
       <c r="E197" s="13" t="s">
         <v>598</v>
@@ -9763,7 +9760,7 @@
         <v>9</v>
       </c>
       <c r="H197" s="13">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="I197" s="13" t="s">
         <v>1</v>
@@ -9771,16 +9768,16 @@
     </row>
     <row r="198" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A198" s="11" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="B198" s="11" t="s">
         <v>22</v>
       </c>
       <c r="C198" s="11" t="s">
+        <v>645</v>
+      </c>
+      <c r="D198" s="11" t="s">
         <v>646</v>
-      </c>
-      <c r="D198" s="11" t="s">
-        <v>647</v>
       </c>
       <c r="E198" s="11" t="s">
         <v>598</v>
@@ -9792,7 +9789,7 @@
         <v>9</v>
       </c>
       <c r="H198" s="11">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="I198" s="11" t="s">
         <v>1</v>
@@ -9800,16 +9797,16 @@
     </row>
     <row r="199" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A199" s="13" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="B199" s="13" t="s">
         <v>22</v>
       </c>
       <c r="C199" s="13" t="s">
+        <v>648</v>
+      </c>
+      <c r="D199" s="13" t="s">
         <v>649</v>
-      </c>
-      <c r="D199" s="13" t="s">
-        <v>650</v>
       </c>
       <c r="E199" s="13" t="s">
         <v>598</v>
@@ -9821,7 +9818,7 @@
         <v>9</v>
       </c>
       <c r="H199" s="13">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="I199" s="13" t="s">
         <v>1</v>
@@ -9829,16 +9826,16 @@
     </row>
     <row r="200" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A200" s="11" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="B200" s="11" t="s">
         <v>22</v>
       </c>
       <c r="C200" s="11" t="s">
+        <v>651</v>
+      </c>
+      <c r="D200" s="11" t="s">
         <v>652</v>
-      </c>
-      <c r="D200" s="11" t="s">
-        <v>653</v>
       </c>
       <c r="E200" s="11" t="s">
         <v>598</v>
@@ -9850,7 +9847,7 @@
         <v>9</v>
       </c>
       <c r="H200" s="11">
-        <v>72</v>
+        <v>38</v>
       </c>
       <c r="I200" s="11" t="s">
         <v>1</v>
@@ -9858,16 +9855,16 @@
     </row>
     <row r="201" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A201" s="13" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="B201" s="13" t="s">
         <v>22</v>
       </c>
       <c r="C201" s="13" t="s">
+        <v>654</v>
+      </c>
+      <c r="D201" s="13" t="s">
         <v>655</v>
-      </c>
-      <c r="D201" s="13" t="s">
-        <v>656</v>
       </c>
       <c r="E201" s="13" t="s">
         <v>598</v>
@@ -9879,7 +9876,7 @@
         <v>9</v>
       </c>
       <c r="H201" s="13">
-        <v>79</v>
+        <v>53</v>
       </c>
       <c r="I201" s="13" t="s">
         <v>1</v>
@@ -9887,16 +9884,16 @@
     </row>
     <row r="202" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A202" s="11" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="B202" s="11" t="s">
         <v>22</v>
       </c>
       <c r="C202" s="11" t="s">
+        <v>657</v>
+      </c>
+      <c r="D202" s="11" t="s">
         <v>658</v>
-      </c>
-      <c r="D202" s="11" t="s">
-        <v>659</v>
       </c>
       <c r="E202" s="11" t="s">
         <v>598</v>
@@ -9908,7 +9905,7 @@
         <v>9</v>
       </c>
       <c r="H202" s="11">
-        <v>47</v>
+        <v>67</v>
       </c>
       <c r="I202" s="11" t="s">
         <v>1</v>
@@ -9916,16 +9913,16 @@
     </row>
     <row r="203" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A203" s="13" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="B203" s="13" t="s">
         <v>22</v>
       </c>
       <c r="C203" s="13" t="s">
+        <v>660</v>
+      </c>
+      <c r="D203" s="13" t="s">
         <v>661</v>
-      </c>
-      <c r="D203" s="13" t="s">
-        <v>662</v>
       </c>
       <c r="E203" s="13" t="s">
         <v>598</v>
@@ -9937,7 +9934,7 @@
         <v>9</v>
       </c>
       <c r="H203" s="13">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="I203" s="13" t="s">
         <v>1</v>
@@ -9945,16 +9942,16 @@
     </row>
     <row r="204" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A204" s="11" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="B204" s="11" t="s">
         <v>22</v>
       </c>
       <c r="C204" s="11" t="s">
+        <v>663</v>
+      </c>
+      <c r="D204" s="11" t="s">
         <v>664</v>
-      </c>
-      <c r="D204" s="11" t="s">
-        <v>665</v>
       </c>
       <c r="E204" s="11" t="s">
         <v>598</v>
@@ -9966,7 +9963,7 @@
         <v>9</v>
       </c>
       <c r="H204" s="11">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="I204" s="11" t="s">
         <v>1</v>
@@ -9974,16 +9971,16 @@
     </row>
     <row r="205" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A205" s="13" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="B205" s="13" t="s">
         <v>22</v>
       </c>
       <c r="C205" s="13" t="s">
+        <v>666</v>
+      </c>
+      <c r="D205" s="13" t="s">
         <v>667</v>
-      </c>
-      <c r="D205" s="13" t="s">
-        <v>668</v>
       </c>
       <c r="E205" s="13" t="s">
         <v>598</v>
@@ -9995,7 +9992,7 @@
         <v>9</v>
       </c>
       <c r="H205" s="13">
-        <v>83</v>
+        <v>33</v>
       </c>
       <c r="I205" s="13" t="s">
         <v>1</v>
@@ -10003,16 +10000,16 @@
     </row>
     <row r="206" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A206" s="11" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="B206" s="11" t="s">
         <v>22</v>
       </c>
       <c r="C206" s="11" t="s">
+        <v>669</v>
+      </c>
+      <c r="D206" s="11" t="s">
         <v>670</v>
-      </c>
-      <c r="D206" s="11" t="s">
-        <v>671</v>
       </c>
       <c r="E206" s="11" t="s">
         <v>598</v>
@@ -10024,7 +10021,7 @@
         <v>9</v>
       </c>
       <c r="H206" s="11">
-        <v>36</v>
+        <v>74</v>
       </c>
       <c r="I206" s="11" t="s">
         <v>1</v>
@@ -10032,16 +10029,16 @@
     </row>
     <row r="207" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A207" s="13" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="B207" s="13" t="s">
         <v>22</v>
       </c>
       <c r="C207" s="13" t="s">
+        <v>672</v>
+      </c>
+      <c r="D207" s="13" t="s">
         <v>673</v>
-      </c>
-      <c r="D207" s="13" t="s">
-        <v>674</v>
       </c>
       <c r="E207" s="13" t="s">
         <v>598</v>
@@ -10053,7 +10050,7 @@
         <v>9</v>
       </c>
       <c r="H207" s="13">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I207" s="13" t="s">
         <v>1</v>
@@ -10061,16 +10058,16 @@
     </row>
     <row r="208" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A208" s="11" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="B208" s="11" t="s">
         <v>22</v>
       </c>
       <c r="C208" s="11" t="s">
+        <v>675</v>
+      </c>
+      <c r="D208" s="11" t="s">
         <v>676</v>
-      </c>
-      <c r="D208" s="11" t="s">
-        <v>677</v>
       </c>
       <c r="E208" s="11" t="s">
         <v>598</v>
@@ -10082,7 +10079,7 @@
         <v>9</v>
       </c>
       <c r="H208" s="11">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="I208" s="11" t="s">
         <v>1</v>
@@ -10090,16 +10087,16 @@
     </row>
     <row r="209" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A209" s="13" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="B209" s="13" t="s">
         <v>22</v>
       </c>
       <c r="C209" s="13" t="s">
+        <v>678</v>
+      </c>
+      <c r="D209" s="13" t="s">
         <v>679</v>
-      </c>
-      <c r="D209" s="13" t="s">
-        <v>680</v>
       </c>
       <c r="E209" s="13" t="s">
         <v>598</v>
@@ -10111,7 +10108,7 @@
         <v>9</v>
       </c>
       <c r="H209" s="13">
-        <v>10</v>
+        <v>87</v>
       </c>
       <c r="I209" s="13" t="s">
         <v>1</v>
@@ -10119,16 +10116,16 @@
     </row>
     <row r="210" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A210" s="11" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="B210" s="11" t="s">
         <v>22</v>
       </c>
       <c r="C210" s="11" t="s">
+        <v>681</v>
+      </c>
+      <c r="D210" s="11" t="s">
         <v>682</v>
-      </c>
-      <c r="D210" s="11" t="s">
-        <v>683</v>
       </c>
       <c r="E210" s="11" t="s">
         <v>598</v>
@@ -10140,7 +10137,7 @@
         <v>9</v>
       </c>
       <c r="H210" s="11">
-        <v>19</v>
+        <v>54</v>
       </c>
       <c r="I210" s="11" t="s">
         <v>1</v>
@@ -10148,16 +10145,16 @@
     </row>
     <row r="211" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A211" s="13" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B211" s="13" t="s">
         <v>22</v>
       </c>
       <c r="C211" s="13" t="s">
+        <v>684</v>
+      </c>
+      <c r="D211" s="13" t="s">
         <v>685</v>
-      </c>
-      <c r="D211" s="13" t="s">
-        <v>686</v>
       </c>
       <c r="E211" s="13" t="s">
         <v>598</v>
@@ -10169,7 +10166,7 @@
         <v>9</v>
       </c>
       <c r="H211" s="13">
-        <v>60</v>
+        <v>19</v>
       </c>
       <c r="I211" s="13" t="s">
         <v>1</v>
@@ -10177,16 +10174,16 @@
     </row>
     <row r="212" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A212" s="11" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="B212" s="11" t="s">
         <v>22</v>
       </c>
       <c r="C212" s="11" t="s">
+        <v>687</v>
+      </c>
+      <c r="D212" s="11" t="s">
         <v>688</v>
-      </c>
-      <c r="D212" s="11" t="s">
-        <v>689</v>
       </c>
       <c r="E212" s="11" t="s">
         <v>598</v>
@@ -10198,7 +10195,7 @@
         <v>9</v>
       </c>
       <c r="H212" s="11">
-        <v>43</v>
+        <v>72</v>
       </c>
       <c r="I212" s="11" t="s">
         <v>1</v>
@@ -10206,16 +10203,16 @@
     </row>
     <row r="213" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A213" s="13" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B213" s="13" t="s">
         <v>22</v>
       </c>
       <c r="C213" s="13" t="s">
+        <v>690</v>
+      </c>
+      <c r="D213" s="13" t="s">
         <v>691</v>
-      </c>
-      <c r="D213" s="13" t="s">
-        <v>692</v>
       </c>
       <c r="E213" s="13" t="s">
         <v>598</v>
@@ -10227,7 +10224,7 @@
         <v>9</v>
       </c>
       <c r="H213" s="13">
-        <v>74</v>
+        <v>14</v>
       </c>
       <c r="I213" s="13" t="s">
         <v>1</v>
@@ -10235,16 +10232,16 @@
     </row>
     <row r="214" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A214" s="11" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="B214" s="11" t="s">
         <v>22</v>
       </c>
       <c r="C214" s="11" t="s">
+        <v>693</v>
+      </c>
+      <c r="D214" s="11" t="s">
         <v>694</v>
-      </c>
-      <c r="D214" s="11" t="s">
-        <v>695</v>
       </c>
       <c r="E214" s="11" t="s">
         <v>598</v>
@@ -10256,7 +10253,7 @@
         <v>9</v>
       </c>
       <c r="H214" s="11">
-        <v>59</v>
+        <v>38</v>
       </c>
       <c r="I214" s="11" t="s">
         <v>1</v>
@@ -10264,16 +10261,16 @@
     </row>
     <row r="215" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A215" s="13" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="B215" s="13" t="s">
         <v>22</v>
       </c>
       <c r="C215" s="13" t="s">
+        <v>696</v>
+      </c>
+      <c r="D215" s="13" t="s">
         <v>697</v>
-      </c>
-      <c r="D215" s="13" t="s">
-        <v>698</v>
       </c>
       <c r="E215" s="13" t="s">
         <v>598</v>
@@ -10285,7 +10282,7 @@
         <v>9</v>
       </c>
       <c r="H215" s="13">
-        <v>37</v>
+        <v>78</v>
       </c>
       <c r="I215" s="13" t="s">
         <v>1</v>
@@ -10293,16 +10290,16 @@
     </row>
     <row r="216" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A216" s="11" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="B216" s="11" t="s">
         <v>22</v>
       </c>
       <c r="C216" s="11" t="s">
+        <v>699</v>
+      </c>
+      <c r="D216" s="11" t="s">
         <v>700</v>
-      </c>
-      <c r="D216" s="11" t="s">
-        <v>701</v>
       </c>
       <c r="E216" s="11" t="s">
         <v>598</v>
@@ -10314,7 +10311,7 @@
         <v>9</v>
       </c>
       <c r="H216" s="11">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I216" s="11" t="s">
         <v>1</v>
@@ -10322,16 +10319,16 @@
     </row>
     <row r="217" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A217" s="13" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="B217" s="13" t="s">
         <v>22</v>
       </c>
       <c r="C217" s="13" t="s">
+        <v>702</v>
+      </c>
+      <c r="D217" s="13" t="s">
         <v>703</v>
-      </c>
-      <c r="D217" s="13" t="s">
-        <v>704</v>
       </c>
       <c r="E217" s="13" t="s">
         <v>598</v>
@@ -10343,7 +10340,7 @@
         <v>9</v>
       </c>
       <c r="H217" s="13">
-        <v>52</v>
+        <v>73</v>
       </c>
       <c r="I217" s="13" t="s">
         <v>1</v>
@@ -10351,16 +10348,16 @@
     </row>
     <row r="218" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A218" s="11" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="B218" s="11" t="s">
         <v>22</v>
       </c>
       <c r="C218" s="11" t="s">
+        <v>705</v>
+      </c>
+      <c r="D218" s="11" t="s">
         <v>706</v>
-      </c>
-      <c r="D218" s="11" t="s">
-        <v>707</v>
       </c>
       <c r="E218" s="11" t="s">
         <v>598</v>
@@ -10372,7 +10369,7 @@
         <v>9</v>
       </c>
       <c r="H218" s="11">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="I218" s="11" t="s">
         <v>1</v>
@@ -10380,16 +10377,16 @@
     </row>
     <row r="219" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A219" s="13" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="B219" s="13" t="s">
         <v>22</v>
       </c>
       <c r="C219" s="13" t="s">
+        <v>708</v>
+      </c>
+      <c r="D219" s="13" t="s">
         <v>709</v>
-      </c>
-      <c r="D219" s="13" t="s">
-        <v>710</v>
       </c>
       <c r="E219" s="13" t="s">
         <v>598</v>
@@ -10401,7 +10398,7 @@
         <v>9</v>
       </c>
       <c r="H219" s="13">
-        <v>72</v>
+        <v>59</v>
       </c>
       <c r="I219" s="13" t="s">
         <v>1</v>
@@ -10409,16 +10406,16 @@
     </row>
     <row r="220" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A220" s="11" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="B220" s="11" t="s">
         <v>22</v>
       </c>
       <c r="C220" s="11" t="s">
+        <v>711</v>
+      </c>
+      <c r="D220" s="11" t="s">
         <v>712</v>
-      </c>
-      <c r="D220" s="11" t="s">
-        <v>713</v>
       </c>
       <c r="E220" s="11" t="s">
         <v>598</v>
@@ -10430,7 +10427,7 @@
         <v>9</v>
       </c>
       <c r="H220" s="11">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="I220" s="11" t="s">
         <v>1</v>
@@ -10438,16 +10435,16 @@
     </row>
     <row r="221" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A221" s="13" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="B221" s="13" t="s">
         <v>22</v>
       </c>
       <c r="C221" s="13" t="s">
+        <v>714</v>
+      </c>
+      <c r="D221" s="13" t="s">
         <v>715</v>
-      </c>
-      <c r="D221" s="13" t="s">
-        <v>716</v>
       </c>
       <c r="E221" s="13" t="s">
         <v>598</v>
@@ -10459,7 +10456,7 @@
         <v>9</v>
       </c>
       <c r="H221" s="13">
-        <v>82</v>
+        <v>44</v>
       </c>
       <c r="I221" s="13" t="s">
         <v>1</v>
@@ -10467,16 +10464,16 @@
     </row>
     <row r="222" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A222" s="11" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="B222" s="11" t="s">
         <v>22</v>
       </c>
       <c r="C222" s="11" t="s">
+        <v>717</v>
+      </c>
+      <c r="D222" s="11" t="s">
         <v>718</v>
-      </c>
-      <c r="D222" s="11" t="s">
-        <v>719</v>
       </c>
       <c r="E222" s="11" t="s">
         <v>598</v>
@@ -10488,7 +10485,7 @@
         <v>9</v>
       </c>
       <c r="H222" s="11">
-        <v>59</v>
+        <v>21</v>
       </c>
       <c r="I222" s="11" t="s">
         <v>1</v>
@@ -10496,16 +10493,16 @@
     </row>
     <row r="223" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A223" s="13" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="B223" s="13" t="s">
         <v>22</v>
       </c>
       <c r="C223" s="13" t="s">
+        <v>720</v>
+      </c>
+      <c r="D223" s="13" t="s">
         <v>721</v>
-      </c>
-      <c r="D223" s="13" t="s">
-        <v>722</v>
       </c>
       <c r="E223" s="13" t="s">
         <v>598</v>
@@ -10517,7 +10514,7 @@
         <v>9</v>
       </c>
       <c r="H223" s="13">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="I223" s="13" t="s">
         <v>1</v>
@@ -10525,16 +10522,16 @@
     </row>
     <row r="224" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A224" s="11" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="B224" s="11" t="s">
         <v>22</v>
       </c>
       <c r="C224" s="11" t="s">
+        <v>723</v>
+      </c>
+      <c r="D224" s="11" t="s">
         <v>724</v>
-      </c>
-      <c r="D224" s="11" t="s">
-        <v>725</v>
       </c>
       <c r="E224" s="11" t="s">
         <v>598</v>
@@ -10546,7 +10543,7 @@
         <v>9</v>
       </c>
       <c r="H224" s="11">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="I224" s="11" t="s">
         <v>1</v>
@@ -10554,16 +10551,16 @@
     </row>
     <row r="225" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A225" s="13" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="B225" s="13" t="s">
         <v>22</v>
       </c>
       <c r="C225" s="13" t="s">
+        <v>726</v>
+      </c>
+      <c r="D225" s="13" t="s">
         <v>727</v>
-      </c>
-      <c r="D225" s="13" t="s">
-        <v>728</v>
       </c>
       <c r="E225" s="13" t="s">
         <v>598</v>
@@ -10575,7 +10572,7 @@
         <v>9</v>
       </c>
       <c r="H225" s="13">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="I225" s="13" t="s">
         <v>1</v>
@@ -10583,16 +10580,16 @@
     </row>
     <row r="226" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A226" s="11" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="B226" s="11" t="s">
         <v>22</v>
       </c>
       <c r="C226" s="11" t="s">
+        <v>729</v>
+      </c>
+      <c r="D226" s="11" t="s">
         <v>730</v>
-      </c>
-      <c r="D226" s="11" t="s">
-        <v>731</v>
       </c>
       <c r="E226" s="11" t="s">
         <v>598</v>
@@ -10604,7 +10601,7 @@
         <v>9</v>
       </c>
       <c r="H226" s="11">
-        <v>59</v>
+        <v>10</v>
       </c>
       <c r="I226" s="11" t="s">
         <v>1</v>
@@ -10612,16 +10609,16 @@
     </row>
     <row r="227" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A227" s="13" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="B227" s="13" t="s">
         <v>22</v>
       </c>
       <c r="C227" s="13" t="s">
+        <v>732</v>
+      </c>
+      <c r="D227" s="13" t="s">
         <v>733</v>
-      </c>
-      <c r="D227" s="13" t="s">
-        <v>734</v>
       </c>
       <c r="E227" s="13" t="s">
         <v>598</v>
@@ -10633,7 +10630,7 @@
         <v>9</v>
       </c>
       <c r="H227" s="13">
-        <v>80</v>
+        <v>31</v>
       </c>
       <c r="I227" s="13" t="s">
         <v>1</v>
@@ -10641,16 +10638,16 @@
     </row>
     <row r="228" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A228" s="11" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="B228" s="11" t="s">
         <v>22</v>
       </c>
       <c r="C228" s="11" t="s">
+        <v>735</v>
+      </c>
+      <c r="D228" s="11" t="s">
         <v>736</v>
-      </c>
-      <c r="D228" s="11" t="s">
-        <v>737</v>
       </c>
       <c r="E228" s="11" t="s">
         <v>598</v>
@@ -10662,7 +10659,7 @@
         <v>9</v>
       </c>
       <c r="H228" s="11">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="I228" s="11" t="s">
         <v>1</v>
@@ -10670,16 +10667,16 @@
     </row>
     <row r="229" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A229" s="13" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="B229" s="13" t="s">
         <v>22</v>
       </c>
       <c r="C229" s="13" t="s">
+        <v>738</v>
+      </c>
+      <c r="D229" s="13" t="s">
         <v>739</v>
-      </c>
-      <c r="D229" s="13" t="s">
-        <v>740</v>
       </c>
       <c r="E229" s="13" t="s">
         <v>598</v>
@@ -10691,7 +10688,7 @@
         <v>9</v>
       </c>
       <c r="H229" s="13">
-        <v>78</v>
+        <v>62</v>
       </c>
       <c r="I229" s="13" t="s">
         <v>1</v>
@@ -10699,16 +10696,16 @@
     </row>
     <row r="230" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A230" s="11" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="B230" s="11" t="s">
         <v>22</v>
       </c>
       <c r="C230" s="11" t="s">
+        <v>741</v>
+      </c>
+      <c r="D230" s="11" t="s">
         <v>742</v>
-      </c>
-      <c r="D230" s="11" t="s">
-        <v>743</v>
       </c>
       <c r="E230" s="11" t="s">
         <v>598</v>
@@ -10720,7 +10717,7 @@
         <v>9</v>
       </c>
       <c r="H230" s="11">
-        <v>26</v>
+        <v>83</v>
       </c>
       <c r="I230" s="11" t="s">
         <v>1</v>
@@ -10728,16 +10725,16 @@
     </row>
     <row r="231" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A231" s="13" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="B231" s="13" t="s">
         <v>22</v>
       </c>
       <c r="C231" s="13" t="s">
+        <v>744</v>
+      </c>
+      <c r="D231" s="13" t="s">
         <v>745</v>
-      </c>
-      <c r="D231" s="13" t="s">
-        <v>746</v>
       </c>
       <c r="E231" s="13" t="s">
         <v>598</v>
@@ -10749,7 +10746,7 @@
         <v>9</v>
       </c>
       <c r="H231" s="13">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="I231" s="13" t="s">
         <v>1</v>
@@ -10757,28 +10754,28 @@
     </row>
     <row r="232" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A232" s="11" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="B232" s="11" t="s">
         <v>23</v>
       </c>
       <c r="C232" s="11" t="s">
+        <v>747</v>
+      </c>
+      <c r="D232" s="11" t="s">
         <v>748</v>
       </c>
-      <c r="D232" s="11" t="s">
+      <c r="E232" s="11" t="s">
         <v>749</v>
       </c>
-      <c r="E232" s="11" t="s">
+      <c r="F232" s="11" t="s">
         <v>750</v>
       </c>
-      <c r="F232" s="11" t="s">
-        <v>751</v>
-      </c>
       <c r="G232" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H232" s="11">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="I232" s="11" t="s">
         <v>1</v>
@@ -10786,28 +10783,28 @@
     </row>
     <row r="233" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A233" s="13" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="B233" s="13" t="s">
         <v>23</v>
       </c>
       <c r="C233" s="13" t="s">
+        <v>752</v>
+      </c>
+      <c r="D233" s="13" t="s">
         <v>753</v>
       </c>
-      <c r="D233" s="13" t="s">
-        <v>754</v>
-      </c>
       <c r="E233" s="13" t="s">
+        <v>749</v>
+      </c>
+      <c r="F233" s="13" t="s">
         <v>750</v>
       </c>
-      <c r="F233" s="13" t="s">
-        <v>751</v>
-      </c>
       <c r="G233" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H233" s="13">
-        <v>54</v>
+        <v>24</v>
       </c>
       <c r="I233" s="13" t="s">
         <v>1</v>
@@ -10815,28 +10812,28 @@
     </row>
     <row r="234" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A234" s="11" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="B234" s="11" t="s">
         <v>23</v>
       </c>
       <c r="C234" s="11" t="s">
+        <v>755</v>
+      </c>
+      <c r="D234" s="11" t="s">
         <v>756</v>
       </c>
-      <c r="D234" s="11" t="s">
-        <v>757</v>
-      </c>
       <c r="E234" s="11" t="s">
+        <v>749</v>
+      </c>
+      <c r="F234" s="11" t="s">
         <v>750</v>
       </c>
-      <c r="F234" s="11" t="s">
-        <v>751</v>
-      </c>
       <c r="G234" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H234" s="11">
-        <v>78</v>
+        <v>35</v>
       </c>
       <c r="I234" s="11" t="s">
         <v>1</v>
@@ -10844,28 +10841,28 @@
     </row>
     <row r="235" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A235" s="13" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="B235" s="13" t="s">
         <v>23</v>
       </c>
       <c r="C235" s="13" t="s">
+        <v>758</v>
+      </c>
+      <c r="D235" s="13" t="s">
         <v>759</v>
       </c>
-      <c r="D235" s="13" t="s">
-        <v>760</v>
-      </c>
       <c r="E235" s="13" t="s">
+        <v>749</v>
+      </c>
+      <c r="F235" s="13" t="s">
         <v>750</v>
       </c>
-      <c r="F235" s="13" t="s">
-        <v>751</v>
-      </c>
       <c r="G235" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H235" s="13">
-        <v>14</v>
+        <v>52</v>
       </c>
       <c r="I235" s="13" t="s">
         <v>1</v>
@@ -10873,28 +10870,28 @@
     </row>
     <row r="236" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A236" s="11" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="B236" s="11" t="s">
         <v>23</v>
       </c>
       <c r="C236" s="11" t="s">
+        <v>761</v>
+      </c>
+      <c r="D236" s="11" t="s">
         <v>762</v>
       </c>
-      <c r="D236" s="11" t="s">
-        <v>763</v>
-      </c>
       <c r="E236" s="11" t="s">
+        <v>749</v>
+      </c>
+      <c r="F236" s="11" t="s">
         <v>750</v>
       </c>
-      <c r="F236" s="11" t="s">
-        <v>751</v>
-      </c>
       <c r="G236" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H236" s="11">
-        <v>56</v>
+        <v>10</v>
       </c>
       <c r="I236" s="11" t="s">
         <v>1</v>
@@ -10902,28 +10899,28 @@
     </row>
     <row r="237" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A237" s="13" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="B237" s="13" t="s">
         <v>23</v>
       </c>
       <c r="C237" s="13" t="s">
+        <v>764</v>
+      </c>
+      <c r="D237" s="13" t="s">
         <v>765</v>
       </c>
-      <c r="D237" s="13" t="s">
-        <v>766</v>
-      </c>
       <c r="E237" s="13" t="s">
+        <v>749</v>
+      </c>
+      <c r="F237" s="13" t="s">
         <v>750</v>
       </c>
-      <c r="F237" s="13" t="s">
-        <v>751</v>
-      </c>
       <c r="G237" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H237" s="13">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="I237" s="13" t="s">
         <v>1</v>
@@ -10931,28 +10928,28 @@
     </row>
     <row r="238" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A238" s="11" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="B238" s="11" t="s">
         <v>23</v>
       </c>
       <c r="C238" s="11" t="s">
+        <v>767</v>
+      </c>
+      <c r="D238" s="11" t="s">
         <v>768</v>
       </c>
-      <c r="D238" s="11" t="s">
-        <v>769</v>
-      </c>
       <c r="E238" s="11" t="s">
+        <v>749</v>
+      </c>
+      <c r="F238" s="11" t="s">
         <v>750</v>
       </c>
-      <c r="F238" s="11" t="s">
-        <v>751</v>
-      </c>
       <c r="G238" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H238" s="11">
-        <v>83</v>
+        <v>11</v>
       </c>
       <c r="I238" s="11" t="s">
         <v>1</v>
@@ -10960,28 +10957,28 @@
     </row>
     <row r="239" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A239" s="13" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="B239" s="13" t="s">
         <v>23</v>
       </c>
       <c r="C239" s="13" t="s">
+        <v>770</v>
+      </c>
+      <c r="D239" s="13" t="s">
         <v>771</v>
       </c>
-      <c r="D239" s="13" t="s">
-        <v>772</v>
-      </c>
       <c r="E239" s="13" t="s">
+        <v>749</v>
+      </c>
+      <c r="F239" s="13" t="s">
         <v>750</v>
       </c>
-      <c r="F239" s="13" t="s">
-        <v>751</v>
-      </c>
       <c r="G239" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H239" s="13">
-        <v>83</v>
+        <v>64</v>
       </c>
       <c r="I239" s="13" t="s">
         <v>1</v>
@@ -10989,28 +10986,28 @@
     </row>
     <row r="240" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A240" s="11" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="B240" s="11" t="s">
         <v>23</v>
       </c>
       <c r="C240" s="11" t="s">
+        <v>773</v>
+      </c>
+      <c r="D240" s="11" t="s">
         <v>774</v>
       </c>
-      <c r="D240" s="11" t="s">
-        <v>775</v>
-      </c>
       <c r="E240" s="11" t="s">
+        <v>749</v>
+      </c>
+      <c r="F240" s="11" t="s">
         <v>750</v>
       </c>
-      <c r="F240" s="11" t="s">
-        <v>751</v>
-      </c>
       <c r="G240" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H240" s="11">
-        <v>82</v>
+        <v>49</v>
       </c>
       <c r="I240" s="11" t="s">
         <v>1</v>
@@ -11018,28 +11015,28 @@
     </row>
     <row r="241" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A241" s="13" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="B241" s="13" t="s">
         <v>23</v>
       </c>
       <c r="C241" s="13" t="s">
+        <v>776</v>
+      </c>
+      <c r="D241" s="13" t="s">
         <v>777</v>
       </c>
-      <c r="D241" s="13" t="s">
-        <v>778</v>
-      </c>
       <c r="E241" s="13" t="s">
+        <v>749</v>
+      </c>
+      <c r="F241" s="13" t="s">
         <v>750</v>
       </c>
-      <c r="F241" s="13" t="s">
-        <v>751</v>
-      </c>
       <c r="G241" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H241" s="13">
-        <v>25</v>
+        <v>88</v>
       </c>
       <c r="I241" s="13" t="s">
         <v>1</v>
@@ -11047,28 +11044,28 @@
     </row>
     <row r="242" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A242" s="11" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="B242" s="11" t="s">
         <v>23</v>
       </c>
       <c r="C242" s="11" t="s">
+        <v>779</v>
+      </c>
+      <c r="D242" s="11" t="s">
         <v>780</v>
       </c>
-      <c r="D242" s="11" t="s">
-        <v>781</v>
-      </c>
       <c r="E242" s="11" t="s">
+        <v>749</v>
+      </c>
+      <c r="F242" s="11" t="s">
         <v>750</v>
       </c>
-      <c r="F242" s="11" t="s">
-        <v>751</v>
-      </c>
       <c r="G242" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H242" s="11">
-        <v>36</v>
+        <v>86</v>
       </c>
       <c r="I242" s="11" t="s">
         <v>1</v>
@@ -11076,28 +11073,28 @@
     </row>
     <row r="243" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A243" s="13" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="B243" s="13" t="s">
         <v>23</v>
       </c>
       <c r="C243" s="13" t="s">
+        <v>782</v>
+      </c>
+      <c r="D243" s="13" t="s">
         <v>783</v>
       </c>
-      <c r="D243" s="13" t="s">
-        <v>784</v>
-      </c>
       <c r="E243" s="13" t="s">
+        <v>749</v>
+      </c>
+      <c r="F243" s="13" t="s">
         <v>750</v>
       </c>
-      <c r="F243" s="13" t="s">
-        <v>751</v>
-      </c>
       <c r="G243" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H243" s="13">
-        <v>27</v>
+        <v>86</v>
       </c>
       <c r="I243" s="13" t="s">
         <v>1</v>
@@ -11105,28 +11102,28 @@
     </row>
     <row r="244" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A244" s="11" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="B244" s="11" t="s">
         <v>23</v>
       </c>
       <c r="C244" s="11" t="s">
+        <v>785</v>
+      </c>
+      <c r="D244" s="11" t="s">
         <v>786</v>
       </c>
-      <c r="D244" s="11" t="s">
-        <v>787</v>
-      </c>
       <c r="E244" s="11" t="s">
+        <v>749</v>
+      </c>
+      <c r="F244" s="11" t="s">
         <v>750</v>
       </c>
-      <c r="F244" s="11" t="s">
-        <v>751</v>
-      </c>
       <c r="G244" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H244" s="11">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="I244" s="11" t="s">
         <v>1</v>
@@ -11134,28 +11131,28 @@
     </row>
     <row r="245" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A245" s="13" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="B245" s="13" t="s">
         <v>23</v>
       </c>
       <c r="C245" s="13" t="s">
+        <v>788</v>
+      </c>
+      <c r="D245" s="13" t="s">
         <v>789</v>
       </c>
-      <c r="D245" s="13" t="s">
-        <v>790</v>
-      </c>
       <c r="E245" s="13" t="s">
+        <v>749</v>
+      </c>
+      <c r="F245" s="13" t="s">
         <v>750</v>
       </c>
-      <c r="F245" s="13" t="s">
-        <v>751</v>
-      </c>
       <c r="G245" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H245" s="13">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="I245" s="13" t="s">
         <v>1</v>
@@ -11163,28 +11160,28 @@
     </row>
     <row r="246" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A246" s="11" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="B246" s="11" t="s">
         <v>23</v>
       </c>
       <c r="C246" s="11" t="s">
+        <v>791</v>
+      </c>
+      <c r="D246" s="11" t="s">
         <v>792</v>
       </c>
-      <c r="D246" s="11" t="s">
-        <v>793</v>
-      </c>
       <c r="E246" s="11" t="s">
+        <v>749</v>
+      </c>
+      <c r="F246" s="11" t="s">
         <v>750</v>
       </c>
-      <c r="F246" s="11" t="s">
-        <v>751</v>
-      </c>
       <c r="G246" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H246" s="11">
-        <v>21</v>
+        <v>74</v>
       </c>
       <c r="I246" s="11" t="s">
         <v>1</v>
@@ -11192,28 +11189,28 @@
     </row>
     <row r="247" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A247" s="13" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="B247" s="13" t="s">
         <v>24</v>
       </c>
       <c r="C247" s="13" t="s">
+        <v>794</v>
+      </c>
+      <c r="D247" s="13" t="s">
         <v>795</v>
       </c>
-      <c r="D247" s="13" t="s">
+      <c r="E247" s="13" t="s">
         <v>796</v>
       </c>
-      <c r="E247" s="13" t="s">
+      <c r="F247" s="13" t="s">
         <v>797</v>
       </c>
-      <c r="F247" s="13" t="s">
-        <v>798</v>
-      </c>
       <c r="G247" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H247" s="13">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="I247" s="13" t="s">
         <v>1</v>
@@ -11221,28 +11218,28 @@
     </row>
     <row r="248" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A248" s="11" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="B248" s="11" t="s">
         <v>24</v>
       </c>
       <c r="C248" s="11" t="s">
+        <v>799</v>
+      </c>
+      <c r="D248" s="11" t="s">
         <v>800</v>
       </c>
-      <c r="D248" s="11" t="s">
-        <v>801</v>
-      </c>
       <c r="E248" s="11" t="s">
+        <v>796</v>
+      </c>
+      <c r="F248" s="11" t="s">
         <v>797</v>
       </c>
-      <c r="F248" s="11" t="s">
-        <v>798</v>
-      </c>
       <c r="G248" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H248" s="11">
-        <v>36</v>
+        <v>56</v>
       </c>
       <c r="I248" s="11" t="s">
         <v>1</v>
@@ -11250,28 +11247,28 @@
     </row>
     <row r="249" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A249" s="13" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="B249" s="13" t="s">
         <v>24</v>
       </c>
       <c r="C249" s="13" t="s">
+        <v>802</v>
+      </c>
+      <c r="D249" s="13" t="s">
         <v>803</v>
       </c>
-      <c r="D249" s="13" t="s">
-        <v>804</v>
-      </c>
       <c r="E249" s="13" t="s">
+        <v>796</v>
+      </c>
+      <c r="F249" s="13" t="s">
         <v>797</v>
       </c>
-      <c r="F249" s="13" t="s">
-        <v>798</v>
-      </c>
       <c r="G249" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H249" s="13">
-        <v>76</v>
+        <v>53</v>
       </c>
       <c r="I249" s="13" t="s">
         <v>1</v>
@@ -11279,28 +11276,28 @@
     </row>
     <row r="250" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A250" s="11" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="B250" s="11" t="s">
         <v>24</v>
       </c>
       <c r="C250" s="11" t="s">
+        <v>805</v>
+      </c>
+      <c r="D250" s="11" t="s">
         <v>806</v>
       </c>
-      <c r="D250" s="11" t="s">
-        <v>807</v>
-      </c>
       <c r="E250" s="11" t="s">
+        <v>796</v>
+      </c>
+      <c r="F250" s="11" t="s">
         <v>797</v>
       </c>
-      <c r="F250" s="11" t="s">
-        <v>798</v>
-      </c>
       <c r="G250" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H250" s="11">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="I250" s="11" t="s">
         <v>1</v>
@@ -11308,28 +11305,28 @@
     </row>
     <row r="251" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A251" s="13" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="B251" s="13" t="s">
         <v>24</v>
       </c>
       <c r="C251" s="13" t="s">
+        <v>808</v>
+      </c>
+      <c r="D251" s="13" t="s">
         <v>809</v>
       </c>
-      <c r="D251" s="13" t="s">
-        <v>810</v>
-      </c>
       <c r="E251" s="13" t="s">
+        <v>796</v>
+      </c>
+      <c r="F251" s="13" t="s">
         <v>797</v>
       </c>
-      <c r="F251" s="13" t="s">
-        <v>798</v>
-      </c>
       <c r="G251" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H251" s="13">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="I251" s="13" t="s">
         <v>1</v>
@@ -11337,28 +11334,28 @@
     </row>
     <row r="252" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A252" s="11" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="B252" s="11" t="s">
         <v>24</v>
       </c>
       <c r="C252" s="11" t="s">
+        <v>811</v>
+      </c>
+      <c r="D252" s="11" t="s">
         <v>812</v>
       </c>
-      <c r="D252" s="11" t="s">
-        <v>813</v>
-      </c>
       <c r="E252" s="11" t="s">
+        <v>796</v>
+      </c>
+      <c r="F252" s="11" t="s">
         <v>797</v>
       </c>
-      <c r="F252" s="11" t="s">
-        <v>798</v>
-      </c>
       <c r="G252" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H252" s="11">
-        <v>61</v>
+        <v>35</v>
       </c>
       <c r="I252" s="11" t="s">
         <v>1</v>
@@ -11366,28 +11363,28 @@
     </row>
     <row r="253" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A253" s="13" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="B253" s="13" t="s">
         <v>24</v>
       </c>
       <c r="C253" s="13" t="s">
+        <v>814</v>
+      </c>
+      <c r="D253" s="13" t="s">
         <v>815</v>
       </c>
-      <c r="D253" s="13" t="s">
-        <v>816</v>
-      </c>
       <c r="E253" s="13" t="s">
+        <v>796</v>
+      </c>
+      <c r="F253" s="13" t="s">
         <v>797</v>
       </c>
-      <c r="F253" s="13" t="s">
-        <v>798</v>
-      </c>
       <c r="G253" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H253" s="13">
-        <v>80</v>
+        <v>33</v>
       </c>
       <c r="I253" s="13" t="s">
         <v>1</v>
@@ -11395,28 +11392,28 @@
     </row>
     <row r="254" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A254" s="11" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="B254" s="11" t="s">
         <v>24</v>
       </c>
       <c r="C254" s="11" t="s">
+        <v>817</v>
+      </c>
+      <c r="D254" s="11" t="s">
         <v>818</v>
       </c>
-      <c r="D254" s="11" t="s">
-        <v>819</v>
-      </c>
       <c r="E254" s="11" t="s">
+        <v>796</v>
+      </c>
+      <c r="F254" s="11" t="s">
         <v>797</v>
       </c>
-      <c r="F254" s="11" t="s">
-        <v>798</v>
-      </c>
       <c r="G254" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H254" s="11">
-        <v>35</v>
+        <v>74</v>
       </c>
       <c r="I254" s="11" t="s">
         <v>1</v>
@@ -11424,28 +11421,28 @@
     </row>
     <row r="255" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A255" s="13" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="B255" s="13" t="s">
         <v>24</v>
       </c>
       <c r="C255" s="13" t="s">
+        <v>820</v>
+      </c>
+      <c r="D255" s="13" t="s">
         <v>821</v>
       </c>
-      <c r="D255" s="13" t="s">
-        <v>822</v>
-      </c>
       <c r="E255" s="13" t="s">
+        <v>796</v>
+      </c>
+      <c r="F255" s="13" t="s">
         <v>797</v>
       </c>
-      <c r="F255" s="13" t="s">
-        <v>798</v>
-      </c>
       <c r="G255" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H255" s="13">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="I255" s="13" t="s">
         <v>1</v>
@@ -11453,28 +11450,28 @@
     </row>
     <row r="256" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A256" s="11" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="B256" s="11" t="s">
         <v>24</v>
       </c>
       <c r="C256" s="11" t="s">
+        <v>823</v>
+      </c>
+      <c r="D256" s="11" t="s">
         <v>824</v>
       </c>
-      <c r="D256" s="11" t="s">
-        <v>825</v>
-      </c>
       <c r="E256" s="11" t="s">
+        <v>796</v>
+      </c>
+      <c r="F256" s="11" t="s">
         <v>797</v>
       </c>
-      <c r="F256" s="11" t="s">
-        <v>798</v>
-      </c>
       <c r="G256" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H256" s="11">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="I256" s="11" t="s">
         <v>1</v>
@@ -11482,28 +11479,28 @@
     </row>
     <row r="257" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A257" s="13" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="B257" s="13" t="s">
         <v>24</v>
       </c>
       <c r="C257" s="13" t="s">
+        <v>826</v>
+      </c>
+      <c r="D257" s="13" t="s">
         <v>827</v>
       </c>
-      <c r="D257" s="13" t="s">
-        <v>828</v>
-      </c>
       <c r="E257" s="13" t="s">
+        <v>796</v>
+      </c>
+      <c r="F257" s="13" t="s">
         <v>797</v>
       </c>
-      <c r="F257" s="13" t="s">
-        <v>798</v>
-      </c>
       <c r="G257" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H257" s="13">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="I257" s="13" t="s">
         <v>1</v>
@@ -11511,28 +11508,28 @@
     </row>
     <row r="258" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A258" s="11" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="B258" s="11" t="s">
         <v>24</v>
       </c>
       <c r="C258" s="11" t="s">
+        <v>829</v>
+      </c>
+      <c r="D258" s="11" t="s">
         <v>830</v>
       </c>
-      <c r="D258" s="11" t="s">
-        <v>831</v>
-      </c>
       <c r="E258" s="11" t="s">
+        <v>796</v>
+      </c>
+      <c r="F258" s="11" t="s">
         <v>797</v>
       </c>
-      <c r="F258" s="11" t="s">
-        <v>798</v>
-      </c>
       <c r="G258" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H258" s="11">
-        <v>86</v>
+        <v>53</v>
       </c>
       <c r="I258" s="11" t="s">
         <v>1</v>
@@ -11540,28 +11537,28 @@
     </row>
     <row r="259" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A259" s="13" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="B259" s="13" t="s">
         <v>24</v>
       </c>
       <c r="C259" s="13" t="s">
+        <v>832</v>
+      </c>
+      <c r="D259" s="13" t="s">
         <v>833</v>
       </c>
-      <c r="D259" s="13" t="s">
-        <v>834</v>
-      </c>
       <c r="E259" s="13" t="s">
+        <v>796</v>
+      </c>
+      <c r="F259" s="13" t="s">
         <v>797</v>
       </c>
-      <c r="F259" s="13" t="s">
-        <v>798</v>
-      </c>
       <c r="G259" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H259" s="13">
-        <v>16</v>
+        <v>67</v>
       </c>
       <c r="I259" s="13" t="s">
         <v>1</v>
@@ -11569,28 +11566,28 @@
     </row>
     <row r="260" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A260" s="11" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="B260" s="11" t="s">
         <v>24</v>
       </c>
       <c r="C260" s="11" t="s">
+        <v>835</v>
+      </c>
+      <c r="D260" s="11" t="s">
         <v>836</v>
       </c>
-      <c r="D260" s="11" t="s">
-        <v>837</v>
-      </c>
       <c r="E260" s="11" t="s">
+        <v>796</v>
+      </c>
+      <c r="F260" s="11" t="s">
         <v>797</v>
       </c>
-      <c r="F260" s="11" t="s">
-        <v>798</v>
-      </c>
       <c r="G260" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H260" s="11">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="I260" s="11" t="s">
         <v>1</v>
@@ -11598,28 +11595,28 @@
     </row>
     <row r="261" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A261" s="13" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="B261" s="13" t="s">
         <v>24</v>
       </c>
       <c r="C261" s="13" t="s">
+        <v>838</v>
+      </c>
+      <c r="D261" s="13" t="s">
         <v>839</v>
       </c>
-      <c r="D261" s="13" t="s">
-        <v>840</v>
-      </c>
       <c r="E261" s="13" t="s">
+        <v>796</v>
+      </c>
+      <c r="F261" s="13" t="s">
         <v>797</v>
       </c>
-      <c r="F261" s="13" t="s">
-        <v>798</v>
-      </c>
       <c r="G261" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H261" s="13">
-        <v>81</v>
+        <v>54</v>
       </c>
       <c r="I261" s="13" t="s">
         <v>1</v>
@@ -11627,28 +11624,28 @@
     </row>
     <row r="262" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A262" s="11" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="B262" s="11" t="s">
         <v>24</v>
       </c>
       <c r="C262" s="11" t="s">
+        <v>841</v>
+      </c>
+      <c r="D262" s="11" t="s">
         <v>842</v>
       </c>
-      <c r="D262" s="11" t="s">
-        <v>843</v>
-      </c>
       <c r="E262" s="11" t="s">
+        <v>796</v>
+      </c>
+      <c r="F262" s="11" t="s">
         <v>797</v>
       </c>
-      <c r="F262" s="11" t="s">
-        <v>798</v>
-      </c>
       <c r="G262" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H262" s="11">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="I262" s="11" t="s">
         <v>1</v>
@@ -11656,28 +11653,28 @@
     </row>
     <row r="263" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A263" s="13" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="B263" s="13" t="s">
         <v>24</v>
       </c>
       <c r="C263" s="13" t="s">
+        <v>844</v>
+      </c>
+      <c r="D263" s="13" t="s">
         <v>845</v>
       </c>
-      <c r="D263" s="13" t="s">
-        <v>846</v>
-      </c>
       <c r="E263" s="13" t="s">
+        <v>796</v>
+      </c>
+      <c r="F263" s="13" t="s">
         <v>797</v>
       </c>
-      <c r="F263" s="13" t="s">
-        <v>798</v>
-      </c>
       <c r="G263" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H263" s="13">
-        <v>86</v>
+        <v>41</v>
       </c>
       <c r="I263" s="13" t="s">
         <v>1</v>
@@ -11685,28 +11682,28 @@
     </row>
     <row r="264" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A264" s="11" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="B264" s="11" t="s">
         <v>24</v>
       </c>
       <c r="C264" s="11" t="s">
+        <v>847</v>
+      </c>
+      <c r="D264" s="11" t="s">
         <v>848</v>
       </c>
-      <c r="D264" s="11" t="s">
-        <v>849</v>
-      </c>
       <c r="E264" s="11" t="s">
+        <v>796</v>
+      </c>
+      <c r="F264" s="11" t="s">
         <v>797</v>
       </c>
-      <c r="F264" s="11" t="s">
-        <v>798</v>
-      </c>
       <c r="G264" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H264" s="11">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="I264" s="11" t="s">
         <v>1</v>
@@ -11714,28 +11711,28 @@
     </row>
     <row r="265" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A265" s="13" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="B265" s="13" t="s">
         <v>24</v>
       </c>
       <c r="C265" s="13" t="s">
+        <v>850</v>
+      </c>
+      <c r="D265" s="13" t="s">
         <v>851</v>
       </c>
-      <c r="D265" s="13" t="s">
-        <v>852</v>
-      </c>
       <c r="E265" s="13" t="s">
+        <v>796</v>
+      </c>
+      <c r="F265" s="13" t="s">
         <v>797</v>
       </c>
-      <c r="F265" s="13" t="s">
-        <v>798</v>
-      </c>
       <c r="G265" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H265" s="13">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="I265" s="13" t="s">
         <v>1</v>
@@ -11743,28 +11740,28 @@
     </row>
     <row r="266" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A266" s="11" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="B266" s="11" t="s">
         <v>24</v>
       </c>
       <c r="C266" s="11" t="s">
+        <v>853</v>
+      </c>
+      <c r="D266" s="11" t="s">
         <v>854</v>
       </c>
-      <c r="D266" s="11" t="s">
-        <v>855</v>
-      </c>
       <c r="E266" s="11" t="s">
+        <v>796</v>
+      </c>
+      <c r="F266" s="11" t="s">
         <v>797</v>
       </c>
-      <c r="F266" s="11" t="s">
-        <v>798</v>
-      </c>
       <c r="G266" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H266" s="11">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="I266" s="11" t="s">
         <v>1</v>
@@ -11772,28 +11769,28 @@
     </row>
     <row r="267" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A267" s="13" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="B267" s="13" t="s">
         <v>25</v>
       </c>
       <c r="C267" s="13" t="s">
+        <v>856</v>
+      </c>
+      <c r="D267" s="13" t="s">
         <v>857</v>
       </c>
-      <c r="D267" s="13" t="s">
+      <c r="E267" s="13" t="s">
         <v>858</v>
       </c>
-      <c r="E267" s="13" t="s">
+      <c r="F267" s="13" t="s">
         <v>859</v>
       </c>
-      <c r="F267" s="13" t="s">
-        <v>860</v>
-      </c>
       <c r="G267" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H267" s="13">
-        <v>88</v>
+        <v>37</v>
       </c>
       <c r="I267" s="13" t="s">
         <v>1</v>
@@ -11801,28 +11798,28 @@
     </row>
     <row r="268" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A268" s="11" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="B268" s="11" t="s">
         <v>25</v>
       </c>
       <c r="C268" s="11" t="s">
+        <v>861</v>
+      </c>
+      <c r="D268" s="11" t="s">
         <v>862</v>
       </c>
-      <c r="D268" s="11" t="s">
-        <v>863</v>
-      </c>
       <c r="E268" s="11" t="s">
+        <v>858</v>
+      </c>
+      <c r="F268" s="11" t="s">
         <v>859</v>
       </c>
-      <c r="F268" s="11" t="s">
-        <v>860</v>
-      </c>
       <c r="G268" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H268" s="11">
-        <v>33</v>
+        <v>82</v>
       </c>
       <c r="I268" s="11" t="s">
         <v>1</v>
@@ -11830,28 +11827,28 @@
     </row>
     <row r="269" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A269" s="13" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="B269" s="13" t="s">
         <v>25</v>
       </c>
       <c r="C269" s="13" t="s">
+        <v>864</v>
+      </c>
+      <c r="D269" s="13" t="s">
         <v>865</v>
       </c>
-      <c r="D269" s="13" t="s">
-        <v>866</v>
-      </c>
       <c r="E269" s="13" t="s">
+        <v>858</v>
+      </c>
+      <c r="F269" s="13" t="s">
         <v>859</v>
       </c>
-      <c r="F269" s="13" t="s">
-        <v>860</v>
-      </c>
       <c r="G269" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H269" s="13">
-        <v>53</v>
+        <v>70</v>
       </c>
       <c r="I269" s="13" t="s">
         <v>1</v>
@@ -11859,28 +11856,28 @@
     </row>
     <row r="270" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A270" s="11" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="B270" s="11" t="s">
         <v>25</v>
       </c>
       <c r="C270" s="11" t="s">
+        <v>867</v>
+      </c>
+      <c r="D270" s="11" t="s">
         <v>868</v>
       </c>
-      <c r="D270" s="11" t="s">
-        <v>869</v>
-      </c>
       <c r="E270" s="11" t="s">
+        <v>858</v>
+      </c>
+      <c r="F270" s="11" t="s">
         <v>859</v>
       </c>
-      <c r="F270" s="11" t="s">
-        <v>860</v>
-      </c>
       <c r="G270" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H270" s="11">
-        <v>22</v>
+        <v>46</v>
       </c>
       <c r="I270" s="11" t="s">
         <v>1</v>
@@ -11888,28 +11885,28 @@
     </row>
     <row r="271" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A271" s="13" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="B271" s="13" t="s">
         <v>25</v>
       </c>
       <c r="C271" s="13" t="s">
+        <v>870</v>
+      </c>
+      <c r="D271" s="13" t="s">
         <v>871</v>
       </c>
-      <c r="D271" s="13" t="s">
-        <v>872</v>
-      </c>
       <c r="E271" s="13" t="s">
+        <v>858</v>
+      </c>
+      <c r="F271" s="13" t="s">
         <v>859</v>
       </c>
-      <c r="F271" s="13" t="s">
-        <v>860</v>
-      </c>
       <c r="G271" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H271" s="13">
-        <v>66</v>
+        <v>45</v>
       </c>
       <c r="I271" s="13" t="s">
         <v>1</v>
@@ -11917,28 +11914,28 @@
     </row>
     <row r="272" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A272" s="11" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="B272" s="11" t="s">
         <v>25</v>
       </c>
       <c r="C272" s="11" t="s">
+        <v>873</v>
+      </c>
+      <c r="D272" s="11" t="s">
         <v>874</v>
       </c>
-      <c r="D272" s="11" t="s">
-        <v>875</v>
-      </c>
       <c r="E272" s="11" t="s">
+        <v>858</v>
+      </c>
+      <c r="F272" s="11" t="s">
         <v>859</v>
       </c>
-      <c r="F272" s="11" t="s">
-        <v>860</v>
-      </c>
       <c r="G272" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H272" s="11">
-        <v>73</v>
+        <v>25</v>
       </c>
       <c r="I272" s="11" t="s">
         <v>1</v>
@@ -11946,28 +11943,28 @@
     </row>
     <row r="273" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A273" s="13" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="B273" s="13" t="s">
         <v>25</v>
       </c>
       <c r="C273" s="13" t="s">
+        <v>876</v>
+      </c>
+      <c r="D273" s="13" t="s">
         <v>877</v>
       </c>
-      <c r="D273" s="13" t="s">
-        <v>878</v>
-      </c>
       <c r="E273" s="13" t="s">
+        <v>858</v>
+      </c>
+      <c r="F273" s="13" t="s">
         <v>859</v>
       </c>
-      <c r="F273" s="13" t="s">
-        <v>860</v>
-      </c>
       <c r="G273" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H273" s="13">
-        <v>80</v>
+        <v>67</v>
       </c>
       <c r="I273" s="13" t="s">
         <v>1</v>
@@ -11975,28 +11972,28 @@
     </row>
     <row r="274" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A274" s="11" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="B274" s="11" t="s">
         <v>25</v>
       </c>
       <c r="C274" s="11" t="s">
+        <v>879</v>
+      </c>
+      <c r="D274" s="11" t="s">
         <v>880</v>
       </c>
-      <c r="D274" s="11" t="s">
-        <v>881</v>
-      </c>
       <c r="E274" s="11" t="s">
+        <v>858</v>
+      </c>
+      <c r="F274" s="11" t="s">
         <v>859</v>
       </c>
-      <c r="F274" s="11" t="s">
-        <v>860</v>
-      </c>
       <c r="G274" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H274" s="11">
-        <v>81</v>
+        <v>31</v>
       </c>
       <c r="I274" s="11" t="s">
         <v>1</v>
@@ -12004,28 +12001,28 @@
     </row>
     <row r="275" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A275" s="13" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="B275" s="13" t="s">
         <v>25</v>
       </c>
       <c r="C275" s="13" t="s">
+        <v>882</v>
+      </c>
+      <c r="D275" s="13" t="s">
         <v>883</v>
       </c>
-      <c r="D275" s="13" t="s">
-        <v>884</v>
-      </c>
       <c r="E275" s="13" t="s">
+        <v>858</v>
+      </c>
+      <c r="F275" s="13" t="s">
         <v>859</v>
       </c>
-      <c r="F275" s="13" t="s">
-        <v>860</v>
-      </c>
       <c r="G275" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H275" s="13">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="I275" s="13" t="s">
         <v>1</v>
@@ -12033,28 +12030,28 @@
     </row>
     <row r="276" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A276" s="11" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="B276" s="11" t="s">
         <v>25</v>
       </c>
       <c r="C276" s="11" t="s">
+        <v>885</v>
+      </c>
+      <c r="D276" s="11" t="s">
         <v>886</v>
       </c>
-      <c r="D276" s="11" t="s">
-        <v>887</v>
-      </c>
       <c r="E276" s="11" t="s">
+        <v>858</v>
+      </c>
+      <c r="F276" s="11" t="s">
         <v>859</v>
       </c>
-      <c r="F276" s="11" t="s">
-        <v>860</v>
-      </c>
       <c r="G276" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H276" s="11">
-        <v>88</v>
+        <v>60</v>
       </c>
       <c r="I276" s="11" t="s">
         <v>1</v>
@@ -12062,28 +12059,28 @@
     </row>
     <row r="277" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A277" s="13" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="B277" s="13" t="s">
         <v>25</v>
       </c>
       <c r="C277" s="13" t="s">
+        <v>888</v>
+      </c>
+      <c r="D277" s="13" t="s">
         <v>889</v>
       </c>
-      <c r="D277" s="13" t="s">
-        <v>890</v>
-      </c>
       <c r="E277" s="13" t="s">
+        <v>858</v>
+      </c>
+      <c r="F277" s="13" t="s">
         <v>859</v>
       </c>
-      <c r="F277" s="13" t="s">
-        <v>860</v>
-      </c>
       <c r="G277" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H277" s="13">
-        <v>47</v>
+        <v>66</v>
       </c>
       <c r="I277" s="13" t="s">
         <v>1</v>
@@ -12091,28 +12088,28 @@
     </row>
     <row r="278" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A278" s="11" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="B278" s="11" t="s">
         <v>25</v>
       </c>
       <c r="C278" s="11" t="s">
+        <v>891</v>
+      </c>
+      <c r="D278" s="11" t="s">
         <v>892</v>
       </c>
-      <c r="D278" s="11" t="s">
-        <v>893</v>
-      </c>
       <c r="E278" s="11" t="s">
+        <v>858</v>
+      </c>
+      <c r="F278" s="11" t="s">
         <v>859</v>
       </c>
-      <c r="F278" s="11" t="s">
-        <v>860</v>
-      </c>
       <c r="G278" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H278" s="11">
-        <v>46</v>
+        <v>21</v>
       </c>
       <c r="I278" s="11" t="s">
         <v>1</v>
@@ -12120,28 +12117,28 @@
     </row>
     <row r="279" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A279" s="13" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="B279" s="13" t="s">
         <v>25</v>
       </c>
       <c r="C279" s="13" t="s">
+        <v>894</v>
+      </c>
+      <c r="D279" s="13" t="s">
         <v>895</v>
       </c>
-      <c r="D279" s="13" t="s">
-        <v>896</v>
-      </c>
       <c r="E279" s="13" t="s">
+        <v>858</v>
+      </c>
+      <c r="F279" s="13" t="s">
         <v>859</v>
       </c>
-      <c r="F279" s="13" t="s">
-        <v>860</v>
-      </c>
       <c r="G279" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H279" s="13">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="I279" s="13" t="s">
         <v>1</v>
@@ -12149,28 +12146,28 @@
     </row>
     <row r="280" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A280" s="11" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="B280" s="11" t="s">
         <v>25</v>
       </c>
       <c r="C280" s="11" t="s">
+        <v>897</v>
+      </c>
+      <c r="D280" s="11" t="s">
         <v>898</v>
       </c>
-      <c r="D280" s="11" t="s">
-        <v>899</v>
-      </c>
       <c r="E280" s="11" t="s">
+        <v>858</v>
+      </c>
+      <c r="F280" s="11" t="s">
         <v>859</v>
       </c>
-      <c r="F280" s="11" t="s">
-        <v>860</v>
-      </c>
       <c r="G280" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H280" s="11">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="I280" s="11" t="s">
         <v>1</v>
@@ -12178,28 +12175,28 @@
     </row>
     <row r="281" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A281" s="13" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="B281" s="13" t="s">
         <v>25</v>
       </c>
       <c r="C281" s="13" t="s">
+        <v>900</v>
+      </c>
+      <c r="D281" s="13" t="s">
         <v>901</v>
       </c>
-      <c r="D281" s="13" t="s">
-        <v>902</v>
-      </c>
       <c r="E281" s="13" t="s">
+        <v>858</v>
+      </c>
+      <c r="F281" s="13" t="s">
         <v>859</v>
       </c>
-      <c r="F281" s="13" t="s">
-        <v>860</v>
-      </c>
       <c r="G281" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H281" s="13">
-        <v>71</v>
+        <v>83</v>
       </c>
       <c r="I281" s="13" t="s">
         <v>1</v>
@@ -12207,28 +12204,28 @@
     </row>
     <row r="282" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A282" s="11" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="B282" s="11" t="s">
         <v>26</v>
       </c>
       <c r="C282" s="11" t="s">
+        <v>903</v>
+      </c>
+      <c r="D282" s="11" t="s">
         <v>904</v>
       </c>
-      <c r="D282" s="11" t="s">
+      <c r="E282" s="11" t="s">
         <v>905</v>
       </c>
-      <c r="E282" s="11" t="s">
+      <c r="F282" s="11" t="s">
         <v>906</v>
       </c>
-      <c r="F282" s="11" t="s">
-        <v>907</v>
-      </c>
       <c r="G282" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H282" s="11">
-        <v>35</v>
+        <v>61</v>
       </c>
       <c r="I282" s="11" t="s">
         <v>1</v>
@@ -12236,28 +12233,28 @@
     </row>
     <row r="283" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A283" s="13" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="B283" s="13" t="s">
         <v>26</v>
       </c>
       <c r="C283" s="13" t="s">
+        <v>908</v>
+      </c>
+      <c r="D283" s="13" t="s">
         <v>909</v>
       </c>
-      <c r="D283" s="13" t="s">
-        <v>910</v>
-      </c>
       <c r="E283" s="13" t="s">
+        <v>905</v>
+      </c>
+      <c r="F283" s="13" t="s">
         <v>906</v>
       </c>
-      <c r="F283" s="13" t="s">
-        <v>907</v>
-      </c>
       <c r="G283" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H283" s="13">
-        <v>63</v>
+        <v>17</v>
       </c>
       <c r="I283" s="13" t="s">
         <v>1</v>
@@ -12265,28 +12262,28 @@
     </row>
     <row r="284" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A284" s="11" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="B284" s="11" t="s">
         <v>26</v>
       </c>
       <c r="C284" s="11" t="s">
+        <v>911</v>
+      </c>
+      <c r="D284" s="11" t="s">
         <v>912</v>
       </c>
-      <c r="D284" s="11" t="s">
-        <v>913</v>
-      </c>
       <c r="E284" s="11" t="s">
+        <v>905</v>
+      </c>
+      <c r="F284" s="11" t="s">
         <v>906</v>
       </c>
-      <c r="F284" s="11" t="s">
-        <v>907</v>
-      </c>
       <c r="G284" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H284" s="11">
-        <v>42</v>
+        <v>66</v>
       </c>
       <c r="I284" s="11" t="s">
         <v>1</v>
@@ -12294,28 +12291,28 @@
     </row>
     <row r="285" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A285" s="13" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="B285" s="13" t="s">
         <v>26</v>
       </c>
       <c r="C285" s="13" t="s">
+        <v>914</v>
+      </c>
+      <c r="D285" s="13" t="s">
         <v>915</v>
       </c>
-      <c r="D285" s="13" t="s">
-        <v>916</v>
-      </c>
       <c r="E285" s="13" t="s">
+        <v>905</v>
+      </c>
+      <c r="F285" s="13" t="s">
         <v>906</v>
       </c>
-      <c r="F285" s="13" t="s">
-        <v>907</v>
-      </c>
       <c r="G285" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H285" s="13">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="I285" s="13" t="s">
         <v>1</v>
@@ -12323,28 +12320,28 @@
     </row>
     <row r="286" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A286" s="11" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="B286" s="11" t="s">
         <v>26</v>
       </c>
       <c r="C286" s="11" t="s">
+        <v>917</v>
+      </c>
+      <c r="D286" s="11" t="s">
         <v>918</v>
       </c>
-      <c r="D286" s="11" t="s">
-        <v>919</v>
-      </c>
       <c r="E286" s="11" t="s">
+        <v>905</v>
+      </c>
+      <c r="F286" s="11" t="s">
         <v>906</v>
       </c>
-      <c r="F286" s="11" t="s">
-        <v>907</v>
-      </c>
       <c r="G286" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H286" s="11">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="I286" s="11" t="s">
         <v>1</v>
@@ -12352,28 +12349,28 @@
     </row>
     <row r="287" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A287" s="13" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="B287" s="13" t="s">
         <v>26</v>
       </c>
       <c r="C287" s="13" t="s">
+        <v>920</v>
+      </c>
+      <c r="D287" s="13" t="s">
         <v>921</v>
       </c>
-      <c r="D287" s="13" t="s">
-        <v>922</v>
-      </c>
       <c r="E287" s="13" t="s">
+        <v>905</v>
+      </c>
+      <c r="F287" s="13" t="s">
         <v>906</v>
       </c>
-      <c r="F287" s="13" t="s">
-        <v>907</v>
-      </c>
       <c r="G287" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H287" s="13">
-        <v>89</v>
+        <v>55</v>
       </c>
       <c r="I287" s="13" t="s">
         <v>1</v>
@@ -12381,28 +12378,28 @@
     </row>
     <row r="288" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A288" s="11" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="B288" s="11" t="s">
         <v>26</v>
       </c>
       <c r="C288" s="11" t="s">
+        <v>923</v>
+      </c>
+      <c r="D288" s="11" t="s">
         <v>924</v>
       </c>
-      <c r="D288" s="11" t="s">
-        <v>925</v>
-      </c>
       <c r="E288" s="11" t="s">
+        <v>905</v>
+      </c>
+      <c r="F288" s="11" t="s">
         <v>906</v>
       </c>
-      <c r="F288" s="11" t="s">
-        <v>907</v>
-      </c>
       <c r="G288" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H288" s="11">
-        <v>89</v>
+        <v>69</v>
       </c>
       <c r="I288" s="11" t="s">
         <v>1</v>
@@ -12410,28 +12407,28 @@
     </row>
     <row r="289" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A289" s="13" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="B289" s="13" t="s">
         <v>26</v>
       </c>
       <c r="C289" s="13" t="s">
+        <v>926</v>
+      </c>
+      <c r="D289" s="13" t="s">
         <v>927</v>
       </c>
-      <c r="D289" s="13" t="s">
-        <v>928</v>
-      </c>
       <c r="E289" s="13" t="s">
+        <v>905</v>
+      </c>
+      <c r="F289" s="13" t="s">
         <v>906</v>
       </c>
-      <c r="F289" s="13" t="s">
-        <v>907</v>
-      </c>
       <c r="G289" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H289" s="13">
-        <v>40</v>
+        <v>58</v>
       </c>
       <c r="I289" s="13" t="s">
         <v>1</v>
@@ -12439,28 +12436,28 @@
     </row>
     <row r="290" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A290" s="11" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="B290" s="11" t="s">
         <v>26</v>
       </c>
       <c r="C290" s="11" t="s">
+        <v>929</v>
+      </c>
+      <c r="D290" s="11" t="s">
         <v>930</v>
       </c>
-      <c r="D290" s="11" t="s">
-        <v>931</v>
-      </c>
       <c r="E290" s="11" t="s">
+        <v>905</v>
+      </c>
+      <c r="F290" s="11" t="s">
         <v>906</v>
       </c>
-      <c r="F290" s="11" t="s">
-        <v>907</v>
-      </c>
       <c r="G290" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H290" s="11">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="I290" s="11" t="s">
         <v>1</v>
@@ -12468,28 +12465,28 @@
     </row>
     <row r="291" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A291" s="13" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="B291" s="13" t="s">
         <v>26</v>
       </c>
       <c r="C291" s="13" t="s">
+        <v>932</v>
+      </c>
+      <c r="D291" s="13" t="s">
         <v>933</v>
       </c>
-      <c r="D291" s="13" t="s">
-        <v>934</v>
-      </c>
       <c r="E291" s="13" t="s">
+        <v>905</v>
+      </c>
+      <c r="F291" s="13" t="s">
         <v>906</v>
       </c>
-      <c r="F291" s="13" t="s">
-        <v>907</v>
-      </c>
       <c r="G291" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H291" s="13">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="I291" s="13" t="s">
         <v>1</v>
@@ -12497,28 +12494,28 @@
     </row>
     <row r="292" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A292" s="11" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="B292" s="11" t="s">
         <v>26</v>
       </c>
       <c r="C292" s="11" t="s">
+        <v>935</v>
+      </c>
+      <c r="D292" s="11" t="s">
         <v>936</v>
       </c>
-      <c r="D292" s="11" t="s">
-        <v>937</v>
-      </c>
       <c r="E292" s="11" t="s">
+        <v>905</v>
+      </c>
+      <c r="F292" s="11" t="s">
         <v>906</v>
       </c>
-      <c r="F292" s="11" t="s">
-        <v>907</v>
-      </c>
       <c r="G292" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H292" s="11">
-        <v>13</v>
+        <v>81</v>
       </c>
       <c r="I292" s="11" t="s">
         <v>1</v>
@@ -12526,28 +12523,28 @@
     </row>
     <row r="293" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A293" s="13" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="B293" s="13" t="s">
         <v>26</v>
       </c>
       <c r="C293" s="13" t="s">
+        <v>938</v>
+      </c>
+      <c r="D293" s="13" t="s">
         <v>939</v>
       </c>
-      <c r="D293" s="13" t="s">
-        <v>940</v>
-      </c>
       <c r="E293" s="13" t="s">
+        <v>905</v>
+      </c>
+      <c r="F293" s="13" t="s">
         <v>906</v>
       </c>
-      <c r="F293" s="13" t="s">
-        <v>907</v>
-      </c>
       <c r="G293" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H293" s="13">
-        <v>84</v>
+        <v>27</v>
       </c>
       <c r="I293" s="13" t="s">
         <v>1</v>
@@ -12555,28 +12552,28 @@
     </row>
     <row r="294" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A294" s="11" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="B294" s="11" t="s">
         <v>26</v>
       </c>
       <c r="C294" s="11" t="s">
+        <v>941</v>
+      </c>
+      <c r="D294" s="11" t="s">
         <v>942</v>
       </c>
-      <c r="D294" s="11" t="s">
-        <v>943</v>
-      </c>
       <c r="E294" s="11" t="s">
+        <v>905</v>
+      </c>
+      <c r="F294" s="11" t="s">
         <v>906</v>
       </c>
-      <c r="F294" s="11" t="s">
-        <v>907</v>
-      </c>
       <c r="G294" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H294" s="11">
-        <v>25</v>
+        <v>81</v>
       </c>
       <c r="I294" s="11" t="s">
         <v>1</v>
@@ -12584,28 +12581,28 @@
     </row>
     <row r="295" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A295" s="13" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="B295" s="13" t="s">
         <v>26</v>
       </c>
       <c r="C295" s="13" t="s">
+        <v>944</v>
+      </c>
+      <c r="D295" s="13" t="s">
         <v>945</v>
       </c>
-      <c r="D295" s="13" t="s">
-        <v>946</v>
-      </c>
       <c r="E295" s="13" t="s">
+        <v>905</v>
+      </c>
+      <c r="F295" s="13" t="s">
         <v>906</v>
       </c>
-      <c r="F295" s="13" t="s">
-        <v>907</v>
-      </c>
       <c r="G295" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H295" s="13">
-        <v>46</v>
+        <v>10</v>
       </c>
       <c r="I295" s="13" t="s">
         <v>1</v>
@@ -12613,28 +12610,28 @@
     </row>
     <row r="296" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A296" s="11" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="B296" s="11" t="s">
         <v>26</v>
       </c>
       <c r="C296" s="11" t="s">
+        <v>947</v>
+      </c>
+      <c r="D296" s="11" t="s">
         <v>948</v>
       </c>
-      <c r="D296" s="11" t="s">
-        <v>949</v>
-      </c>
       <c r="E296" s="11" t="s">
+        <v>905</v>
+      </c>
+      <c r="F296" s="11" t="s">
         <v>906</v>
       </c>
-      <c r="F296" s="11" t="s">
-        <v>907</v>
-      </c>
       <c r="G296" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H296" s="11">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="I296" s="11" t="s">
         <v>1</v>
@@ -12642,28 +12639,28 @@
     </row>
     <row r="297" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A297" s="13" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="B297" s="13" t="s">
         <v>26</v>
       </c>
       <c r="C297" s="13" t="s">
+        <v>950</v>
+      </c>
+      <c r="D297" s="13" t="s">
         <v>951</v>
       </c>
-      <c r="D297" s="13" t="s">
-        <v>952</v>
-      </c>
       <c r="E297" s="13" t="s">
+        <v>905</v>
+      </c>
+      <c r="F297" s="13" t="s">
         <v>906</v>
       </c>
-      <c r="F297" s="13" t="s">
-        <v>907</v>
-      </c>
       <c r="G297" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H297" s="13">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="I297" s="13" t="s">
         <v>1</v>
@@ -12671,28 +12668,28 @@
     </row>
     <row r="298" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A298" s="11" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="B298" s="11" t="s">
         <v>26</v>
       </c>
       <c r="C298" s="11" t="s">
+        <v>953</v>
+      </c>
+      <c r="D298" s="11" t="s">
         <v>954</v>
       </c>
-      <c r="D298" s="11" t="s">
-        <v>955</v>
-      </c>
       <c r="E298" s="11" t="s">
+        <v>905</v>
+      </c>
+      <c r="F298" s="11" t="s">
         <v>906</v>
       </c>
-      <c r="F298" s="11" t="s">
-        <v>907</v>
-      </c>
       <c r="G298" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H298" s="11">
-        <v>12</v>
+        <v>51</v>
       </c>
       <c r="I298" s="11" t="s">
         <v>1</v>
@@ -12700,28 +12697,28 @@
     </row>
     <row r="299" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A299" s="13" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="B299" s="13" t="s">
         <v>26</v>
       </c>
       <c r="C299" s="13" t="s">
+        <v>956</v>
+      </c>
+      <c r="D299" s="13" t="s">
         <v>957</v>
       </c>
-      <c r="D299" s="13" t="s">
-        <v>958</v>
-      </c>
       <c r="E299" s="13" t="s">
+        <v>905</v>
+      </c>
+      <c r="F299" s="13" t="s">
         <v>906</v>
       </c>
-      <c r="F299" s="13" t="s">
-        <v>907</v>
-      </c>
       <c r="G299" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H299" s="13">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="I299" s="13" t="s">
         <v>1</v>
@@ -12729,28 +12726,28 @@
     </row>
     <row r="300" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A300" s="11" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="B300" s="11" t="s">
         <v>26</v>
       </c>
       <c r="C300" s="11" t="s">
+        <v>959</v>
+      </c>
+      <c r="D300" s="11" t="s">
         <v>960</v>
       </c>
-      <c r="D300" s="11" t="s">
-        <v>961</v>
-      </c>
       <c r="E300" s="11" t="s">
+        <v>905</v>
+      </c>
+      <c r="F300" s="11" t="s">
         <v>906</v>
       </c>
-      <c r="F300" s="11" t="s">
-        <v>907</v>
-      </c>
       <c r="G300" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H300" s="11">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="I300" s="11" t="s">
         <v>1</v>
@@ -12758,28 +12755,28 @@
     </row>
     <row r="301" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A301" s="13" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="B301" s="13" t="s">
         <v>26</v>
       </c>
       <c r="C301" s="13" t="s">
+        <v>962</v>
+      </c>
+      <c r="D301" s="13" t="s">
         <v>963</v>
       </c>
-      <c r="D301" s="13" t="s">
-        <v>964</v>
-      </c>
       <c r="E301" s="13" t="s">
+        <v>905</v>
+      </c>
+      <c r="F301" s="13" t="s">
         <v>906</v>
       </c>
-      <c r="F301" s="13" t="s">
-        <v>907</v>
-      </c>
       <c r="G301" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H301" s="13">
-        <v>75</v>
+        <v>39</v>
       </c>
       <c r="I301" s="13" t="s">
         <v>1</v>
@@ -12787,28 +12784,28 @@
     </row>
     <row r="302" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A302" s="11" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="B302" s="11" t="s">
         <v>26</v>
       </c>
       <c r="C302" s="11" t="s">
+        <v>965</v>
+      </c>
+      <c r="D302" s="11" t="s">
         <v>966</v>
       </c>
-      <c r="D302" s="11" t="s">
-        <v>967</v>
-      </c>
       <c r="E302" s="11" t="s">
+        <v>905</v>
+      </c>
+      <c r="F302" s="11" t="s">
         <v>906</v>
       </c>
-      <c r="F302" s="11" t="s">
-        <v>907</v>
-      </c>
       <c r="G302" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H302" s="11">
-        <v>66</v>
+        <v>27</v>
       </c>
       <c r="I302" s="11" t="s">
         <v>1</v>
@@ -12816,28 +12813,28 @@
     </row>
     <row r="303" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A303" s="13" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="B303" s="13" t="s">
         <v>26</v>
       </c>
       <c r="C303" s="13" t="s">
+        <v>968</v>
+      </c>
+      <c r="D303" s="13" t="s">
         <v>969</v>
       </c>
-      <c r="D303" s="13" t="s">
-        <v>970</v>
-      </c>
       <c r="E303" s="13" t="s">
+        <v>905</v>
+      </c>
+      <c r="F303" s="13" t="s">
         <v>906</v>
       </c>
-      <c r="F303" s="13" t="s">
-        <v>907</v>
-      </c>
       <c r="G303" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H303" s="13">
-        <v>71</v>
+        <v>38</v>
       </c>
       <c r="I303" s="13" t="s">
         <v>1</v>
@@ -12845,28 +12842,28 @@
     </row>
     <row r="304" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A304" s="11" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="B304" s="11" t="s">
         <v>26</v>
       </c>
       <c r="C304" s="11" t="s">
+        <v>971</v>
+      </c>
+      <c r="D304" s="11" t="s">
         <v>972</v>
       </c>
-      <c r="D304" s="11" t="s">
-        <v>973</v>
-      </c>
       <c r="E304" s="11" t="s">
+        <v>905</v>
+      </c>
+      <c r="F304" s="11" t="s">
         <v>906</v>
       </c>
-      <c r="F304" s="11" t="s">
-        <v>907</v>
-      </c>
       <c r="G304" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H304" s="11">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="I304" s="11" t="s">
         <v>1</v>
@@ -12874,28 +12871,28 @@
     </row>
     <row r="305" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A305" s="13" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="B305" s="13" t="s">
         <v>26</v>
       </c>
       <c r="C305" s="13" t="s">
+        <v>974</v>
+      </c>
+      <c r="D305" s="13" t="s">
         <v>975</v>
       </c>
-      <c r="D305" s="13" t="s">
-        <v>976</v>
-      </c>
       <c r="E305" s="13" t="s">
+        <v>905</v>
+      </c>
+      <c r="F305" s="13" t="s">
         <v>906</v>
       </c>
-      <c r="F305" s="13" t="s">
-        <v>907</v>
-      </c>
       <c r="G305" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H305" s="13">
-        <v>54</v>
+        <v>27</v>
       </c>
       <c r="I305" s="13" t="s">
         <v>1</v>
@@ -12903,28 +12900,28 @@
     </row>
     <row r="306" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A306" s="11" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="B306" s="11" t="s">
         <v>26</v>
       </c>
       <c r="C306" s="11" t="s">
+        <v>977</v>
+      </c>
+      <c r="D306" s="11" t="s">
         <v>978</v>
       </c>
-      <c r="D306" s="11" t="s">
-        <v>979</v>
-      </c>
       <c r="E306" s="11" t="s">
+        <v>905</v>
+      </c>
+      <c r="F306" s="11" t="s">
         <v>906</v>
       </c>
-      <c r="F306" s="11" t="s">
-        <v>907</v>
-      </c>
       <c r="G306" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H306" s="11">
-        <v>55</v>
+        <v>71</v>
       </c>
       <c r="I306" s="11" t="s">
         <v>1</v>
@@ -12932,28 +12929,28 @@
     </row>
     <row r="307" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A307" s="13" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="B307" s="13" t="s">
         <v>27</v>
       </c>
       <c r="C307" s="13" t="s">
+        <v>980</v>
+      </c>
+      <c r="D307" s="13" t="s">
         <v>981</v>
       </c>
-      <c r="D307" s="13" t="s">
+      <c r="E307" s="13" t="s">
         <v>982</v>
       </c>
-      <c r="E307" s="13" t="s">
+      <c r="F307" s="13" t="s">
         <v>983</v>
       </c>
-      <c r="F307" s="13" t="s">
-        <v>984</v>
-      </c>
       <c r="G307" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H307" s="13">
-        <v>55</v>
+        <v>77</v>
       </c>
       <c r="I307" s="13" t="s">
         <v>1</v>
@@ -12961,28 +12958,28 @@
     </row>
     <row r="308" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A308" s="11" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="B308" s="11" t="s">
         <v>27</v>
       </c>
       <c r="C308" s="11" t="s">
+        <v>985</v>
+      </c>
+      <c r="D308" s="11" t="s">
         <v>986</v>
       </c>
-      <c r="D308" s="11" t="s">
-        <v>987</v>
-      </c>
       <c r="E308" s="11" t="s">
+        <v>982</v>
+      </c>
+      <c r="F308" s="11" t="s">
         <v>983</v>
       </c>
-      <c r="F308" s="11" t="s">
-        <v>984</v>
-      </c>
       <c r="G308" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H308" s="11">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="I308" s="11" t="s">
         <v>1</v>
@@ -12990,28 +12987,28 @@
     </row>
     <row r="309" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A309" s="13" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="B309" s="13" t="s">
         <v>27</v>
       </c>
       <c r="C309" s="13" t="s">
+        <v>988</v>
+      </c>
+      <c r="D309" s="13" t="s">
         <v>989</v>
       </c>
-      <c r="D309" s="13" t="s">
-        <v>990</v>
-      </c>
       <c r="E309" s="13" t="s">
+        <v>982</v>
+      </c>
+      <c r="F309" s="13" t="s">
         <v>983</v>
       </c>
-      <c r="F309" s="13" t="s">
-        <v>984</v>
-      </c>
       <c r="G309" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H309" s="13">
-        <v>33</v>
+        <v>64</v>
       </c>
       <c r="I309" s="13" t="s">
         <v>1</v>
@@ -13019,28 +13016,28 @@
     </row>
     <row r="310" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A310" s="11" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="B310" s="11" t="s">
         <v>27</v>
       </c>
       <c r="C310" s="11" t="s">
+        <v>991</v>
+      </c>
+      <c r="D310" s="11" t="s">
         <v>992</v>
       </c>
-      <c r="D310" s="11" t="s">
-        <v>993</v>
-      </c>
       <c r="E310" s="11" t="s">
+        <v>982</v>
+      </c>
+      <c r="F310" s="11" t="s">
         <v>983</v>
       </c>
-      <c r="F310" s="11" t="s">
-        <v>984</v>
-      </c>
       <c r="G310" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H310" s="11">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="I310" s="11" t="s">
         <v>1</v>
@@ -13048,28 +13045,28 @@
     </row>
     <row r="311" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A311" s="13" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="B311" s="13" t="s">
         <v>27</v>
       </c>
       <c r="C311" s="13" t="s">
+        <v>994</v>
+      </c>
+      <c r="D311" s="13" t="s">
         <v>995</v>
       </c>
-      <c r="D311" s="13" t="s">
-        <v>996</v>
-      </c>
       <c r="E311" s="13" t="s">
+        <v>982</v>
+      </c>
+      <c r="F311" s="13" t="s">
         <v>983</v>
       </c>
-      <c r="F311" s="13" t="s">
-        <v>984</v>
-      </c>
       <c r="G311" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H311" s="13">
-        <v>47</v>
+        <v>26</v>
       </c>
       <c r="I311" s="13" t="s">
         <v>1</v>
@@ -13077,28 +13074,28 @@
     </row>
     <row r="312" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A312" s="11" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="B312" s="11" t="s">
         <v>27</v>
       </c>
       <c r="C312" s="11" t="s">
+        <v>997</v>
+      </c>
+      <c r="D312" s="11" t="s">
         <v>998</v>
       </c>
-      <c r="D312" s="11" t="s">
-        <v>999</v>
-      </c>
       <c r="E312" s="11" t="s">
+        <v>982</v>
+      </c>
+      <c r="F312" s="11" t="s">
         <v>983</v>
       </c>
-      <c r="F312" s="11" t="s">
-        <v>984</v>
-      </c>
       <c r="G312" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H312" s="11">
-        <v>47</v>
+        <v>71</v>
       </c>
       <c r="I312" s="11" t="s">
         <v>1</v>
@@ -13106,28 +13103,28 @@
     </row>
     <row r="313" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A313" s="13" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
       <c r="B313" s="13" t="s">
         <v>27</v>
       </c>
       <c r="C313" s="13" t="s">
+        <v>1000</v>
+      </c>
+      <c r="D313" s="13" t="s">
         <v>1001</v>
       </c>
-      <c r="D313" s="13" t="s">
-        <v>1002</v>
-      </c>
       <c r="E313" s="13" t="s">
+        <v>982</v>
+      </c>
+      <c r="F313" s="13" t="s">
         <v>983</v>
       </c>
-      <c r="F313" s="13" t="s">
-        <v>984</v>
-      </c>
       <c r="G313" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H313" s="13">
-        <v>54</v>
+        <v>71</v>
       </c>
       <c r="I313" s="13" t="s">
         <v>1</v>
@@ -13135,28 +13132,28 @@
     </row>
     <row r="314" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A314" s="11" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="B314" s="11" t="s">
         <v>27</v>
       </c>
       <c r="C314" s="11" t="s">
+        <v>1003</v>
+      </c>
+      <c r="D314" s="11" t="s">
         <v>1004</v>
       </c>
-      <c r="D314" s="11" t="s">
-        <v>1005</v>
-      </c>
       <c r="E314" s="11" t="s">
+        <v>982</v>
+      </c>
+      <c r="F314" s="11" t="s">
         <v>983</v>
       </c>
-      <c r="F314" s="11" t="s">
-        <v>984</v>
-      </c>
       <c r="G314" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H314" s="11">
-        <v>66</v>
+        <v>39</v>
       </c>
       <c r="I314" s="11" t="s">
         <v>1</v>
@@ -13164,28 +13161,28 @@
     </row>
     <row r="315" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A315" s="13" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="B315" s="13" t="s">
         <v>27</v>
       </c>
       <c r="C315" s="13" t="s">
+        <v>1006</v>
+      </c>
+      <c r="D315" s="13" t="s">
         <v>1007</v>
       </c>
-      <c r="D315" s="13" t="s">
-        <v>1008</v>
-      </c>
       <c r="E315" s="13" t="s">
+        <v>982</v>
+      </c>
+      <c r="F315" s="13" t="s">
         <v>983</v>
       </c>
-      <c r="F315" s="13" t="s">
-        <v>984</v>
-      </c>
       <c r="G315" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H315" s="13">
-        <v>35</v>
+        <v>69</v>
       </c>
       <c r="I315" s="13" t="s">
         <v>1</v>
@@ -13193,28 +13190,28 @@
     </row>
     <row r="316" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A316" s="11" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="B316" s="11" t="s">
         <v>27</v>
       </c>
       <c r="C316" s="11" t="s">
+        <v>1009</v>
+      </c>
+      <c r="D316" s="11" t="s">
         <v>1010</v>
       </c>
-      <c r="D316" s="11" t="s">
-        <v>1011</v>
-      </c>
       <c r="E316" s="11" t="s">
+        <v>982</v>
+      </c>
+      <c r="F316" s="11" t="s">
         <v>983</v>
       </c>
-      <c r="F316" s="11" t="s">
-        <v>984</v>
-      </c>
       <c r="G316" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H316" s="11">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="I316" s="11" t="s">
         <v>1</v>
@@ -13222,28 +13219,28 @@
     </row>
     <row r="317" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A317" s="13" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="B317" s="13" t="s">
         <v>27</v>
       </c>
       <c r="C317" s="13" t="s">
+        <v>1012</v>
+      </c>
+      <c r="D317" s="13" t="s">
         <v>1013</v>
       </c>
-      <c r="D317" s="13" t="s">
-        <v>1014</v>
-      </c>
       <c r="E317" s="13" t="s">
+        <v>982</v>
+      </c>
+      <c r="F317" s="13" t="s">
         <v>983</v>
       </c>
-      <c r="F317" s="13" t="s">
-        <v>984</v>
-      </c>
       <c r="G317" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H317" s="13">
-        <v>73</v>
+        <v>32</v>
       </c>
       <c r="I317" s="13" t="s">
         <v>1</v>
@@ -13251,28 +13248,28 @@
     </row>
     <row r="318" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A318" s="11" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="B318" s="11" t="s">
         <v>27</v>
       </c>
       <c r="C318" s="11" t="s">
+        <v>1015</v>
+      </c>
+      <c r="D318" s="11" t="s">
         <v>1016</v>
       </c>
-      <c r="D318" s="11" t="s">
-        <v>1017</v>
-      </c>
       <c r="E318" s="11" t="s">
+        <v>982</v>
+      </c>
+      <c r="F318" s="11" t="s">
         <v>983</v>
       </c>
-      <c r="F318" s="11" t="s">
-        <v>984</v>
-      </c>
       <c r="G318" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H318" s="11">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="I318" s="11" t="s">
         <v>1</v>
@@ -13280,28 +13277,28 @@
     </row>
     <row r="319" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A319" s="13" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
       <c r="B319" s="13" t="s">
         <v>27</v>
       </c>
       <c r="C319" s="13" t="s">
+        <v>1018</v>
+      </c>
+      <c r="D319" s="13" t="s">
         <v>1019</v>
       </c>
-      <c r="D319" s="13" t="s">
-        <v>1020</v>
-      </c>
       <c r="E319" s="13" t="s">
+        <v>982</v>
+      </c>
+      <c r="F319" s="13" t="s">
         <v>983</v>
       </c>
-      <c r="F319" s="13" t="s">
-        <v>984</v>
-      </c>
       <c r="G319" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H319" s="13">
-        <v>72</v>
+        <v>12</v>
       </c>
       <c r="I319" s="13" t="s">
         <v>1</v>
@@ -13309,28 +13306,28 @@
     </row>
     <row r="320" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A320" s="11" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="B320" s="11" t="s">
         <v>27</v>
       </c>
       <c r="C320" s="11" t="s">
+        <v>1021</v>
+      </c>
+      <c r="D320" s="11" t="s">
         <v>1022</v>
       </c>
-      <c r="D320" s="11" t="s">
-        <v>1023</v>
-      </c>
       <c r="E320" s="11" t="s">
+        <v>982</v>
+      </c>
+      <c r="F320" s="11" t="s">
         <v>983</v>
       </c>
-      <c r="F320" s="11" t="s">
-        <v>984</v>
-      </c>
       <c r="G320" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H320" s="11">
-        <v>84</v>
+        <v>24</v>
       </c>
       <c r="I320" s="11" t="s">
         <v>1</v>
@@ -13338,28 +13335,28 @@
     </row>
     <row r="321" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A321" s="13" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="B321" s="13" t="s">
         <v>27</v>
       </c>
       <c r="C321" s="13" t="s">
+        <v>1024</v>
+      </c>
+      <c r="D321" s="13" t="s">
         <v>1025</v>
       </c>
-      <c r="D321" s="13" t="s">
-        <v>1026</v>
-      </c>
       <c r="E321" s="13" t="s">
+        <v>982</v>
+      </c>
+      <c r="F321" s="13" t="s">
         <v>983</v>
       </c>
-      <c r="F321" s="13" t="s">
-        <v>984</v>
-      </c>
       <c r="G321" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H321" s="13">
-        <v>57</v>
+        <v>34</v>
       </c>
       <c r="I321" s="13" t="s">
         <v>1</v>

--- a/testing/selenium-tests/Test_Report.xlsx
+++ b/testing/selenium-tests/Test_Report.xlsx
@@ -2282,7 +2282,7 @@
         <v>9</v>
       </c>
       <c r="H2" s="11">
-        <v>40</v>
+        <v>85</v>
       </c>
       <c r="I2" s="11" t="s">
         <v>1</v>
@@ -2311,7 +2311,7 @@
         <v>9</v>
       </c>
       <c r="H3" s="13">
-        <v>91</v>
+        <v>62</v>
       </c>
       <c r="I3" s="13" t="s">
         <v>1</v>
@@ -2340,7 +2340,7 @@
         <v>9</v>
       </c>
       <c r="H4" s="11">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="I4" s="11" t="s">
         <v>1</v>
@@ -2369,7 +2369,7 @@
         <v>9</v>
       </c>
       <c r="H5" s="13">
-        <v>55</v>
+        <v>82</v>
       </c>
       <c r="I5" s="13" t="s">
         <v>1</v>
@@ -2398,7 +2398,7 @@
         <v>9</v>
       </c>
       <c r="H6" s="11">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="I6" s="11" t="s">
         <v>1</v>
@@ -2427,7 +2427,7 @@
         <v>9</v>
       </c>
       <c r="H7" s="13">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="I7" s="13" t="s">
         <v>1</v>
@@ -2456,7 +2456,7 @@
         <v>9</v>
       </c>
       <c r="H8" s="11">
-        <v>73</v>
+        <v>26</v>
       </c>
       <c r="I8" s="11" t="s">
         <v>1</v>
@@ -2485,7 +2485,7 @@
         <v>9</v>
       </c>
       <c r="H9" s="13">
-        <v>65</v>
+        <v>17</v>
       </c>
       <c r="I9" s="13" t="s">
         <v>1</v>
@@ -2514,7 +2514,7 @@
         <v>9</v>
       </c>
       <c r="H10" s="11">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I10" s="11" t="s">
         <v>1</v>
@@ -2543,7 +2543,7 @@
         <v>9</v>
       </c>
       <c r="H11" s="13">
-        <v>34</v>
+        <v>72</v>
       </c>
       <c r="I11" s="13" t="s">
         <v>1</v>
@@ -2572,7 +2572,7 @@
         <v>9</v>
       </c>
       <c r="H12" s="11">
-        <v>84</v>
+        <v>17</v>
       </c>
       <c r="I12" s="11" t="s">
         <v>1</v>
@@ -2601,7 +2601,7 @@
         <v>9</v>
       </c>
       <c r="H13" s="13">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="I13" s="13" t="s">
         <v>1</v>
@@ -2630,7 +2630,7 @@
         <v>9</v>
       </c>
       <c r="H14" s="11">
-        <v>93</v>
+        <v>46</v>
       </c>
       <c r="I14" s="11" t="s">
         <v>1</v>
@@ -2659,7 +2659,7 @@
         <v>9</v>
       </c>
       <c r="H15" s="13">
-        <v>23</v>
+        <v>81</v>
       </c>
       <c r="I15" s="13" t="s">
         <v>1</v>
@@ -2688,7 +2688,7 @@
         <v>9</v>
       </c>
       <c r="H16" s="11">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="I16" s="11" t="s">
         <v>1</v>
@@ -2717,7 +2717,7 @@
         <v>9</v>
       </c>
       <c r="H17" s="13">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="I17" s="13" t="s">
         <v>1</v>
@@ -2746,7 +2746,7 @@
         <v>9</v>
       </c>
       <c r="H18" s="11">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="I18" s="11" t="s">
         <v>1</v>
@@ -2775,7 +2775,7 @@
         <v>9</v>
       </c>
       <c r="H19" s="13">
-        <v>42</v>
+        <v>86</v>
       </c>
       <c r="I19" s="13" t="s">
         <v>1</v>
@@ -2804,7 +2804,7 @@
         <v>9</v>
       </c>
       <c r="H20" s="11">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="I20" s="11" t="s">
         <v>1</v>
@@ -2833,7 +2833,7 @@
         <v>9</v>
       </c>
       <c r="H21" s="13">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="I21" s="13" t="s">
         <v>1</v>
@@ -2862,7 +2862,7 @@
         <v>9</v>
       </c>
       <c r="H22" s="11">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="I22" s="11" t="s">
         <v>1</v>
@@ -2891,7 +2891,7 @@
         <v>9</v>
       </c>
       <c r="H23" s="13">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="I23" s="13" t="s">
         <v>1</v>
@@ -2920,7 +2920,7 @@
         <v>9</v>
       </c>
       <c r="H24" s="11">
-        <v>93</v>
+        <v>54</v>
       </c>
       <c r="I24" s="11" t="s">
         <v>1</v>
@@ -2949,7 +2949,7 @@
         <v>9</v>
       </c>
       <c r="H25" s="13">
-        <v>79</v>
+        <v>27</v>
       </c>
       <c r="I25" s="13" t="s">
         <v>1</v>
@@ -2978,7 +2978,7 @@
         <v>9</v>
       </c>
       <c r="H26" s="11">
-        <v>49</v>
+        <v>82</v>
       </c>
       <c r="I26" s="11" t="s">
         <v>1</v>
@@ -3007,7 +3007,7 @@
         <v>9</v>
       </c>
       <c r="H27" s="13">
-        <v>27</v>
+        <v>76</v>
       </c>
       <c r="I27" s="13" t="s">
         <v>1</v>
@@ -3036,7 +3036,7 @@
         <v>9</v>
       </c>
       <c r="H28" s="11">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="I28" s="11" t="s">
         <v>1</v>
@@ -3065,7 +3065,7 @@
         <v>9</v>
       </c>
       <c r="H29" s="13">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="I29" s="13" t="s">
         <v>1</v>
@@ -3094,7 +3094,7 @@
         <v>9</v>
       </c>
       <c r="H30" s="11">
-        <v>91</v>
+        <v>18</v>
       </c>
       <c r="I30" s="11" t="s">
         <v>1</v>
@@ -3123,7 +3123,7 @@
         <v>9</v>
       </c>
       <c r="H31" s="13">
-        <v>64</v>
+        <v>20</v>
       </c>
       <c r="I31" s="13" t="s">
         <v>1</v>
@@ -3152,7 +3152,7 @@
         <v>9</v>
       </c>
       <c r="H32" s="11">
-        <v>21</v>
+        <v>63</v>
       </c>
       <c r="I32" s="11" t="s">
         <v>1</v>
@@ -3181,7 +3181,7 @@
         <v>9</v>
       </c>
       <c r="H33" s="13">
-        <v>76</v>
+        <v>39</v>
       </c>
       <c r="I33" s="13" t="s">
         <v>1</v>
@@ -3210,7 +3210,7 @@
         <v>9</v>
       </c>
       <c r="H34" s="11">
-        <v>41</v>
+        <v>18</v>
       </c>
       <c r="I34" s="11" t="s">
         <v>1</v>
@@ -3239,7 +3239,7 @@
         <v>9</v>
       </c>
       <c r="H35" s="13">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="I35" s="13" t="s">
         <v>1</v>
@@ -3268,7 +3268,7 @@
         <v>9</v>
       </c>
       <c r="H36" s="11">
-        <v>57</v>
+        <v>29</v>
       </c>
       <c r="I36" s="11" t="s">
         <v>1</v>
@@ -3297,7 +3297,7 @@
         <v>9</v>
       </c>
       <c r="H37" s="13">
-        <v>36</v>
+        <v>79</v>
       </c>
       <c r="I37" s="13" t="s">
         <v>1</v>
@@ -3326,7 +3326,7 @@
         <v>9</v>
       </c>
       <c r="H38" s="11">
-        <v>44</v>
+        <v>84</v>
       </c>
       <c r="I38" s="11" t="s">
         <v>1</v>
@@ -3355,7 +3355,7 @@
         <v>9</v>
       </c>
       <c r="H39" s="13">
-        <v>83</v>
+        <v>50</v>
       </c>
       <c r="I39" s="13" t="s">
         <v>1</v>
@@ -3384,7 +3384,7 @@
         <v>9</v>
       </c>
       <c r="H40" s="11">
-        <v>62</v>
+        <v>27</v>
       </c>
       <c r="I40" s="11" t="s">
         <v>1</v>
@@ -3413,7 +3413,7 @@
         <v>9</v>
       </c>
       <c r="H41" s="13">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="I41" s="13" t="s">
         <v>1</v>
@@ -3442,7 +3442,7 @@
         <v>9</v>
       </c>
       <c r="H42" s="11">
-        <v>19</v>
+        <v>91</v>
       </c>
       <c r="I42" s="11" t="s">
         <v>1</v>
@@ -3471,7 +3471,7 @@
         <v>9</v>
       </c>
       <c r="H43" s="13">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="I43" s="13" t="s">
         <v>1</v>
@@ -3500,7 +3500,7 @@
         <v>9</v>
       </c>
       <c r="H44" s="11">
-        <v>92</v>
+        <v>49</v>
       </c>
       <c r="I44" s="11" t="s">
         <v>1</v>
@@ -3529,7 +3529,7 @@
         <v>9</v>
       </c>
       <c r="H45" s="13">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="I45" s="13" t="s">
         <v>1</v>
@@ -3558,7 +3558,7 @@
         <v>9</v>
       </c>
       <c r="H46" s="11">
-        <v>45</v>
+        <v>75</v>
       </c>
       <c r="I46" s="11" t="s">
         <v>1</v>
@@ -3587,7 +3587,7 @@
         <v>9</v>
       </c>
       <c r="H47" s="13">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="I47" s="13" t="s">
         <v>1</v>
@@ -3616,7 +3616,7 @@
         <v>9</v>
       </c>
       <c r="H48" s="11">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I48" s="11" t="s">
         <v>1</v>
@@ -3645,7 +3645,7 @@
         <v>9</v>
       </c>
       <c r="H49" s="13">
-        <v>36</v>
+        <v>56</v>
       </c>
       <c r="I49" s="13" t="s">
         <v>1</v>
@@ -3674,7 +3674,7 @@
         <v>9</v>
       </c>
       <c r="H50" s="11">
-        <v>38</v>
+        <v>64</v>
       </c>
       <c r="I50" s="11" t="s">
         <v>1</v>
@@ -3703,7 +3703,7 @@
         <v>9</v>
       </c>
       <c r="H51" s="13">
-        <v>60</v>
+        <v>43</v>
       </c>
       <c r="I51" s="13" t="s">
         <v>1</v>
@@ -3732,7 +3732,7 @@
         <v>9</v>
       </c>
       <c r="H52" s="11">
-        <v>78</v>
+        <v>57</v>
       </c>
       <c r="I52" s="11" t="s">
         <v>1</v>
@@ -3761,7 +3761,7 @@
         <v>9</v>
       </c>
       <c r="H53" s="13">
-        <v>53</v>
+        <v>91</v>
       </c>
       <c r="I53" s="13" t="s">
         <v>1</v>
@@ -3790,7 +3790,7 @@
         <v>9</v>
       </c>
       <c r="H54" s="11">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="I54" s="11" t="s">
         <v>1</v>
@@ -3819,7 +3819,7 @@
         <v>9</v>
       </c>
       <c r="H55" s="13">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="I55" s="13" t="s">
         <v>1</v>
@@ -3848,7 +3848,7 @@
         <v>9</v>
       </c>
       <c r="H56" s="11">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="I56" s="11" t="s">
         <v>1</v>
@@ -3877,7 +3877,7 @@
         <v>9</v>
       </c>
       <c r="H57" s="13">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="I57" s="13" t="s">
         <v>1</v>
@@ -3906,7 +3906,7 @@
         <v>9</v>
       </c>
       <c r="H58" s="11">
-        <v>69</v>
+        <v>30</v>
       </c>
       <c r="I58" s="11" t="s">
         <v>1</v>
@@ -3935,7 +3935,7 @@
         <v>9</v>
       </c>
       <c r="H59" s="13">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="I59" s="13" t="s">
         <v>1</v>
@@ -3964,7 +3964,7 @@
         <v>9</v>
       </c>
       <c r="H60" s="11">
-        <v>47</v>
+        <v>16</v>
       </c>
       <c r="I60" s="11" t="s">
         <v>1</v>
@@ -3993,7 +3993,7 @@
         <v>9</v>
       </c>
       <c r="H61" s="13">
-        <v>50</v>
+        <v>16</v>
       </c>
       <c r="I61" s="13" t="s">
         <v>1</v>
@@ -4022,7 +4022,7 @@
         <v>9</v>
       </c>
       <c r="H62" s="11">
-        <v>89</v>
+        <v>23</v>
       </c>
       <c r="I62" s="11" t="s">
         <v>1</v>
@@ -4051,7 +4051,7 @@
         <v>9</v>
       </c>
       <c r="H63" s="13">
-        <v>80</v>
+        <v>17</v>
       </c>
       <c r="I63" s="13" t="s">
         <v>1</v>
@@ -4080,7 +4080,7 @@
         <v>9</v>
       </c>
       <c r="H64" s="11">
-        <v>31</v>
+        <v>62</v>
       </c>
       <c r="I64" s="11" t="s">
         <v>1</v>
@@ -4109,7 +4109,7 @@
         <v>9</v>
       </c>
       <c r="H65" s="13">
-        <v>41</v>
+        <v>65</v>
       </c>
       <c r="I65" s="13" t="s">
         <v>1</v>
@@ -4138,7 +4138,7 @@
         <v>9</v>
       </c>
       <c r="H66" s="11">
-        <v>47</v>
+        <v>79</v>
       </c>
       <c r="I66" s="11" t="s">
         <v>1</v>
@@ -4167,7 +4167,7 @@
         <v>9</v>
       </c>
       <c r="H67" s="13">
-        <v>76</v>
+        <v>33</v>
       </c>
       <c r="I67" s="13" t="s">
         <v>1</v>
@@ -4196,7 +4196,7 @@
         <v>9</v>
       </c>
       <c r="H68" s="11">
-        <v>55</v>
+        <v>26</v>
       </c>
       <c r="I68" s="11" t="s">
         <v>1</v>
@@ -4225,7 +4225,7 @@
         <v>9</v>
       </c>
       <c r="H69" s="13">
-        <v>90</v>
+        <v>46</v>
       </c>
       <c r="I69" s="13" t="s">
         <v>1</v>
@@ -4254,7 +4254,7 @@
         <v>9</v>
       </c>
       <c r="H70" s="11">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="I70" s="11" t="s">
         <v>1</v>
@@ -4283,7 +4283,7 @@
         <v>9</v>
       </c>
       <c r="H71" s="13">
-        <v>16</v>
+        <v>81</v>
       </c>
       <c r="I71" s="13" t="s">
         <v>1</v>
@@ -4312,7 +4312,7 @@
         <v>9</v>
       </c>
       <c r="H72" s="11">
-        <v>26</v>
+        <v>77</v>
       </c>
       <c r="I72" s="11" t="s">
         <v>1</v>
@@ -4341,7 +4341,7 @@
         <v>9</v>
       </c>
       <c r="H73" s="13">
-        <v>90</v>
+        <v>47</v>
       </c>
       <c r="I73" s="13" t="s">
         <v>1</v>
@@ -4370,7 +4370,7 @@
         <v>9</v>
       </c>
       <c r="H74" s="11">
-        <v>27</v>
+        <v>90</v>
       </c>
       <c r="I74" s="11" t="s">
         <v>1</v>
